--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +769,7 @@
         <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>6.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1348,10 +1348,10 @@
         <v>2.18</v>
       </c>
       <c r="I5" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.56</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,395 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>19:45:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CA Independiente</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Union Santa Fe</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-08 01:59:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20:20:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Atletico Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Deportivo Pereira</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 04:19:56</t>
+          <t>2026-03-08 06:41:10</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
         <v>1.98</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
@@ -966,7 +966,7 @@
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
         <v>1.79</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 04:19:56</t>
+          <t>2026-03-08 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 04:19:56</t>
+          <t>2026-03-08 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.85</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H5" t="n">
         <v>2.18</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 04:19:56</t>
+          <t>2026-03-08 06:41:10</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G6" t="n">
         <v>1.5</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 04:19:56</t>
+          <t>2026-03-08 06:41:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
         <v>1.6</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 06:41:10</t>
+          <t>2026-03-08 09:01:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bregenz</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>2.62</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2.74</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 06:41:10</t>
+          <t>2026-03-08 09:01:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SK Sturm Graz II</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Liefering</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>1.42</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.43</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,395 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 06:41:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Egyptian Premier</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>El Gounah</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Al-Masry</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-08 06:41:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20:20:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Atletico Bucaramanga</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Deportivo Pereira</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-08 06:41:10</t>
+          <t>2026-03-08 09:01:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
         <v>2.18</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
         <v>1.49</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
         <v>5.1</v>
@@ -960,7 +960,7 @@
         <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
         <v>2.82</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
         <v>1.49</v>
@@ -1154,7 +1154,7 @@
         <v>5.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -775,16 +775,16 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -793,141 +793,141 @@
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,378 +937,1542 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Bregenz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SK Sturm Graz II</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FC Liefering</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al-Masry</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.49</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H10" t="n">
         <v>5.9</v>
       </c>
-      <c r="I4" t="n">
-        <v>110</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
         <v>4.1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K10" t="n">
         <v>6.2</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q10" t="n">
         <v>2.08</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-03-08 13:33:25</t>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -793,19 +793,19 @@
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -978,13 +978,13 @@
         <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
@@ -999,10 +999,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>980</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>980</v>
@@ -1038,7 +1038,7 @@
         <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
         <v>980</v>
@@ -1059,13 +1059,13 @@
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS3" t="n">
         <v>4.2</v>
@@ -1077,7 +1077,7 @@
         <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AW3" t="n">
         <v>4.1</v>
@@ -1104,17 +1104,17 @@
         <v>3.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG3" t="n">
         <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O4" t="n">
         <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
         <v>4.5</v>
@@ -1348,7 +1348,7 @@
         <v>1.83</v>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
@@ -1357,40 +1357,40 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q5" t="n">
         <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1399,7 +1399,7 @@
         <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
@@ -1411,25 +1411,25 @@
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK5" t="n">
         <v>44</v>
@@ -1444,25 +1444,25 @@
         <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AP5" t="n">
         <v>23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV5" t="n">
         <v>9.800000000000001</v>
@@ -1498,11 +1498,11 @@
         <v>29</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
@@ -1533,34 +1533,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
         <v>2.18</v>
       </c>
       <c r="I6" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
         <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
         <v>1.46</v>
@@ -1569,141 +1569,141 @@
         <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE7" t="n">
         <v>2.38</v>
       </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>38</v>
-      </c>
       <c r="BF7" t="n">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT8" t="n">
         <v>9.6</v>
       </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AU8" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,378 +2101,2318 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.65</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.77</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.68</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
         <v>18</v>
       </c>
-      <c r="AB9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>22</v>
+        <v>1.82</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>1.78</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>1.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>1.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>1.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>10.5</v>
+        <v>1.98</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>1.89</v>
       </c>
       <c r="AX9" t="n">
-        <v>38</v>
+        <v>1.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>18</v>
+        <v>1.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>1.83</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>1.91</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>1.92</v>
       </c>
       <c r="BC9" t="n">
-        <v>40</v>
+        <v>1.89</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>1.91</v>
       </c>
       <c r="BE9" t="n">
-        <v>44</v>
+        <v>1.98</v>
       </c>
       <c r="BF9" t="n">
-        <v>23</v>
+        <v>1.98</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>1.98</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 15:45:03</t>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ayr</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Queens Park</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Aldershot</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Carlisle</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Eastleigh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Brackley Town</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tamworth FC</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X14" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gateshead</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Scunthorpe</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sutton Utd</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X17" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.49</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H20" t="n">
         <v>5.9</v>
       </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I20" t="n">
+        <v>110</v>
+      </c>
+      <c r="J20" t="n">
         <v>4.1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K20" t="n">
         <v>6.2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q20" t="n">
         <v>2.08</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-03-08 15:45:03</t>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-08 17:55:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -805,7 +805,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
         <v>1.48</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
         <v>3.15</v>
@@ -993,10 +993,10 @@
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1151,10 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1169,31 +1169,31 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
         <v>1.46</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.83</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.84</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
@@ -1357,7 +1357,7 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1366,31 +1366,31 @@
         <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R5" t="n">
         <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1399,13 +1399,13 @@
         <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
         <v>38</v>
@@ -1423,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
         <v>95</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
@@ -1441,7 +1441,7 @@
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
         <v>7.6</v>
@@ -1456,10 +1456,10 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
         <v>9.4</v>
@@ -1468,7 +1468,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX5" t="n">
         <v>34</v>
@@ -1483,10 +1483,10 @@
         <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BC5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD5" t="n">
         <v>38</v>
@@ -1495,14 +1495,14 @@
         <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.53</v>
@@ -1575,10 +1575,10 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
         <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1760,7 +1760,7 @@
         <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
         <v>1.28</v>
@@ -1769,16 +1769,16 @@
         <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
@@ -1963,16 +1963,16 @@
         <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
         <v>1.84</v>
@@ -2163,10 +2163,10 @@
         <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
         <v>22</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
         <v>1.36</v>
@@ -2345,16 +2345,16 @@
         <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
         <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.22</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G11" t="n">
         <v>3.65</v>
@@ -2527,16 +2527,16 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
         <v>1.44</v>
@@ -2599,7 +2599,7 @@
         <v>980</v>
       </c>
       <c r="AL11" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
         <v>75</v>
@@ -2653,7 +2653,7 @@
         <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
         <v>7.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>32</v>
       </c>
-      <c r="AG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>21</v>
       </c>
-      <c r="AI12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AS12" t="n">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.93</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.98</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.99</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.12</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.14</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.1</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.12</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X13" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>3.9</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="V14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN14" t="n">
         <v>4.5</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X14" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>980</v>
-      </c>
       <c r="AO14" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF14" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG14" t="n">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC15" t="n">
         <v>13</v>
       </c>
-      <c r="J15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD15" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.24</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3464,88 +3464,88 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>980</v>
       </c>
       <c r="Y16" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
         <v>980</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AB16" t="n">
         <v>980</v>
       </c>
       <c r="AC16" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>980</v>
@@ -3554,10 +3554,10 @@
         <v>980</v>
       </c>
       <c r="AG16" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>980</v>
@@ -3572,71 +3572,71 @@
         <v>980</v>
       </c>
       <c r="AM16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
         <v>980</v>
       </c>
       <c r="AO16" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G17" t="n">
         <v>3.1</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
@@ -3685,19 +3685,19 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>1.49</v>
@@ -3706,25 +3706,25 @@
         <v>1.77</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U17" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
         <v>29</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
@@ -3736,10 +3736,10 @@
         <v>22</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3751,19 +3751,19 @@
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
         <v>30</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
       </c>
       <c r="AM17" t="n">
         <v>46</v>
@@ -3781,13 +3781,13 @@
         <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>9.6</v>
@@ -3796,10 +3796,10 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY17" t="n">
         <v>12.5</v>
@@ -3814,7 +3814,7 @@
         <v>42</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>27</v>
@@ -3823,14 +3823,14 @@
         <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG17" t="n">
         <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3861,46 +3861,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I18" t="n">
         <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
         <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
         <v>1.85</v>
@@ -3912,10 +3912,10 @@
         <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
         <v>25</v>
@@ -3924,10 +3924,10 @@
         <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
         <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG18" t="n">
         <v>9.6</v>
@@ -3951,10 +3951,10 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK18" t="n">
         <v>15</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>15.5</v>
       </c>
       <c r="AL18" t="n">
         <v>32</v>
@@ -3981,31 +3981,31 @@
         <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
         <v>9.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
@@ -4014,17 +4014,17 @@
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4061,16 +4061,16 @@
         <v>5.3</v>
       </c>
       <c r="H19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I19" t="n">
         <v>1.66</v>
       </c>
-      <c r="I19" t="n">
-        <v>1.68</v>
-      </c>
       <c r="J19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -4079,16 +4079,16 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R19" t="n">
         <v>1.78</v>
@@ -4103,22 +4103,22 @@
         <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y19" t="n">
         <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AB19" t="n">
         <v>29</v>
@@ -4133,10 +4133,10 @@
         <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>16.5</v>
@@ -4145,25 +4145,25 @@
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK19" t="n">
         <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
         <v>5.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
@@ -4175,10 +4175,10 @@
         <v>16.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV19" t="n">
         <v>9.6</v>
@@ -4193,7 +4193,7 @@
         <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>21</v>
@@ -4202,217 +4202,605 @@
         <v>40</v>
       </c>
       <c r="BC19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD19" t="n">
         <v>40</v>
       </c>
-      <c r="BD19" t="n">
-        <v>42</v>
-      </c>
       <c r="BE19" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CA Independiente</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Union Santa Fe</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-08 20:05:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19:45:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-08 20:05:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Atletico Bucaramanga</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G22" t="n">
         <v>1.49</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H22" t="n">
         <v>5.9</v>
       </c>
-      <c r="I20" t="n">
-        <v>110</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
         <v>4.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K22" t="n">
         <v>6.2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P22" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q22" t="n">
         <v>2.08</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S22" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V22" t="n">
         <v>0</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X22" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y22" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z22" t="n">
         <v>0</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA22" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AB22" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AD22" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE22" t="n">
         <v>0</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AF22" t="n">
         <v>0</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AG22" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH22" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AI22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AJ22" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK22" t="n">
         <v>0</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AL22" t="n">
         <v>0</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AM22" t="n">
         <v>0</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AN22" t="n">
         <v>0</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AO22" t="n">
         <v>0</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP22" t="n">
         <v>0</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ22" t="n">
         <v>0</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR22" t="n">
         <v>0</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AS22" t="n">
         <v>0</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AU22" t="n">
         <v>0</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AV22" t="n">
         <v>0</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AW22" t="n">
         <v>0</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AY22" t="n">
         <v>0</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="AZ22" t="n">
         <v>0</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BA22" t="n">
         <v>0</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB22" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BD22" t="n">
         <v>0</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BE22" t="n">
         <v>0</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BF22" t="n">
         <v>0</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BG22" t="n">
         <v>0</v>
       </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-03-08 17:55:29</t>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -760,16 +760,16 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -808,7 +808,7 @@
         <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -975,10 +975,10 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.86</v>
@@ -987,16 +987,16 @@
         <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
         <v>2.72</v>
@@ -1172,7 +1172,7 @@
         <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.34</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1357,34 +1357,34 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V5" t="n">
         <v>2.2</v>
@@ -1393,7 +1393,7 @@
         <v>1.27</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
         <v>13.5</v>
@@ -1402,13 +1402,13 @@
         <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
         <v>24</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>10</v>
@@ -1426,25 +1426,25 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP5" t="n">
         <v>23</v>
@@ -1456,13 +1456,13 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV5" t="n">
         <v>9.800000000000001</v>
@@ -1483,7 +1483,7 @@
         <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BC5" t="n">
         <v>40</v>
@@ -1498,11 +1498,11 @@
         <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
         <v>2.18</v>
@@ -1554,13 +1554,13 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
         <v>1.46</v>
@@ -1569,134 +1569,134 @@
         <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
         <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR6" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AS6" t="n">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.12</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.12</v>
+        <v>18.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.12</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.12</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.12</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.12</v>
+        <v>7.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.12</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1775,10 +1775,10 @@
         <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1835,49 +1835,49 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW7" t="n">
         <v>2.28</v>
       </c>
-      <c r="AT7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AX7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>2.18</v>
       </c>
-      <c r="AY7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BA7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2.28</v>
       </c>
-      <c r="BB7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BD7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BE7" t="n">
         <v>2.38</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2163,10 +2163,10 @@
         <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
         <v>22</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AR9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AS9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BA9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BC9" t="n">
         <v>1.91</v>
       </c>
-      <c r="BB9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BD9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.91</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>5.7</v>
@@ -2327,7 +2327,7 @@
         <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX10" t="n">
         <v>2.06</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AY10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G11" t="n">
         <v>3.65</v>
@@ -2527,25 +2527,25 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
         <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
         <v>2.28</v>
@@ -2572,7 +2572,7 @@
         <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
@@ -2620,7 +2620,7 @@
         <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
@@ -2644,29 +2644,29 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2736,7 +2736,7 @@
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>1.68</v>
@@ -2793,7 +2793,7 @@
         <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
         <v>90</v>
@@ -2802,7 +2802,7 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
         <v>14</v>
@@ -2814,43 +2814,43 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
         <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
         <v>3.75</v>
@@ -2942,7 +2942,7 @@
         <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
         <v>980</v>
@@ -3011,37 +3011,37 @@
         <v>3.85</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AV13" t="n">
         <v>3.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AX13" t="n">
         <v>3.55</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ13" t="n">
         <v>3.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC13" t="n">
         <v>3.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BE13" t="n">
         <v>3.9</v>
@@ -3050,11 +3050,11 @@
         <v>3.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
         <v>1.43</v>
@@ -3139,7 +3139,7 @@
         <v>3.3</v>
       </c>
       <c r="X14" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Y14" t="n">
         <v>55</v>
@@ -3151,25 +3151,25 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AC14" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AD14" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AI14" t="n">
         <v>110</v>
@@ -3178,31 +3178,31 @@
         <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.5</v>
+        <v>980</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT14" t="n">
         <v>4.9</v>
@@ -3211,10 +3211,10 @@
         <v>5.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AX14" t="n">
         <v>4.6</v>
@@ -3223,10 +3223,10 @@
         <v>4.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BB14" t="n">
         <v>2.4</v>
@@ -3235,20 +3235,20 @@
         <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
         <v>3.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J16" t="n">
         <v>3.3</v>
@@ -3494,7 +3494,7 @@
         <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>5.1</v>
@@ -3521,7 +3521,7 @@
         <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
         <v>1.47</v>
@@ -3545,7 +3545,7 @@
         <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>980</v>
@@ -3560,7 +3560,7 @@
         <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
         <v>980</v>
@@ -3578,22 +3578,22 @@
         <v>980</v>
       </c>
       <c r="AO16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
@@ -3605,7 +3605,7 @@
         <v>17.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>3.65</v>
       </c>
       <c r="AY16" t="n">
         <v>9.6</v>
@@ -3614,29 +3614,29 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
         <v>19</v>
       </c>
       <c r="BD16" t="n">
-        <v>22</v>
+        <v>3.95</v>
       </c>
       <c r="BE16" t="n">
         <v>4</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="n">
         <v>2.3</v>
@@ -3691,25 +3691,25 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q17" t="n">
         <v>1.49</v>
       </c>
       <c r="R17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S17" t="n">
         <v>2.24</v>
       </c>
       <c r="T17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U17" t="n">
         <v>2.96</v>
@@ -3718,10 +3718,10 @@
         <v>1.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y17" t="n">
         <v>18</v>
@@ -3742,10 +3742,10 @@
         <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
@@ -3754,25 +3754,25 @@
         <v>13.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ17" t="n">
         <v>50</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN17" t="n">
         <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP17" t="n">
         <v>25</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3811,10 +3811,10 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>27</v>
@@ -3823,14 +3823,14 @@
         <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
         <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
         <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.34</v>
@@ -3885,22 +3885,22 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
         <v>1.85</v>
@@ -3912,13 +3912,13 @@
         <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X18" t="n">
         <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>55</v>
@@ -3930,7 +3930,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
@@ -3939,7 +3939,7 @@
         <v>85</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>9.6</v>
@@ -3948,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
         <v>14.5</v>
@@ -3957,7 +3957,7 @@
         <v>15</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
@@ -3966,16 +3966,16 @@
         <v>7.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AS18" t="n">
         <v>46</v>
@@ -3987,10 +3987,10 @@
         <v>9.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AX18" t="n">
         <v>9.199999999999999</v>
@@ -4002,7 +4002,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I19" t="n">
         <v>1.66</v>
@@ -4070,10 +4070,10 @@
         <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -4085,7 +4085,7 @@
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q19" t="n">
         <v>1.48</v>
@@ -4094,7 +4094,7 @@
         <v>1.78</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
         <v>1.57</v>
@@ -4103,7 +4103,7 @@
         <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
@@ -4136,7 +4136,7 @@
         <v>46</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
         <v>16.5</v>
@@ -4148,13 +4148,13 @@
         <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
         <v>36</v>
@@ -4163,7 +4163,7 @@
         <v>5.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
@@ -4175,7 +4175,7 @@
         <v>16.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -4187,7 +4187,7 @@
         <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AY19" t="n">
         <v>19</v>
@@ -4202,10 +4202,10 @@
         <v>40</v>
       </c>
       <c r="BC19" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD19" t="n">
         <v>42</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>40</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4267,13 +4267,13 @@
         <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.47</v>
@@ -4285,16 +4285,16 @@
         <v>2.56</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
         <v>1.31</v>
@@ -4306,46 +4306,46 @@
         <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4461,16 +4461,16 @@
         <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
         <v>1.41</v>
@@ -4479,70 +4479,70 @@
         <v>2.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>6.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G22" t="n">
         <v>1.49</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4655,152 +4655,152 @@
         <v>6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
         <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -996,7 +996,7 @@
         <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
         <v>980</v>
@@ -1059,10 +1059,10 @@
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR3" t="n">
         <v>3.95</v>
@@ -1071,22 +1071,22 @@
         <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AW3" t="n">
         <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ3" t="n">
         <v>3.65</v>
@@ -1095,7 +1095,7 @@
         <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BC3" t="n">
         <v>3.65</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
         <v>2.72</v>
@@ -1196,7 +1196,7 @@
         <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.82</v>
       </c>
       <c r="I5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
@@ -1381,13 +1381,13 @@
         <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
         <v>2.64</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W5" t="n">
         <v>1.27</v>
@@ -1396,7 +1396,7 @@
         <v>25</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
@@ -1423,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
@@ -1453,13 +1453,13 @@
         <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>9.6</v>
@@ -1471,7 +1471,7 @@
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
@@ -1486,13 +1486,13 @@
         <v>55</v>
       </c>
       <c r="BC5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD5" t="n">
         <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
         <v>30</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="n">
         <v>2.18</v>
@@ -1548,7 +1548,7 @@
         <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1569,16 +1569,16 @@
         <v>2.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V6" t="n">
         <v>1.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -1775,7 +1775,7 @@
         <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.52</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,113 +2106,113 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>1.79</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL9" t="n">
         <v>65</v>
       </c>
-      <c r="AK9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="BE9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="BF9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH11" t="n">
         <v>24</v>
       </c>
-      <c r="AF11" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
       <c r="AI11" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.5</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>1.87</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>1.94</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>1.79</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>18.5</v>
+        <v>1.91</v>
       </c>
       <c r="AX11" t="n">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>1.85</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>1.94</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>1.93</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.75</v>
@@ -2942,7 +2942,7 @@
         <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
         <v>980</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
         <v>3.3</v>
@@ -3521,7 +3521,7 @@
         <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
         <v>1.47</v>
@@ -3620,7 +3620,7 @@
         <v>3.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="BD16" t="n">
         <v>3.95</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3673,10 +3673,10 @@
         <v>3.15</v>
       </c>
       <c r="H17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.32</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
@@ -3697,25 +3697,25 @@
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S17" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.48</v>
       </c>
       <c r="U17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W17" t="n">
         <v>1.46</v>
@@ -3745,7 +3745,7 @@
         <v>19.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
         <v>14.5</v>
@@ -3760,7 +3760,7 @@
         <v>50</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>29</v>
@@ -3775,7 +3775,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3811,7 +3811,7 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3823,14 +3823,14 @@
         <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I18" t="n">
         <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
         <v>4.8</v>
@@ -3897,7 +3897,7 @@
         <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
         <v>2.88</v>
@@ -3924,13 +3924,13 @@
         <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
@@ -3963,7 +3963,7 @@
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO18" t="n">
         <v>85</v>
@@ -3975,7 +3975,7 @@
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AS18" t="n">
         <v>46</v>
@@ -3984,13 +3984,13 @@
         <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV18" t="n">
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AX18" t="n">
         <v>9.199999999999999</v>
@@ -3999,19 +3999,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
         <v>65</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE18" t="n">
         <v>38</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>5.1</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H19" t="n">
         <v>1.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J19" t="n">
         <v>4.9</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -4085,7 +4085,7 @@
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q19" t="n">
         <v>1.48</v>
@@ -4103,13 +4103,13 @@
         <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="n">
         <v>14.5</v>
@@ -4118,7 +4118,7 @@
         <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AB19" t="n">
         <v>29</v>
@@ -4187,10 +4187,10 @@
         <v>13.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>15.5</v>
@@ -4202,10 +4202,10 @@
         <v>40</v>
       </c>
       <c r="BC19" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BD19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.56</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.81</v>
-      </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW20" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AX20" t="n">
         <v>13</v>
       </c>
-      <c r="AH20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
+      <c r="AY20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC20" t="n">
         <v>36</v>
       </c>
-      <c r="AK20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY20" t="n">
+      <c r="BD20" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG20" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.56</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB21" t="n">
         <v>7.4</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="BC21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="BF21" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="BG21" t="n">
         <v>70</v>
       </c>
-      <c r="AF21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4691,116 +4691,1086 @@
         <v>3</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="Y22" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>980</v>
       </c>
       <c r="AC22" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AD22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Internacional de Palmira</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Newells</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medell</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL27" t="n">
         <v>65</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AX22" t="n">
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW27" t="n">
         <v>2.22</v>
       </c>
-      <c r="AY22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-03-08 22:14:33</t>
+      <c r="AX27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -790,13 +790,13 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -805,11 +805,11 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.51</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW3" t="n">
         <v>4.1</v>
@@ -1098,7 +1098,7 @@
         <v>3.65</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD3" t="n">
         <v>3.95</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
         <v>2.72</v>
@@ -1172,7 +1172,7 @@
         <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
         <v>2.34</v>
@@ -1181,7 +1181,7 @@
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
         <v>2.08</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1411,7 +1411,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
@@ -1462,7 +1462,7 @@
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
         <v>9.800000000000001</v>
@@ -1471,7 +1471,7 @@
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY5" t="n">
         <v>15.5</v>
@@ -1495,14 +1495,14 @@
         <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG5" t="n">
         <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
         <v>4.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,16 +1557,16 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.16</v>
@@ -1575,16 +1575,16 @@
         <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
         <v>8.199999999999999</v>
@@ -1641,7 +1641,7 @@
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.9</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
         <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -1763,19 +1763,19 @@
         <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
         <v>1.52</v>
@@ -1784,10 +1784,10 @@
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -1799,7 +1799,7 @@
         <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.1</v>
@@ -1844,53 +1844,53 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV7" t="n">
         <v>2.1</v>
       </c>
-      <c r="AU7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AW7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA7" t="n">
         <v>2.28</v>
       </c>
-      <c r="AX7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BB7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BC7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD7" t="n">
         <v>2.28</v>
       </c>
-      <c r="BD7" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BE7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2115,43 +2115,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
         <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
         <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
         <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
         <v>3.35</v>
@@ -2175,7 +2175,7 @@
         <v>23</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,10 +2184,10 @@
         <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AR9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AV9" t="n">
         <v>2.28</v>
       </c>
-      <c r="AS9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AW9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
         <v>2.12</v>
@@ -2321,13 +2321,13 @@
         <v>2.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2342,19 +2342,19 @@
         <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
         <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
         <v>1.71</v>
@@ -2375,7 +2375,7 @@
         <v>980</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2387,7 +2387,7 @@
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>15.5</v>
@@ -2405,13 +2405,13 @@
         <v>980</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
@@ -2426,19 +2426,19 @@
         <v>13</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX10" t="n">
         <v>21</v>
@@ -2450,29 +2450,29 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.35</v>
@@ -2542,16 +2542,16 @@
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
@@ -2596,7 +2596,7 @@
         <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -2617,16 +2617,16 @@
         <v>1.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AT11" t="n">
         <v>1.79</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AV11" t="n">
         <v>1.8</v>
@@ -2635,13 +2635,13 @@
         <v>1.91</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AY11" t="n">
         <v>1.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BA11" t="n">
         <v>1.93</v>
@@ -2650,23 +2650,23 @@
         <v>1.94</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BD11" t="n">
         <v>1.93</v>
       </c>
       <c r="BE11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2939,10 +2939,10 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
         <v>980</v>
@@ -2999,16 +2999,16 @@
         <v>980</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT13" t="n">
         <v>3.35</v>
@@ -3017,22 +3017,22 @@
         <v>3.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW13" t="n">
         <v>3.75</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AY13" t="n">
         <v>3.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB13" t="n">
         <v>3.8</v>
@@ -3044,7 +3044,7 @@
         <v>3.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
         <v>3.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G14" t="n">
         <v>1.43</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I14" t="n">
         <v>12.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
         <v>5.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
         <v>3.2</v>
@@ -3124,7 +3124,7 @@
         <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="T14" t="n">
         <v>1.7</v>
@@ -3142,7 +3142,7 @@
         <v>980</v>
       </c>
       <c r="Y14" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3175,7 +3175,7 @@
         <v>110</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AK14" t="n">
         <v>980</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AR14" t="n">
         <v>1.65</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.89</v>
+        <v>6.6</v>
       </c>
       <c r="AW14" t="n">
         <v>1.66</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY14" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="BF14" t="n">
         <v>3.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>4.8</v>
@@ -3303,34 +3303,34 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q15" t="n">
         <v>1.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="T15" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>980</v>
@@ -3381,68 +3381,68 @@
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>980</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
         <v>980</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD15" t="n">
         <v>6</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BE15" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
         <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
         <v>3.3</v>
@@ -3494,7 +3494,7 @@
         <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
         <v>5.1</v>
@@ -3584,7 +3584,7 @@
         <v>3.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR16" t="n">
         <v>3.6</v>
@@ -3623,7 +3623,7 @@
         <v>3.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
         <v>4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>3.15</v>
       </c>
       <c r="H17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.28</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.3</v>
-      </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -3691,7 +3691,7 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
@@ -3715,7 +3715,7 @@
         <v>2.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W17" t="n">
         <v>1.46</v>
@@ -3724,7 +3724,7 @@
         <v>28</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
@@ -3745,10 +3745,10 @@
         <v>19.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
         <v>13.5</v>
@@ -3775,7 +3775,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
@@ -3799,7 +3799,7 @@
         <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY17" t="n">
         <v>12.5</v>
@@ -3811,7 +3811,7 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3826,11 +3826,11 @@
         <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G18" t="n">
         <v>1.58</v>
@@ -3990,7 +3990,7 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX18" t="n">
         <v>9.199999999999999</v>
@@ -4002,7 +4002,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
@@ -4011,7 +4011,7 @@
         <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE18" t="n">
         <v>38</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>5.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="J19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -4085,13 +4085,13 @@
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q19" t="n">
         <v>1.48</v>
       </c>
       <c r="R19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S19" t="n">
         <v>2.22</v>
@@ -4103,7 +4103,7 @@
         <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
@@ -4121,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="AB19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC19" t="n">
         <v>11.5</v>
@@ -4130,19 +4130,19 @@
         <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF19" t="n">
         <v>46</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH19" t="n">
         <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
         <v>110</v>
@@ -4190,7 +4190,7 @@
         <v>40</v>
       </c>
       <c r="AY19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
         <v>15.5</v>
@@ -4199,10 +4199,10 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD19" t="n">
         <v>40</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>2.82</v>
@@ -4273,13 +4273,13 @@
         <v>1.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O20" t="n">
         <v>1.64</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q20" t="n">
         <v>2.96</v>
@@ -4297,10 +4297,10 @@
         <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
         <v>7.4</v>
@@ -4336,7 +4336,7 @@
         <v>980</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
         <v>980</v>
@@ -4348,7 +4348,7 @@
         <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN20" t="n">
         <v>1000</v>
@@ -4366,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AT20" t="n">
         <v>6.2</v>
@@ -4378,7 +4378,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
@@ -4387,13 +4387,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>36</v>
@@ -4402,17 +4402,17 @@
         <v>65</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H21" t="n">
         <v>3.75</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
         <v>3.5</v>
@@ -4467,7 +4467,7 @@
         <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
         <v>1.55</v>
@@ -4479,7 +4479,7 @@
         <v>2.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S21" t="n">
         <v>5.6</v>
@@ -4488,13 +4488,13 @@
         <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
@@ -4512,7 +4512,7 @@
         <v>6.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>980</v>
@@ -4542,7 +4542,7 @@
         <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
@@ -4557,7 +4557,7 @@
         <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS21" t="n">
         <v>65</v>
@@ -4581,32 +4581,32 @@
         <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG21" t="n">
         <v>70</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G22" t="n">
         <v>1.49</v>
@@ -4661,7 +4661,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4858,19 +4858,19 @@
         <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
         <v>1.13</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -5058,7 +5058,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R24" t="n">
         <v>1.37</v>
@@ -5136,10 +5136,10 @@
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>5.9</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -5276,13 +5276,13 @@
         <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Z25" t="n">
         <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB25" t="n">
         <v>10</v>
@@ -5294,16 +5294,16 @@
         <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5312,7 +5312,7 @@
         <v>85</v>
       </c>
       <c r="AK25" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5327,10 +5327,10 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AR25" t="n">
         <v>13.5</v>
@@ -5342,25 +5342,25 @@
         <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BB25" t="n">
         <v>38</v>
@@ -5369,20 +5369,20 @@
         <v>36</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
         <v>2.08</v>
       </c>
       <c r="I26" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J26" t="n">
         <v>3.1</v>
@@ -5437,146 +5437,146 @@
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>1.54</v>
+        <v>2.52</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT26" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY26" t="n">
         <v>16</v>
       </c>
-      <c r="AC26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>2.06</v>
+        <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.14</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
         <v>3.4</v>
@@ -5622,7 +5622,7 @@
         <v>2.96</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5649,7 +5649,7 @@
         <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U27" t="n">
         <v>1.78</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>2.04</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AR27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AX27" t="n">
         <v>2.14</v>
       </c>
-      <c r="AS27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AY27" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
         <v>2.96</v>
@@ -766,7 +766,7 @@
         <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -805,7 +805,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
         <v>1.51</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
         <v>5.1</v>
@@ -963,10 +963,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.34</v>
@@ -981,10 +981,10 @@
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -1002,7 +1002,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
         <v>980</v>
@@ -1038,7 +1038,7 @@
         <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>980</v>
@@ -1050,7 +1050,7 @@
         <v>980</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
         <v>980</v>
@@ -1059,62 +1059,62 @@
         <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="AX3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB3" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.65</v>
       </c>
       <c r="BC3" t="n">
         <v>3.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
         <v>9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1151,28 +1151,28 @@
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.34</v>
@@ -1181,28 +1181,28 @@
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,13 +1211,13 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1345,10 @@
         <v>4.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
@@ -1369,28 +1369,28 @@
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
         <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
         <v>25</v>
@@ -1414,7 +1414,7 @@
         <v>10.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF5" t="n">
         <v>38</v>
@@ -1450,19 +1450,19 @@
         <v>23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV5" t="n">
         <v>9.800000000000001</v>
@@ -1483,26 +1483,26 @@
         <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BC5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD5" t="n">
         <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG5" t="n">
         <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
@@ -1557,7 +1557,7 @@
         <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
         <v>1.59</v>
@@ -1578,10 +1578,10 @@
         <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
         <v>1.29</v>
@@ -1590,7 +1590,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
         <v>13.5</v>
@@ -1608,7 +1608,7 @@
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
         <v>1000</v>
@@ -1632,13 +1632,13 @@
         <v>130</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>7</v>
@@ -1650,19 +1650,19 @@
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>18.5</v>
@@ -1674,29 +1674,29 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
         <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -1766,10 +1766,10 @@
         <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>1.84</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
         <v>1.75</v>
@@ -2151,134 +2151,134 @@
         <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
         <v>2.1</v>
       </c>
       <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC9" t="n">
         <v>18</v>
       </c>
-      <c r="Y9" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD9" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
         <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2339,7 +2339,7 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.72</v>
@@ -2357,7 +2357,7 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
         <v>1.37</v>
@@ -2375,7 +2375,7 @@
         <v>980</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2399,19 +2399,19 @@
         <v>980</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
         <v>980</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
@@ -2429,7 +2429,7 @@
         <v>6.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
@@ -2453,26 +2453,26 @@
         <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE10" t="n">
         <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2506,22 +2506,22 @@
         <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.6</v>
       </c>
       <c r="I11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -2536,7 +2536,7 @@
         <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
@@ -2545,34 +2545,34 @@
         <v>2.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z11" t="n">
         <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -2581,10 +2581,10 @@
         <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.37</v>
@@ -2757,10 +2757,10 @@
         <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
@@ -2769,10 +2769,10 @@
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>16.5</v>
@@ -2781,7 +2781,7 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -2802,19 +2802,19 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -2823,44 +2823,44 @@
         <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2915,7 +2915,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
@@ -2924,7 +2924,7 @@
         <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
@@ -2939,7 +2939,7 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
         <v>1.73</v>
@@ -2999,62 +2999,62 @@
         <v>980</v>
       </c>
       <c r="AP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT13" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AU13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AW13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX13" t="n">
         <v>3.9</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY13" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF13" t="n">
         <v>3.8</v>
       </c>
-      <c r="BC13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>1.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
         <v>4.6</v>
@@ -3103,7 +3103,7 @@
         <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
         <v>1.02</v>
@@ -3184,7 +3184,7 @@
         <v>980</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
         <v>980</v>
@@ -3196,10 +3196,10 @@
         <v>1.82</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AS14" t="n">
         <v>1.67</v>
@@ -3226,13 +3226,13 @@
         <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD14" t="n">
         <v>1.81</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
@@ -3297,10 +3297,10 @@
         <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>5.5</v>
@@ -3309,16 +3309,16 @@
         <v>1.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
         <v>1.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
         <v>1.54</v>
@@ -3330,7 +3330,7 @@
         <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X15" t="n">
         <v>980</v>
@@ -3381,68 +3381,68 @@
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>980</v>
       </c>
       <c r="AO15" t="n">
         <v>980</v>
       </c>
       <c r="AP15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV15" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AW15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6</v>
-      </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3476,25 +3476,25 @@
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.24</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>5.1</v>
@@ -3503,7 +3503,7 @@
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
         <v>1.5</v>
@@ -3515,16 +3515,16 @@
         <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X16" t="n">
         <v>980</v>
@@ -3542,7 +3542,7 @@
         <v>980</v>
       </c>
       <c r="AC16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD16" t="n">
         <v>15.5</v>
@@ -3554,89 +3554,89 @@
         <v>980</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO16" t="n">
         <v>18</v>
       </c>
-      <c r="AI16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AP16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AR16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>3.6</v>
       </c>
-      <c r="AS16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11</v>
-      </c>
       <c r="BA16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
         <v>11.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.03</v>
@@ -3694,25 +3694,25 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>1.78</v>
@@ -3721,7 +3721,7 @@
         <v>1.46</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y17" t="n">
         <v>17.5</v>
@@ -3757,10 +3757,10 @@
         <v>24</v>
       </c>
       <c r="AJ17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
         <v>29</v>
@@ -3769,28 +3769,28 @@
         <v>44</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AQ17" t="n">
         <v>16</v>
       </c>
       <c r="AR17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>10.5</v>
@@ -3811,7 +3811,7 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3820,17 +3820,17 @@
         <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
         <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
         <v>4.8</v>
@@ -3891,19 +3891,19 @@
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
@@ -3915,7 +3915,7 @@
         <v>2.72</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>24</v>
@@ -3927,10 +3927,10 @@
         <v>190</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
@@ -3960,7 +3960,7 @@
         <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
         <v>7.2</v>
@@ -3969,7 +3969,7 @@
         <v>85</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>22</v>
@@ -3990,10 +3990,10 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
@@ -4002,13 +4002,13 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB18" t="n">
         <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K19" t="n">
         <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -4085,25 +4085,25 @@
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q19" t="n">
         <v>1.48</v>
       </c>
       <c r="R19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S19" t="n">
         <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
         <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="W19" t="n">
         <v>1.23</v>
@@ -4112,22 +4112,22 @@
         <v>32</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB19" t="n">
         <v>28</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE19" t="n">
         <v>14.5</v>
@@ -4136,7 +4136,7 @@
         <v>46</v>
       </c>
       <c r="AG19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
         <v>16.5</v>
@@ -4151,7 +4151,7 @@
         <v>50</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
         <v>60</v>
@@ -4166,13 +4166,13 @@
         <v>29</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>26</v>
@@ -4184,13 +4184,13 @@
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>15.5</v>
@@ -4199,10 +4199,10 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC19" t="n">
         <v>44</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>46</v>
       </c>
       <c r="BD19" t="n">
         <v>40</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H20" t="n">
         <v>3.3</v>
@@ -4267,7 +4267,7 @@
         <v>3.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
         <v>1.16</v>
@@ -4285,7 +4285,7 @@
         <v>2.96</v>
       </c>
       <c r="R20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S20" t="n">
         <v>6.4</v>
@@ -4294,13 +4294,13 @@
         <v>2.26</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
         <v>7.4</v>
@@ -4342,10 +4342,10 @@
         <v>980</v>
       </c>
       <c r="AK20" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM20" t="n">
         <v>300</v>
@@ -4357,7 +4357,7 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.6</v>
@@ -4378,7 +4378,7 @@
         <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
@@ -4393,7 +4393,7 @@
         <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC20" t="n">
         <v>36</v>
@@ -4405,14 +4405,14 @@
         <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
         <v>1.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>1.35</v>
       </c>
       <c r="G22" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4655,28 +4655,28 @@
         <v>6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
         <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
         <v>2.28</v>
@@ -4685,10 +4685,10 @@
         <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X22" t="n">
         <v>980</v>
@@ -4703,7 +4703,7 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>980</v>
+        <v>6.4</v>
       </c>
       <c r="AC22" t="n">
         <v>980</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>980</v>
+        <v>7.2</v>
       </c>
       <c r="AG22" t="n">
         <v>980</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU22" t="n">
         <v>5.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="AX22" t="n">
         <v>5.8</v>
       </c>
       <c r="AY22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB22" t="n">
         <v>5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.9</v>
       </c>
       <c r="BC22" t="n">
         <v>6</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5043,13 +5043,13 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>1.3</v>
@@ -5064,7 +5064,7 @@
         <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
         <v>1.71</v>
@@ -5082,7 +5082,7 @@
         <v>18</v>
       </c>
       <c r="Y24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
         <v>34</v>
@@ -5094,7 +5094,7 @@
         <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
         <v>18.5</v>
@@ -5136,13 +5136,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -5154,7 +5154,7 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5166,7 +5166,7 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB24" t="n">
         <v>21</v>
@@ -5175,20 +5175,20 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF24" t="n">
         <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>2.8</v>
       </c>
       <c r="G25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
         <v>3.1</v>
@@ -5240,13 +5240,13 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N25" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="O25" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="P25" t="n">
         <v>1.38</v>
@@ -5255,134 +5255,134 @@
         <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT25" t="n">
         <v>6.2</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6</v>
-      </c>
       <c r="AU25" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.06</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>2.04</v>
+        <v>5.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.14</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.28</v>
+        <v>7.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.28</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.28</v>
+        <v>50</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I26" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J26" t="n">
         <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
         <v>1.54</v>
@@ -5437,16 +5437,16 @@
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O26" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
         <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
         <v>1.19</v>
@@ -5461,13 +5461,13 @@
         <v>1.76</v>
       </c>
       <c r="V26" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" t="n">
         <v>7.4</v>
@@ -5476,7 +5476,7 @@
         <v>13</v>
       </c>
       <c r="AA26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB26" t="n">
         <v>12</v>
@@ -5494,7 +5494,7 @@
         <v>32</v>
       </c>
       <c r="AG26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>25</v>
@@ -5503,7 +5503,7 @@
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
         <v>75</v>
@@ -5518,7 +5518,7 @@
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP26" t="n">
         <v>8</v>
@@ -5554,29 +5554,29 @@
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG26" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
         <v>2.96</v>
@@ -5628,7 +5628,7 @@
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
         <v>1.84</v>
@@ -5652,7 +5652,7 @@
         <v>1.55</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5661,7 +5661,7 @@
         <v>1.47</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
         <v>15.5</v>
@@ -5691,7 +5691,7 @@
         <v>17.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5721,7 +5721,7 @@
         <v>2.04</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AS27" t="n">
         <v>2.34</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>FK Qabala</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,34 +781,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bregenz</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>2.76</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1136,25 +1136,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SK Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Liefering</t>
+          <t>Bregenz</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1163,159 +1163,159 @@
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AD4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN4" t="n">
         <v>14</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>3.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SK Sturm Graz II</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FC Liefering</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.83</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>14</v>
       </c>
-      <c r="Z5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.47</v>
+        <v>2.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>75</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG6" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,120 +1713,120 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dumbarton</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.08</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.26</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.18</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.1</v>
+        <v>15.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.16</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.36</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.36</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Annan</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.2</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
         <v>17</v>
       </c>
-      <c r="AI10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB11" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>18</v>
-      </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AJ11" t="n">
         <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.1</v>
+        <v>9.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.26</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.2</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.12</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.18</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.26</v>
+        <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.28</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.38</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.38</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.27</v>
       </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
         <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>1.97</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>2.26</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>2.16</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.1</v>
+        <v>2.28</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>2.26</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>2.28</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>2.38</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.18</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.34</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>980</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3076,67 +3076,67 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.38</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W14" t="n">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
       <c r="X14" t="n">
         <v>980</v>
@@ -3145,22 +3145,22 @@
         <v>980</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
         <v>980</v>
       </c>
       <c r="AC14" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>980</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF14" t="n">
         <v>980</v>
@@ -3172,7 +3172,7 @@
         <v>980</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="AJ14" t="n">
         <v>980</v>
@@ -3184,71 +3184,71 @@
         <v>980</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
         <v>980</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.85</v>
+        <v>3.85</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.66</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.66</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.77</v>
+        <v>3.85</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.81</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.66</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3270,88 +3270,88 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="n">
-        <v>1.97</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.1</v>
       </c>
-      <c r="I15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.51</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W15" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
         <v>980</v>
       </c>
       <c r="Y15" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
         <v>980</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AB15" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
         <v>980</v>
@@ -3360,10 +3360,10 @@
         <v>980</v>
       </c>
       <c r="AG15" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>980</v>
@@ -3378,71 +3378,71 @@
         <v>980</v>
       </c>
       <c r="AM15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN15" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU15" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.9</v>
       </c>
-      <c r="AV15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94</v>
+        <v>1.44</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT16" t="n">
         <v>5.1</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X16" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AU16" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.55</v>
+        <v>1.84</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AZ16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3.6</v>
       </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>1.66</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.26</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="T17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR17" t="n">
         <v>7</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X17" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>26</v>
+        <v>5.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA17" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>5.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.56</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3888,22 +3888,22 @@
         <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
@@ -3912,28 +3912,28 @@
         <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
         <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>85</v>
@@ -3963,7 +3963,7 @@
         <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO18" t="n">
         <v>85</v>
@@ -3972,7 +3972,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
         <v>48</v>
@@ -3981,25 +3981,25 @@
         <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
         <v>65</v>
@@ -4008,23 +4008,23 @@
         <v>13.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
         <v>75</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>5.3</v>
       </c>
       <c r="H19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I19" t="n">
         <v>1.65</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.66</v>
       </c>
       <c r="J19" t="n">
         <v>4.9</v>
@@ -4079,28 +4079,28 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S19" t="n">
         <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
         <v>2.52</v>
@@ -4118,22 +4118,22 @@
         <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB19" t="n">
         <v>28</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>14.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -4148,10 +4148,10 @@
         <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>60</v>
@@ -4163,10 +4163,10 @@
         <v>5.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
         <v>12.5</v>
@@ -4184,7 +4184,7 @@
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX19" t="n">
         <v>42</v>
@@ -4199,33 +4199,33 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD19" t="n">
         <v>40</v>
       </c>
       <c r="BE19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG19" t="n">
         <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,120 +4235,120 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>6.4</v>
+        <v>1.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
         <v>1000</v>
@@ -4357,69 +4357,69 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>2.32</v>
       </c>
       <c r="I21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.1</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.55</v>
+        <v>2.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="R21" t="n">
-        <v>1.19</v>
+        <v>1.81</v>
       </c>
       <c r="S21" t="n">
-        <v>5.6</v>
+        <v>2.16</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="Y21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC21" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD21" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>19.5</v>
       </c>
       <c r="AF21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY21" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG21" t="n">
         <v>9</v>
       </c>
-      <c r="AR21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>70</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.45</v>
+        <v>2.86</v>
       </c>
       <c r="H22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y22" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I22" t="n">
+      <c r="Z22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="AG22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT22" t="n">
         <v>6.2</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AU22" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.1</v>
+        <v>65</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,120 +4817,120 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="G24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS24" t="n">
         <v>2.16</v>
       </c>
-      <c r="H24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6</v>
-      </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.7</v>
+        <v>2.16</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.8</v>
+        <v>2.42</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>2.16</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.7</v>
+        <v>2.16</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,120 +5205,120 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>1.29</v>
       </c>
       <c r="R25" t="n">
         <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>6.8</v>
+        <v>1.29</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
         <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
         <v>1000</v>
@@ -5327,69 +5327,69 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I26" t="n">
         <v>4.1</v>
       </c>
-      <c r="G26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.28</v>
-      </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="X26" t="n">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="AK26" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="n">
         <v>110</v>
       </c>
-      <c r="AM26" t="n">
-        <v>220</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO26" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS26" t="n">
         <v>6</v>
       </c>
-      <c r="AR26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY26" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,572 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medell</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.1</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
       </c>
       <c r="W27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-09 06:53:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-09 06:53:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medell</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.47</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X29" t="n">
         <v>18</v>
       </c>
-      <c r="Y27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
         <v>28</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AD29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE29" t="n">
         <v>48</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AF29" t="n">
         <v>25</v>
       </c>
-      <c r="AG27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
         <v>24</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
         <v>44</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AL29" t="n">
         <v>65</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
         <v>2.08</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AQ29" t="n">
         <v>2.04</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AR29" t="n">
         <v>2.18</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AS29" t="n">
         <v>2.34</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AT29" t="n">
         <v>2.04</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AU29" t="n">
         <v>1.92</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AV29" t="n">
         <v>2.08</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AW29" t="n">
         <v>2.24</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AX29" t="n">
         <v>2.14</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AY29" t="n">
         <v>2.08</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="AZ29" t="n">
         <v>2.14</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BA29" t="n">
         <v>2.34</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB29" t="n">
         <v>2.34</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BC29" t="n">
         <v>2.24</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BD29" t="n">
         <v>2.28</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BE29" t="n">
         <v>2.36</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BF29" t="n">
         <v>2.34</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BG29" t="n">
         <v>2.34</v>
       </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-09 04:43:26</t>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7</v>
+        <v>2.94</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AP2" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>50</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>28</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>50</v>
+        <v>5.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
         <v>2.66</v>
@@ -963,22 +963,22 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
         <v>2.14</v>
@@ -987,16 +987,16 @@
         <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
         <v>1.5</v>
@@ -1005,116 +1005,116 @@
         <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
@@ -1169,13 +1169,13 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
         <v>1.93</v>
@@ -1184,7 +1184,7 @@
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
         <v>1.87</v>
@@ -1196,7 +1196,7 @@
         <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>980</v>
@@ -1223,7 +1223,7 @@
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AG4" t="n">
         <v>980</v>
@@ -1247,68 +1247,68 @@
         <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AO4" t="n">
         <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
         <v>9</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1366,25 +1366,25 @@
         <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
         <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="T5" t="n">
         <v>1.57</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
         <v>1.6</v>
@@ -1450,59 +1450,59 @@
         <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
         <v>4.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
         <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
         <v>14.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
         <v>1.82</v>
@@ -1545,10 +1545,10 @@
         <v>1.83</v>
       </c>
       <c r="J6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.28</v>
@@ -1557,7 +1557,7 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
@@ -1569,13 +1569,13 @@
         <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
         <v>2.62</v>
@@ -1638,7 +1638,7 @@
         <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP6" t="n">
         <v>23</v>
@@ -1677,7 +1677,7 @@
         <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC6" t="n">
         <v>40</v>
@@ -1692,11 +1692,11 @@
         <v>30</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1733,16 +1733,16 @@
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I7" t="n">
         <v>2.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.51</v>
@@ -1751,7 +1751,7 @@
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
         <v>1.59</v>
@@ -1772,7 +1772,7 @@
         <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
         <v>1.73</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>5.9</v>
@@ -1859,7 +1859,7 @@
         <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY7" t="n">
         <v>15.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
         <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
@@ -1939,152 +1939,152 @@
         <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
         <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.47</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF8" t="n">
         <v>23</v>
       </c>
-      <c r="Y8" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF8" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BG8" t="n">
-        <v>2.36</v>
+        <v>17.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
         <v>4.2</v>
@@ -2130,7 +2130,7 @@
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
@@ -2151,10 +2151,10 @@
         <v>1.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2166,7 +2166,7 @@
         <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H10" t="n">
         <v>4.8</v>
@@ -2324,10 +2324,10 @@
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H12" t="n">
         <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2718,149 +2718,149 @@
         <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF12" t="n">
         <v>18</v>
       </c>
-      <c r="Z12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5</v>
-      </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>1.97</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.2</v>
+        <v>2.08</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>1.98</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="BF13" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
@@ -3109,146 +3109,146 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X14" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV14" t="n">
         <v>3.85</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X14" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AW14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE14" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY14" t="n">
+      <c r="BF14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG14" t="n">
         <v>3.55</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.56</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
         <v>1.5</v>
@@ -3336,19 +3336,19 @@
         <v>980</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AA15" t="n">
         <v>980</v>
       </c>
       <c r="AB15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
         <v>15.5</v>
@@ -3357,10 +3357,10 @@
         <v>980</v>
       </c>
       <c r="AF15" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -3378,71 +3378,71 @@
         <v>980</v>
       </c>
       <c r="AM15" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AZ15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4</v>
-      </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="n">
         <v>5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
         <v>3.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="S16" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.1</v>
       </c>
       <c r="W16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X16" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3.25</v>
       </c>
-      <c r="X16" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="BG16" t="n">
         <v>1.83</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
         <v>1.97</v>
@@ -3676,25 +3676,25 @@
         <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
         <v>2.56</v>
@@ -3706,7 +3706,7 @@
         <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
@@ -3715,122 +3715,122 @@
         <v>2.48</v>
       </c>
       <c r="V17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
         <v>980</v>
       </c>
       <c r="Z17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
         <v>980</v>
       </c>
       <c r="AC17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
         <v>980</v>
       </c>
       <c r="AE17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>980</v>
       </c>
       <c r="AK17" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
         <v>980</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.4</v>
+        <v>1.39</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.2</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>1.39</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.8</v>
+        <v>1.39</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>1.28</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.9</v>
+        <v>1.39</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>1.39</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.5</v>
+        <v>1.39</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.9</v>
+        <v>1.39</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.7</v>
+        <v>1.39</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>1.39</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>1.32</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.8</v>
+        <v>1.31</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>1.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>1.37</v>
       </c>
       <c r="BF17" t="n">
         <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>1.39</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" t="n">
         <v>6.8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>7</v>
       </c>
       <c r="J18" t="n">
         <v>4.8</v>
@@ -3891,7 +3891,7 @@
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
         <v>1.71</v>
@@ -3900,10 +3900,10 @@
         <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
@@ -3912,10 +3912,10 @@
         <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
         <v>25</v>
@@ -3927,7 +3927,7 @@
         <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>10.5</v>
@@ -3948,10 +3948,10 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK18" t="n">
         <v>15</v>
@@ -3960,10 +3960,10 @@
         <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO18" t="n">
         <v>85</v>
@@ -3972,7 +3972,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
         <v>48</v>
@@ -3993,19 +3993,19 @@
         <v>50</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
         <v>65</v>
       </c>
       <c r="BB18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
@@ -4014,17 +4014,17 @@
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF18" t="n">
         <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>5.2</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H19" t="n">
         <v>1.64</v>
@@ -4088,7 +4088,7 @@
         <v>2.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R19" t="n">
         <v>1.77</v>
@@ -4106,7 +4106,7 @@
         <v>2.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
         <v>32</v>
@@ -4157,13 +4157,13 @@
         <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
         <v>5.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ19" t="n">
         <v>12.5</v>
@@ -4190,7 +4190,7 @@
         <v>42</v>
       </c>
       <c r="AY19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
         <v>15.5</v>
@@ -4199,7 +4199,7 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BC19" t="n">
         <v>46</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -4273,28 +4273,28 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O20" t="n">
         <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I21" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J21" t="n">
         <v>4.1</v>
@@ -4461,7 +4461,7 @@
         <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -4470,16 +4470,16 @@
         <v>6.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R21" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S21" t="n">
         <v>2.16</v>
@@ -4488,13 +4488,13 @@
         <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X21" t="n">
         <v>29</v>
@@ -4503,7 +4503,7 @@
         <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>32</v>
@@ -4533,10 +4533,10 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>28</v>
@@ -4548,16 +4548,16 @@
         <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4575,10 +4575,10 @@
         <v>18.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
         <v>13</v>
@@ -4590,7 +4590,7 @@
         <v>44</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
         <v>26</v>
@@ -4599,14 +4599,14 @@
         <v>40</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4637,106 +4637,106 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="G22" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H22" t="n">
         <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="M22" t="n">
         <v>1.16</v>
       </c>
       <c r="N22" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P22" t="n">
         <v>1.43</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
         <v>6.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
         <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
         <v>17</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="AF22" t="n">
         <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
       </c>
       <c r="AJ22" t="n">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AK22" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BC22" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BG22" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>1.55</v>
       </c>
       <c r="P23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q23" t="n">
         <v>2.6</v>
@@ -4876,7 +4876,7 @@
         <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V23" t="n">
         <v>1.32</v>
@@ -4921,10 +4921,10 @@
         <v>110</v>
       </c>
       <c r="AJ23" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL23" t="n">
         <v>60</v>
@@ -4960,7 +4960,7 @@
         <v>6.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX23" t="n">
         <v>10.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X24" t="n">
         <v>980</v>
@@ -5091,104 +5091,104 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR24" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
         <v>5.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>6.2</v>
       </c>
-      <c r="BD24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE24" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.57</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H25" t="n">
         <v>3.8</v>
@@ -5246,19 +5246,19 @@
         <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="R25" t="n">
         <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
         <v>2.18</v>
@@ -5500,7 +5500,7 @@
         <v>18.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
         <v>27</v>
@@ -5509,7 +5509,7 @@
         <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
@@ -5518,7 +5518,7 @@
         <v>17</v>
       </c>
       <c r="AO26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -5527,7 +5527,7 @@
         <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>2.98</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
         <v>2.78</v>
@@ -5625,7 +5625,7 @@
         <v>3.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
         <v>1.17</v>
@@ -5655,7 +5655,7 @@
         <v>1.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
         <v>1.46</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
         <v>1.12</v>
@@ -5834,7 +5834,7 @@
         <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.19</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H29" t="n">
         <v>2.8</v>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J29" t="n">
         <v>2.96</v>
@@ -6013,16 +6013,16 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P29" t="n">
         <v>1.84</v>
@@ -6031,31 +6031,31 @@
         <v>1.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="U29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
         <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6064,22 +6064,22 @@
         <v>970</v>
       </c>
       <c r="AC29" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6088,13 +6088,13 @@
         <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.34</v>
+        <v>32</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.34</v>
+        <v>4.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Qabala</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.34</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.41</v>
+        <v>8.6</v>
       </c>
       <c r="H2" t="n">
-        <v>10.5</v>
+        <v>1.49</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>1.56</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>2.78</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="Y2" t="n">
         <v>980</v>
       </c>
       <c r="Z2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL2" t="n">
         <v>130</v>
       </c>
-      <c r="AA2" t="n">
-        <v>590</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AM2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN2" t="n">
         <v>200</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AO2" t="n">
-        <v>410</v>
+        <v>980</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AV2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>2.44</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>1.89</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>2.44</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>FK Qabala</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>1.31</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>1.37</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>3.6</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>330</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL3" t="n">
         <v>55</v>
       </c>
-      <c r="AB3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN3" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>620</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.75</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bregenz</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="X4" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF4" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>980</v>
-      </c>
       <c r="AG4" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>980</v>
+        <v>6.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AU4" t="n">
         <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SK Sturm Graz II</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Liefering</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
         <v>4.3</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB5" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>11</v>
       </c>
-      <c r="AD5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG5" t="n">
         <v>14.5</v>
       </c>
-      <c r="BG5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bregenz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>1.82</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.2</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AM6" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.4</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>23</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>23</v>
+        <v>4.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
-        <v>36</v>
+        <v>4.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>80</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>SK Sturm Graz II</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>FC Liefering</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT7" t="n">
         <v>3.95</v>
       </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9</v>
-      </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>15.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>3.85</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dumbarton</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.72</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS8" t="n">
         <v>19</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AT8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8" t="n">
         <v>15</v>
       </c>
-      <c r="Z8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AX8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="BA8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD8" t="n">
         <v>38</v>
       </c>
-      <c r="AF8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="BE8" t="n">
         <v>48</v>
       </c>
-      <c r="AM8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="BF8" t="n">
         <v>28</v>
       </c>
-      <c r="AO8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Annan</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.36</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.64</v>
-      </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>3.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>2.44</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="W10" t="n">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
         <v>13</v>
       </c>
-      <c r="Y10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="BC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>9</v>
       </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8</v>
-      </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>11</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H12" t="n">
         <v>3.15</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I12" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.32</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF13" t="n">
         <v>18</v>
       </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>95</v>
+        <v>980</v>
       </c>
       <c r="AB14" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>980</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO14" t="n">
         <v>15</v>
       </c>
-      <c r="AG14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>980</v>
-      </c>
       <c r="AP14" t="n">
-        <v>3.35</v>
+        <v>15.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>12.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.6</v>
+        <v>19</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.65</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.45</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="X15" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AW15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>17</v>
       </c>
-      <c r="AI15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.38</v>
+        <v>2.44</v>
       </c>
       <c r="G16" t="n">
-        <v>1.42</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.3</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X16" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD16" t="n">
-        <v>2.24</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.79</v>
+        <v>55</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.25</v>
+        <v>17</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.83</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX17" t="n">
         <v>5</v>
       </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="AY17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA17" t="n">
         <v>5.4</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BB17" t="n">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.31</v>
+        <v>5.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.33</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.39</v>
+        <v>4.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="G18" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>2.76</v>
+        <v>1.92</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Z18" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AA18" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.8</v>
+        <v>980</v>
       </c>
       <c r="AO18" t="n">
-        <v>85</v>
+        <v>980</v>
       </c>
       <c r="AP18" t="n">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>3.65</v>
       </c>
       <c r="AR18" t="n">
-        <v>48</v>
+        <v>3.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>3.95</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>3.55</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BE18" t="n">
-        <v>80</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>70</v>
+        <v>3.95</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.2</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>1.42</v>
       </c>
       <c r="H19" t="n">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.65</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
         <v>6.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="R19" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="S19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X19" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AY19" t="n">
         <v>2.22</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X19" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>2.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>21</v>
+        <v>1.82</v>
       </c>
       <c r="BB19" t="n">
-        <v>95</v>
+        <v>2.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>46</v>
+        <v>2.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>40</v>
+        <v>2.14</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>1.95</v>
       </c>
       <c r="BF19" t="n">
-        <v>34</v>
+        <v>3.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>1.82</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>1.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1.52</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="H21" t="n">
-        <v>2.36</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.16</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.49</v>
+        <v>2.88</v>
       </c>
       <c r="X21" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="n">
-        <v>32</v>
+        <v>190</v>
       </c>
       <c r="AB21" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>27</v>
+        <v>9.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AI21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>48</v>
-      </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AL21" t="n">
         <v>28</v>
       </c>
       <c r="AM21" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AO21" t="n">
-        <v>9.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="AP21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>27</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>26</v>
-      </c>
       <c r="BE21" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.74</v>
+        <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>1.64</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>1.65</v>
       </c>
       <c r="J22" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O22" t="n">
         <v>1.16</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.67</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>2.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="Z22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
         <v>21</v>
       </c>
-      <c r="AA22" t="n">
-        <v>990</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>470</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>40</v>
-      </c>
       <c r="BB22" t="n">
+        <v>95</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD22" t="n">
         <v>42</v>
       </c>
-      <c r="BC22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>38</v>
-      </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BF22" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BG22" t="n">
-        <v>55</v>
+        <v>5.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,120 +4817,120 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="H23" t="n">
-        <v>3.75</v>
+        <v>2.52</v>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="S23" t="n">
-        <v>5.6</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>1.46</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>2.34</v>
       </c>
       <c r="I24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X24" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN24" t="n">
         <v>15</v>
       </c>
-      <c r="J24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.5</v>
+        <v>29</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.35</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.3</v>
+        <v>44</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,120 +5205,120 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.57</v>
+        <v>2.74</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.32</v>
+        <v>3.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>1.32</v>
+        <v>6.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>730</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN25" t="n">
         <v>1000</v>
@@ -5327,69 +5327,69 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G26" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH26" t="n">
         <v>34</v>
       </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ26" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>5.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AU26" t="n">
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="BA26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB26" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB26" t="n">
-        <v>21</v>
-      </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.7</v>
+        <v>70</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="G27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W27" t="n">
         <v>3.2</v>
       </c>
-      <c r="H27" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="X27" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR27" t="n">
         <v>6.8</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X27" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AS27" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AW27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>6</v>
-      </c>
       <c r="BA27" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>7</v>
+        <v>2.62</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,960 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV28" t="n">
         <v>4.1</v>
       </c>
-      <c r="G28" t="n">
+      <c r="AW28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.6</v>
       </c>
-      <c r="H28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S28" t="n">
-        <v>5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>3.45</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Newells</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Atletico Nacional Medell</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G32" t="n">
         <v>3.05</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H32" t="n">
         <v>2.8</v>
       </c>
-      <c r="I29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J32" t="n">
         <v>2.96</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
         <v>4.1</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="AQ32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU32" t="n">
         <v>3.45</v>
       </c>
-      <c r="O29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X29" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
+      <c r="AV32" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AW32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB32" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW29" t="n">
+      <c r="BC32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF32" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG29" t="n">
+      <c r="BG32" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-09 09:03:27</t>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.49</v>
@@ -769,7 +769,7 @@
         <v>1.56</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.9</v>
@@ -796,7 +796,7 @@
         <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
@@ -811,37 +811,37 @@
         <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>980</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AB2" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
         <v>980</v>
@@ -856,71 +856,71 @@
         <v>130</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
         <v>200</v>
       </c>
       <c r="AO2" t="n">
-        <v>980</v>
+        <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.89</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
         <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,146 +975,146 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD3" t="n">
         <v>980</v>
       </c>
-      <c r="Z3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>60</v>
-      </c>
       <c r="AE3" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.3</v>
+        <v>1.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>1.82</v>
       </c>
       <c r="AS3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
       <c r="AU3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.6</v>
+        <v>1.78</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>1.82</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>1.56</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>1.76</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>1.82</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>1.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>1.82</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>1.82</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
         <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>3.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE4" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF4" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
         <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1363,22 +1363,22 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
@@ -1390,7 +1390,7 @@
         <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1408,7 +1408,7 @@
         <v>16.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
         <v>15.5</v>
@@ -1456,7 +1456,7 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
         <v>11.5</v>
@@ -1468,31 +1468,31 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>19.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
         <v>1.19</v>
@@ -1596,31 +1596,31 @@
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
         <v>980</v>
       </c>
       <c r="AE6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF6" t="n">
         <v>980</v>
       </c>
       <c r="AG6" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>980</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="n">
         <v>980</v>
@@ -1632,71 +1632,71 @@
         <v>980</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AY6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -1763,22 +1763,22 @@
         <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
         <v>15.5</v>
@@ -1841,56 +1841,56 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1927,19 +1927,19 @@
         <v>4.6</v>
       </c>
       <c r="H8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.83</v>
       </c>
-      <c r="I8" t="n">
-        <v>1.84</v>
-      </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
@@ -1951,7 +1951,7 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
         <v>1.54</v>
@@ -1963,13 +1963,13 @@
         <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.27</v>
@@ -1984,16 +1984,16 @@
         <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>10.5</v>
       </c>
       <c r="AE8" t="n">
         <v>16</v>
@@ -2005,7 +2005,7 @@
         <v>17.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>24</v>
@@ -2014,7 +2014,7 @@
         <v>85</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
@@ -2029,7 +2029,7 @@
         <v>7.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>13</v>
@@ -2038,16 +2038,16 @@
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
         <v>15</v>
@@ -2080,11 +2080,11 @@
         <v>28</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2139,13 +2139,13 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
         <v>1.81</v>
@@ -2154,7 +2154,7 @@
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
         <v>1.86</v>
@@ -2163,19 +2163,19 @@
         <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
         <v>2.36</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
         <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>210</v>
@@ -2187,7 +2187,7 @@
         <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE9" t="n">
         <v>110</v>
@@ -2211,7 +2211,7 @@
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
         <v>150</v>
@@ -2223,62 +2223,62 @@
         <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2330,13 +2330,13 @@
         <v>1.51</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
         <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
         <v>1.47</v>
@@ -2351,10 +2351,10 @@
         <v>5.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
         <v>1.7</v>
@@ -2468,11 +2468,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -2542,7 +2542,7 @@
         <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
         <v>1.69</v>
@@ -2638,7 +2638,7 @@
         <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
         <v>12</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.58</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
@@ -2909,19 +2909,19 @@
         <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
         <v>1.85</v>
@@ -2930,16 +2930,16 @@
         <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -3011,13 +3011,13 @@
         <v>3.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -3026,10 +3026,10 @@
         <v>16.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>3.95</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="n">
         <v>2.1</v>
@@ -3121,7 +3121,7 @@
         <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
         <v>2.84</v>
@@ -3136,119 +3136,119 @@
         <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
         <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
         <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT14" t="n">
         <v>13</v>
       </c>
-      <c r="AS14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
         <v>11</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="n">
         <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -3309,109 +3309,109 @@
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
         <v>1.96</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>110</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP15" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
@@ -3420,29 +3420,29 @@
         <v>18.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>2.72</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.32</v>
@@ -3497,13 +3497,13 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
         <v>1.81</v>
@@ -3518,10 +3518,10 @@
         <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
         <v>1.58</v>
@@ -3563,7 +3563,7 @@
         <v>46</v>
       </c>
       <c r="AJ16" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="n">
         <v>29</v>
@@ -3587,10 +3587,10 @@
         <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3602,7 +3602,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
         <v>15.5</v>
@@ -3614,16 +3614,16 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
         <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
         <v>55</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3673,46 +3673,46 @@
         <v>2.92</v>
       </c>
       <c r="H17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
         <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
         <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V17" t="n">
         <v>1.5</v>
@@ -3736,7 +3736,7 @@
         <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -3745,13 +3745,13 @@
         <v>980</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AG17" t="n">
         <v>980</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>980</v>
@@ -3781,10 +3781,10 @@
         <v>4.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT17" t="n">
         <v>4.5</v>
@@ -3799,7 +3799,7 @@
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY17" t="n">
         <v>4.4</v>
@@ -3811,26 +3811,26 @@
         <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD17" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
         <v>4.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.75</v>
       </c>
-      <c r="I18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
@@ -3885,34 +3885,34 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X18" t="n">
         <v>980</v>
@@ -3927,10 +3927,10 @@
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AC18" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
         <v>980</v>
@@ -3939,10 +3939,10 @@
         <v>980</v>
       </c>
       <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
         <v>980</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>980</v>
@@ -3960,7 +3960,7 @@
         <v>980</v>
       </c>
       <c r="AM18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
         <v>980</v>
@@ -3969,19 +3969,19 @@
         <v>980</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AR18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT18" t="n">
         <v>3.9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.8</v>
       </c>
       <c r="AU18" t="n">
         <v>3.75</v>
@@ -3990,41 +3990,41 @@
         <v>4.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA18" t="n">
         <v>5</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
         <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
         <v>1.42</v>
@@ -4064,10 +4064,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K19" t="n">
         <v>5.3</v>
@@ -4094,13 +4094,13 @@
         <v>1.89</v>
       </c>
       <c r="S19" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.1</v>
@@ -4157,68 +4157,68 @@
         <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO19" t="n">
         <v>95</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="AU19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>2.36</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.95</v>
       </c>
       <c r="BF19" t="n">
         <v>3.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.78</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -4285,7 +4285,7 @@
         <v>1.51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
         <v>2.28</v>
@@ -4297,13 +4297,13 @@
         <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
         <v>2.02</v>
       </c>
       <c r="X20" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
         <v>980</v>
@@ -4318,22 +4318,22 @@
         <v>980</v>
       </c>
       <c r="AC20" t="n">
-        <v>980</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>980</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>980</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
         <v>980</v>
@@ -4342,77 +4342,77 @@
         <v>980</v>
       </c>
       <c r="AK20" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
         <v>980</v>
       </c>
       <c r="AM20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
-        <v>980</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>980</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AT20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW20" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AX20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB20" t="n">
         <v>5</v>
       </c>
-      <c r="AV20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BF20" t="n">
         <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -4443,28 +4443,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I21" t="n">
         <v>7</v>
       </c>
-      <c r="I21" t="n">
-        <v>7.2</v>
-      </c>
       <c r="J21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K21" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>5.2</v>
@@ -4476,16 +4476,16 @@
         <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R21" t="n">
         <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
         <v>2.18</v>
@@ -4494,10 +4494,10 @@
         <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
         <v>27</v>
@@ -4512,19 +4512,19 @@
         <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF21" t="n">
         <v>9.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
         <v>21</v>
@@ -4539,13 +4539,13 @@
         <v>14.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM21" t="n">
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO21" t="n">
         <v>85</v>
@@ -4554,13 +4554,13 @@
         <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
         <v>50</v>
       </c>
       <c r="AS21" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
         <v>9.6</v>
@@ -4569,25 +4569,25 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
         <v>70</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA21" t="n">
         <v>65</v>
       </c>
       <c r="BB21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>13.5</v>
@@ -4596,17 +4596,17 @@
         <v>27</v>
       </c>
       <c r="BE21" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BF21" t="n">
         <v>6</v>
       </c>
       <c r="BG21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>5.2</v>
       </c>
       <c r="G22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J22" t="n">
         <v>4.9</v>
@@ -4667,13 +4667,13 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
         <v>2.26</v>
@@ -4688,7 +4688,7 @@
         <v>2.52</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
         <v>32</v>
@@ -4703,28 +4703,28 @@
         <v>18</v>
       </c>
       <c r="AB22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC22" t="n">
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE22" t="n">
         <v>14.5</v>
       </c>
       <c r="AF22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG22" t="n">
         <v>20</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ22" t="n">
         <v>120</v>
@@ -4736,7 +4736,7 @@
         <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN22" t="n">
         <v>38</v>
@@ -4757,7 +4757,7 @@
         <v>17</v>
       </c>
       <c r="AT22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU22" t="n">
         <v>10.5</v>
@@ -4766,13 +4766,13 @@
         <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY22" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
@@ -4787,7 +4787,7 @@
         <v>46</v>
       </c>
       <c r="BD22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE22" t="n">
         <v>55</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="G23" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H23" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="K23" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="P23" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="Q23" t="n">
         <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -5055,13 +5055,13 @@
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q24" t="n">
         <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S24" t="n">
         <v>2.2</v>
@@ -5070,7 +5070,7 @@
         <v>1.47</v>
       </c>
       <c r="U24" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V24" t="n">
         <v>1.73</v>
@@ -5136,10 +5136,10 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS24" t="n">
         <v>29</v>
@@ -5172,7 +5172,7 @@
         <v>44</v>
       </c>
       <c r="BC24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD24" t="n">
         <v>26</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>2.74</v>
       </c>
       <c r="G25" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H25" t="n">
         <v>3.15</v>
@@ -5231,25 +5231,25 @@
         <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K25" t="n">
         <v>3.05</v>
       </c>
       <c r="L25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O25" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="P25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q25" t="n">
         <v>3.05</v>
@@ -5258,19 +5258,19 @@
         <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
         <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X25" t="n">
         <v>7.2</v>
@@ -5279,13 +5279,13 @@
         <v>8.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>730</v>
+        <v>65</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC25" t="n">
         <v>7</v>
@@ -5294,7 +5294,7 @@
         <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
@@ -5309,10 +5309,10 @@
         <v>120</v>
       </c>
       <c r="AJ25" t="n">
-        <v>980</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5327,25 +5327,25 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>46</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
         <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
         <v>48</v>
@@ -5354,35 +5354,35 @@
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
         <v>38</v>
       </c>
       <c r="BB25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG25" t="n">
         <v>34</v>
       </c>
-      <c r="BD25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>55</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -5419,46 +5419,46 @@
         <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K26" t="n">
         <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
         <v>1.12</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" t="n">
         <v>2.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V26" t="n">
         <v>1.32</v>
@@ -5479,7 +5479,7 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC26" t="n">
         <v>8.199999999999999</v>
@@ -5497,7 +5497,7 @@
         <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
         <v>110</v>
@@ -5506,7 +5506,7 @@
         <v>980</v>
       </c>
       <c r="AK26" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
         <v>80</v>
@@ -5527,7 +5527,7 @@
         <v>7.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS26" t="n">
         <v>65</v>
@@ -5539,10 +5539,10 @@
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5551,32 +5551,32 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC26" t="n">
         <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
         <v>70</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>1.36</v>
       </c>
       <c r="G27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
@@ -5646,19 +5646,19 @@
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X27" t="n">
         <v>980</v>
@@ -5673,10 +5673,10 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AD27" t="n">
         <v>980</v>
@@ -5685,7 +5685,7 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>980</v>
+        <v>7.4</v>
       </c>
       <c r="AG27" t="n">
         <v>980</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AU27" t="n">
         <v>4.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AX27" t="n">
         <v>5.8</v>
       </c>
       <c r="AY27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD27" t="n">
         <v>4.4</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE27" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="BF27" t="n">
         <v>6.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>1.57</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H28" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
@@ -5825,16 +5825,16 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
@@ -5843,16 +5843,16 @@
         <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W28" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X28" t="n">
         <v>15</v>
@@ -5879,7 +5879,7 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
@@ -5891,10 +5891,10 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
         <v>60</v>
@@ -5903,68 +5903,68 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AY28" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC28" t="n">
         <v>3.7</v>
       </c>
-      <c r="BC28" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE28" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R29" t="n">
         <v>1.37</v>
@@ -6052,7 +6052,7 @@
         <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
@@ -6103,7 +6103,7 @@
         <v>48</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>12.5</v>
@@ -6118,7 +6118,7 @@
         <v>9</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
         <v>14</v>
@@ -6136,7 +6136,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -6145,10 +6145,10 @@
         <v>18.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.84</v>
       </c>
       <c r="G30" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>3.05</v>
@@ -6213,10 +6213,10 @@
         <v>1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="P30" t="n">
         <v>1.4</v>
@@ -6243,7 +6243,7 @@
         <v>1.5</v>
       </c>
       <c r="X30" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
         <v>8</v>
@@ -6255,7 +6255,7 @@
         <v>400</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC30" t="n">
         <v>7.4</v>
@@ -6264,16 +6264,16 @@
         <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>20</v>
       </c>
       <c r="AH30" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
         <v>110</v>
@@ -6321,7 +6321,7 @@
         <v>29</v>
       </c>
       <c r="AX30" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY30" t="n">
         <v>13.5</v>
@@ -6345,14 +6345,14 @@
         <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BG30" t="n">
         <v>34</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="G31" t="n">
         <v>4.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I31" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
         <v>3.35</v>
@@ -6407,31 +6407,31 @@
         <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q31" t="n">
         <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
         <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V31" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="W31" t="n">
         <v>1.29</v>
@@ -6446,7 +6446,7 @@
         <v>13</v>
       </c>
       <c r="AA31" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB31" t="n">
         <v>12</v>
@@ -6461,7 +6461,7 @@
         <v>32</v>
       </c>
       <c r="AF31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>19</v>
@@ -6500,7 +6500,7 @@
         <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
         <v>9.6</v>
@@ -6512,10 +6512,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY31" t="n">
         <v>16</v>
@@ -6524,29 +6524,29 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC31" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB31" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF31" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG31" t="n">
         <v>7.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>2.8</v>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J32" t="n">
         <v>2.96</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -6610,13 +6610,13 @@
         <v>1.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R32" t="n">
         <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
         <v>1.79</v>
@@ -6628,7 +6628,7 @@
         <v>1.44</v>
       </c>
       <c r="W32" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X32" t="n">
         <v>970</v>
@@ -6661,7 +6661,7 @@
         <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6706,7 +6706,7 @@
         <v>4.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX32" t="n">
         <v>4.4</v>
@@ -6727,7 +6727,7 @@
         <v>4.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
         <v>5.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Iskenderunspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bucaspor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>8.4</v>
+        <v>1.76</v>
       </c>
       <c r="H2" t="n">
-        <v>1.49</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.56</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Qabala</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>7.4</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>24</v>
+        <v>1.61</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,153 +975,153 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>2.64</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.4</v>
+        <v>70</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.82</v>
+        <v>12.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.56</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.82</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.75</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.82</v>
+        <v>5.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>FK Qabala</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.56</v>
-      </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AA4" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="AF4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG4" t="n">
         <v>11</v>
       </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="AN4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.86</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>1.58</v>
       </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.98</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK5" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AL5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>19</v>
       </c>
-      <c r="AI5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>26</v>
-      </c>
       <c r="BC5" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bregenz</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.82</v>
+        <v>2.76</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="X6" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA6" t="n">
         <v>55</v>
       </c>
-      <c r="AA6" t="n">
-        <v>180</v>
-      </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG6" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SK Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Liefering</t>
+          <t>Bregenz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>11</v>
       </c>
       <c r="AD7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
         <v>14</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AO7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="AW7" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>18</v>
-      </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SK Sturm Graz II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FC Liefering</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="J8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.3</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.54</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.72</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
         <v>14</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>75</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>28</v>
-      </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.59</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>1.81</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>1.82</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>2.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AB9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AP9" t="n">
         <v>26</v>
       </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>19.5</v>
       </c>
-      <c r="AK9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AT9" t="n">
-        <v>3.1</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.2</v>
+        <v>36</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.2</v>
+        <v>16.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.6</v>
+        <v>75</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.65</v>
+        <v>40</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.3</v>
+        <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.2</v>
+        <v>28</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Masry</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>3.9</v>
       </c>
-      <c r="G10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="BA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF10" t="n">
         <v>3.25</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dumbarton</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stranraer</t>
+          <t>Al-Masry</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.29</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="AZ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG11" t="n">
         <v>30</v>
       </c>
-      <c r="AP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Annan</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elgin City FC</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
-        <v>2.98</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.85</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AB14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK14" t="n">
         <v>38</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>40</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
         <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="AT14" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -3315,16 +3315,16 @@
         <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
         <v>3.85</v>
       </c>
       <c r="T15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
@@ -3423,10 +3423,10 @@
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Eastleigh</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL16" t="n">
         <v>50</v>
       </c>
-      <c r="AB16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>7</v>
       </c>
       <c r="AV16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11</v>
       </c>
-      <c r="AW16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>20</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="H17" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.05</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.47</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
-        <v>980</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.4</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H18" t="n">
         <v>3.6</v>
@@ -3876,7 +3876,7 @@
         <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
@@ -3894,7 +3894,7 @@
         <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.48</v>
@@ -3912,7 +3912,7 @@
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X18" t="n">
         <v>980</v>
@@ -3939,7 +3939,7 @@
         <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AG18" t="n">
         <v>980</v>
@@ -3969,62 +3969,62 @@
         <v>980</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AV18" t="n">
         <v>4.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
         <v>4.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
         <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>1.39</v>
       </c>
       <c r="R19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S19" t="n">
         <v>1.84</v>
@@ -4163,7 +4163,7 @@
         <v>95</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AQ19" t="n">
         <v>6.2</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H20" t="n">
         <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -4282,7 +4282,7 @@
         <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
         <v>1.56</v>
@@ -4297,10 +4297,10 @@
         <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="X20" t="n">
         <v>32</v>
@@ -4315,10 +4315,10 @@
         <v>90</v>
       </c>
       <c r="AB20" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
         <v>21</v>
@@ -4327,10 +4327,10 @@
         <v>980</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>18.5</v>
@@ -4351,34 +4351,34 @@
         <v>70</v>
       </c>
       <c r="AN20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU20" t="n">
         <v>9</v>
       </c>
-      <c r="AO20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AV20" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4390,36 +4390,36 @@
         <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
         <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8</v>
+        <v>1.54</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="Y21" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AA21" t="n">
-        <v>190</v>
+        <v>980</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>980</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.6</v>
+        <v>980</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AL21" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>85</v>
+        <v>980</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>50</v>
+        <v>3.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>24</v>
+        <v>3.55</v>
       </c>
       <c r="AW21" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>65</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>27</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>80</v>
+        <v>4.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>75</v>
+        <v>3.9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -4661,19 +4661,19 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O22" t="n">
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
         <v>2.26</v>
@@ -4709,7 +4709,7 @@
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>14.5</v>
@@ -4718,7 +4718,7 @@
         <v>48</v>
       </c>
       <c r="AG22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
         <v>17.5</v>
@@ -4766,7 +4766,7 @@
         <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX22" t="n">
         <v>42</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H23" t="n">
         <v>2.82</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,7 +4855,7 @@
         <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
         <v>1.49</v>
@@ -4864,13 +4864,13 @@
         <v>1.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
         <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -4879,10 +4879,10 @@
         <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
@@ -4900,7 +4900,7 @@
         <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
         <v>16.5</v>
@@ -4939,49 +4939,49 @@
         <v>60</v>
       </c>
       <c r="AP23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>3.1</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AR23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU23" t="n">
         <v>2.86</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4</v>
       </c>
-      <c r="BB23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE23" t="n">
         <v>4.2</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J24" t="n">
         <v>4.1</v>
@@ -5049,22 +5049,22 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P24" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T24" t="n">
         <v>1.47</v>
@@ -5073,7 +5073,7 @@
         <v>3.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
@@ -5082,7 +5082,7 @@
         <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z24" t="n">
         <v>20</v>
@@ -5097,7 +5097,7 @@
         <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
         <v>19.5</v>
@@ -5118,7 +5118,7 @@
         <v>48</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
         <v>18.5</v>
@@ -5148,16 +5148,16 @@
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
         <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.74</v>
       </c>
-      <c r="G25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6.8</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>1.52</v>
+        <v>2.68</v>
       </c>
       <c r="X25" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="Z25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH25" t="n">
         <v>20</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AI25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS25" t="n">
         <v>65</v>
       </c>
-      <c r="AB25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>390</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AT25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF25" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>29</v>
-      </c>
       <c r="BG25" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26</v>
+        <v>2.96</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="K26" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="P26" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AQ26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV26" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AW26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC26" t="n">
         <v>36</v>
       </c>
-      <c r="AI26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="BD26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG26" t="n">
         <v>34</v>
       </c>
-      <c r="AL26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>70</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,81 +5593,81 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>1.46</v>
+        <v>2.26</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="X27" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>140</v>
+        <v>980</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -5676,108 +5676,108 @@
         <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>980</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AH27" t="n">
         <v>980</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="n">
         <v>980</v>
       </c>
       <c r="AK27" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF27" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG27" t="n">
-        <v>2.7</v>
+        <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="G28" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="U28" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W28" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="Y28" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AD28" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AH28" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="H29" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X29" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>4</v>
       </c>
-      <c r="J29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X29" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>7</v>
-      </c>
       <c r="BE29" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BF29" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="H30" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="I30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.25</v>
       </c>
-      <c r="J30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S30" t="n">
-        <v>7.4</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="X30" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>18.5</v>
       </c>
       <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
         <v>110</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>260</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>350</v>
-      </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV30" t="n">
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF30" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -6374,373 +6374,567 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="G31" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="H31" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="I31" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="K31" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N31" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="O31" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="P31" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S31" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="U31" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="V31" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="X31" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>250</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY31" t="n">
         <v>13</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AZ31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG31" t="n">
         <v>34</v>
       </c>
-      <c r="AB31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-09 15:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Atletico Nacional Medell</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G33" t="n">
         <v>3.05</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>2.8</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>3.25</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>2.96</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>3.6</v>
       </c>
-      <c r="L32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="L33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M33" t="n">
         <v>1.08</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>3.45</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>1.35</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>1.92</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>1.32</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>3.35</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>1.79</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>2.1</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>1.44</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X32" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC32" t="n">
+      <c r="W33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X33" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM32" t="n">
+      <c r="AD33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM33" t="n">
         <v>120</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ33" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR33" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS33" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT33" t="n">
         <v>3.9</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU33" t="n">
         <v>3.45</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV33" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW33" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX33" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY33" t="n">
         <v>4</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ33" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA33" t="n">
         <v>32</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB33" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BE33" t="n">
         <v>5.4</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BF33" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BG33" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-09 13:23:49</t>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -760,55 +760,55 @@
         <v>1.4</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W2" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H3" t="n">
         <v>1.53</v>
@@ -969,34 +969,34 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
         <v>2.64</v>
@@ -1005,40 +1005,40 @@
         <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
         <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB3" t="n">
         <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG3" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AJ3" t="n">
         <v>260</v>
@@ -1053,16 +1053,16 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
@@ -1071,50 +1071,50 @@
         <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>21</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>13.5</v>
@@ -1223,10 +1223,10 @@
         <v>340</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>980</v>
@@ -1235,7 +1235,7 @@
         <v>270</v>
       </c>
       <c r="AJ4" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1244,10 +1244,10 @@
         <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1256,25 +1256,25 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR4" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
         <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,10 +1283,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
@@ -1295,20 +1295,20 @@
         <v>13.5</v>
       </c>
       <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1369,121 +1369,121 @@
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.66</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.72</v>
-      </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
         <v>980</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB5" t="n">
         <v>9.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
         <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
         <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AM5" t="n">
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1492,17 +1492,17 @@
         <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1572,7 +1572,7 @@
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.69</v>
@@ -1584,7 +1584,7 @@
         <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1593,13 +1593,13 @@
         <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
@@ -1623,7 +1623,7 @@
         <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
         <v>32</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>25</v>
@@ -1644,13 +1644,13 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
@@ -1662,10 +1662,10 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
@@ -1677,26 +1677,26 @@
         <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>3.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
         <v>980</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AA7" t="n">
         <v>180</v>
@@ -1805,7 +1805,7 @@
         <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
         <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV7" t="n">
         <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF7" t="n">
         <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.75</v>
@@ -1969,13 +1969,13 @@
         <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
         <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
         <v>16.5</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG8" t="n">
         <v>15.5</v>
@@ -2029,16 +2029,16 @@
         <v>16.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>18</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,16 +2062,16 @@
         <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
         <v>4.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
@@ -2148,16 +2148,16 @@
         <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
         <v>2.68</v>
@@ -2172,7 +2172,7 @@
         <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
@@ -2223,7 +2223,7 @@
         <v>7.2</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2241,7 +2241,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
@@ -2274,11 +2274,11 @@
         <v>28</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2315,37 +2315,37 @@
         <v>1.73</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
         <v>3.05</v>
@@ -2357,7 +2357,7 @@
         <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
         <v>2.36</v>
@@ -2408,71 +2408,71 @@
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>130</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.85</v>
+        <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.95</v>
+        <v>19.5</v>
       </c>
       <c r="AW10" t="n">
         <v>4.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.9</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.7</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -2527,7 +2527,7 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.58</v>
@@ -2551,10 +2551,10 @@
         <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
         <v>8.199999999999999</v>
@@ -2581,13 +2581,13 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
         <v>19.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
         <v>18.5</v>
@@ -2650,7 +2650,7 @@
         <v>8.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD11" t="n">
         <v>8.6</v>
@@ -2662,11 +2662,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2736,7 +2736,7 @@
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.69</v>
@@ -2805,10 +2805,10 @@
         <v>30</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2817,25 +2817,25 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
         <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>3.95</v>
@@ -2844,10 +2844,10 @@
         <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
         <v>4.1</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U14" t="n">
         <v>2.22</v>
@@ -3220,7 +3220,7 @@
         <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
@@ -3303,28 +3303,28 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
         <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
@@ -3384,7 +3384,7 @@
         <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
         <v>10.5</v>
@@ -3402,31 +3402,31 @@
         <v>5.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3476,22 +3476,22 @@
         <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3506,25 +3506,25 @@
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
         <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -3536,13 +3536,13 @@
         <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AB16" t="n">
         <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>13</v>
@@ -3554,19 +3554,19 @@
         <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AJ16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AL16" t="n">
         <v>50</v>
@@ -3587,22 +3587,22 @@
         <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>9.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX16" t="n">
         <v>19.5</v>
@@ -3614,29 +3614,29 @@
         <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3697,16 +3697,16 @@
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
         <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3718,7 +3718,7 @@
         <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X17" t="n">
         <v>18.5</v>
@@ -3727,22 +3727,22 @@
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
@@ -3751,10 +3751,10 @@
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ17" t="n">
         <v>38</v>
@@ -3766,7 +3766,7 @@
         <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
         <v>20</v>
@@ -3778,13 +3778,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>38</v>
+        <v>6.6</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
@@ -3793,44 +3793,44 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
         <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BG17" t="n">
         <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H18" t="n">
         <v>3.6</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>3.75</v>
@@ -3885,34 +3885,34 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
         <v>980</v>
@@ -3939,10 +3939,10 @@
         <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>980</v>
@@ -3969,62 +3969,62 @@
         <v>980</v>
       </c>
       <c r="AP18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BB18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
         <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.19</v>
@@ -4079,7 +4079,7 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
@@ -4088,25 +4088,25 @@
         <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S19" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
@@ -4115,7 +4115,7 @@
         <v>980</v>
       </c>
       <c r="Z19" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -4130,7 +4130,7 @@
         <v>980</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="n">
         <v>980</v>
@@ -4142,7 +4142,7 @@
         <v>980</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
         <v>980</v>
@@ -4157,68 +4157,68 @@
         <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE19" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -4282,13 +4282,13 @@
         <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="T20" t="n">
         <v>1.54</v>
@@ -4297,7 +4297,7 @@
         <v>2.48</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
         <v>1.99</v>
@@ -4312,7 +4312,7 @@
         <v>980</v>
       </c>
       <c r="AA20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="n">
         <v>16</v>
@@ -4327,10 +4327,10 @@
         <v>980</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>18.5</v>
@@ -4357,62 +4357,62 @@
         <v>980</v>
       </c>
       <c r="AP20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR20" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>5</v>
-      </c>
       <c r="AS20" t="n">
-        <v>55</v>
+        <v>5.2</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>19.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
         <v>6.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4446,55 +4446,55 @@
         <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="H21" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="I21" t="n">
         <v>3.05</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="T21" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X21" t="n">
         <v>980</v>
@@ -4503,7 +4503,7 @@
         <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
         <v>980</v>
@@ -4512,7 +4512,7 @@
         <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>15.5</v>
@@ -4527,7 +4527,7 @@
         <v>980</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>980</v>
@@ -4545,68 +4545,68 @@
         <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO21" t="n">
         <v>980</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF21" t="n">
         <v>4.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I22" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="J22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>1.26</v>
@@ -4673,7 +4673,7 @@
         <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
         <v>2.26</v>
@@ -4682,13 +4682,13 @@
         <v>1.58</v>
       </c>
       <c r="U22" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V22" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>32</v>
@@ -4697,10 +4697,10 @@
         <v>13.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB22" t="n">
         <v>28</v>
@@ -4718,10 +4718,10 @@
         <v>48</v>
       </c>
       <c r="AG22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>23</v>
@@ -4730,10 +4730,10 @@
         <v>120</v>
       </c>
       <c r="AK22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
         <v>65</v>
@@ -4757,10 +4757,10 @@
         <v>17</v>
       </c>
       <c r="AT22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV22" t="n">
         <v>9.6</v>
@@ -4772,7 +4772,7 @@
         <v>42</v>
       </c>
       <c r="AY22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G23" t="n">
         <v>3.1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4855,7 +4855,7 @@
         <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="O23" t="n">
         <v>1.49</v>
@@ -4864,13 +4864,13 @@
         <v>1.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="R23" t="n">
         <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -4879,13 +4879,13 @@
         <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
@@ -4906,7 +4906,7 @@
         <v>16.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF23" t="n">
         <v>22</v>
@@ -4915,86 +4915,86 @@
         <v>16.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
         <v>60</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW23" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4</v>
-      </c>
       <c r="AX23" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF23" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF23" t="n">
-        <v>4</v>
-      </c>
       <c r="BG23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
         <v>3.05</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
         <v>4.1</v>
@@ -5058,13 +5058,13 @@
         <v>2.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
         <v>1.47</v>
@@ -5073,13 +5073,13 @@
         <v>3.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y24" t="n">
         <v>18.5</v>
@@ -5091,7 +5091,7 @@
         <v>32</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
@@ -5133,19 +5133,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ24" t="n">
         <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
         <v>29</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -5163,16 +5163,16 @@
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
         <v>44</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>26</v>
@@ -5181,14 +5181,14 @@
         <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -5219,31 +5219,31 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.58</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.59</v>
-      </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
         <v>1.23</v>
@@ -5255,22 +5255,22 @@
         <v>1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T25" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X25" t="n">
         <v>22</v>
@@ -5282,22 +5282,22 @@
         <v>55</v>
       </c>
       <c r="AA25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE25" t="n">
         <v>80</v>
       </c>
       <c r="AF25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
         <v>9.800000000000001</v>
@@ -5318,10 +5318,10 @@
         <v>29</v>
       </c>
       <c r="AM25" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO25" t="n">
         <v>85</v>
@@ -5339,7 +5339,7 @@
         <v>65</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
@@ -5348,25 +5348,25 @@
         <v>22</v>
       </c>
       <c r="AW25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
         <v>9.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
         <v>27</v>
@@ -5375,14 +5375,14 @@
         <v>80</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
         <v>70</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.76</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H26" t="n">
         <v>3.1</v>
@@ -5476,7 +5476,7 @@
         <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>65</v>
+        <v>820</v>
       </c>
       <c r="AB26" t="n">
         <v>7.4</v>
@@ -5488,22 +5488,22 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>370</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG26" t="n">
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AI26" t="n">
         <v>120</v>
       </c>
       <c r="AJ26" t="n">
-        <v>140</v>
+        <v>980</v>
       </c>
       <c r="AK26" t="n">
         <v>980</v>
@@ -5530,7 +5530,7 @@
         <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT26" t="n">
         <v>6.8</v>
@@ -5542,7 +5542,7 @@
         <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5560,7 +5560,7 @@
         <v>42</v>
       </c>
       <c r="BC26" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD26" t="n">
         <v>38</v>
@@ -5569,14 +5569,14 @@
         <v>13</v>
       </c>
       <c r="BF26" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BG26" t="n">
         <v>34</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
         <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R27" t="n">
         <v>1.17</v>
@@ -5655,7 +5655,7 @@
         <v>1.68</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
         <v>1.79</v>
@@ -5664,7 +5664,7 @@
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z27" t="n">
         <v>980</v>
@@ -5679,16 +5679,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
         <v>12.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
         <v>980</v>
@@ -5700,7 +5700,7 @@
         <v>980</v>
       </c>
       <c r="AK27" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AL27" t="n">
         <v>80</v>
@@ -5718,10 +5718,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS27" t="n">
         <v>65</v>
@@ -5733,10 +5733,10 @@
         <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
@@ -5745,13 +5745,13 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC27" t="n">
         <v>26</v>
@@ -5760,17 +5760,17 @@
         <v>50</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG27" t="n">
         <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J28" t="n">
         <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.35</v>
@@ -5825,7 +5825,7 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
@@ -5843,7 +5843,7 @@
         <v>3.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U28" t="n">
         <v>1.56</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX28" t="n">
         <v>5.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BF28" t="n">
         <v>6.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>1.67</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I29" t="n">
         <v>8.4</v>
@@ -6019,13 +6019,13 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
         <v>2.08</v>
@@ -6034,7 +6034,7 @@
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
         <v>2.12</v>
@@ -6061,10 +6061,10 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
         <v>36</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,13 +6106,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT29" t="n">
         <v>5.9</v>
@@ -6121,10 +6121,10 @@
         <v>7.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX29" t="n">
         <v>7.2</v>
@@ -6133,32 +6133,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB29" t="n">
         <v>12.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G30" t="n">
         <v>2.14</v>
       </c>
       <c r="H30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
         <v>1.39</v>
@@ -6213,7 +6213,7 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
         <v>1.3</v>
@@ -6222,25 +6222,25 @@
         <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
         <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V30" t="n">
         <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X30" t="n">
         <v>18</v>
@@ -6258,7 +6258,7 @@
         <v>10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
         <v>16.5</v>
@@ -6276,10 +6276,10 @@
         <v>18.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -6291,22 +6291,22 @@
         <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>13</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
         <v>9</v>
@@ -6318,7 +6318,7 @@
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>11.5</v>
@@ -6327,10 +6327,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB30" t="n">
         <v>21</v>
@@ -6339,20 +6339,20 @@
         <v>18.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -6398,16 +6398,16 @@
         <v>2.84</v>
       </c>
       <c r="K31" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L31" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M31" t="n">
         <v>1.17</v>
       </c>
       <c r="N31" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O31" t="n">
         <v>1.73</v>
@@ -6425,7 +6425,7 @@
         <v>7.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
         <v>1.64</v>
@@ -6440,43 +6440,43 @@
         <v>6.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG31" t="n">
         <v>15.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AK31" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="n">
         <v>100</v>
@@ -6488,13 +6488,13 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
         <v>13.5</v>
@@ -6506,10 +6506,10 @@
         <v>6.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW31" t="n">
         <v>40</v>
@@ -6518,25 +6518,25 @@
         <v>14.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
         <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BD31" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="BE31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF31" t="n">
         <v>50</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>4.4</v>
       </c>
       <c r="H32" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L32" t="n">
         <v>1.56</v>
@@ -6604,46 +6604,46 @@
         <v>2.62</v>
       </c>
       <c r="O32" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P32" t="n">
         <v>1.51</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U32" t="n">
         <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="W32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
         <v>9</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC32" t="n">
         <v>7.6</v>
@@ -6655,7 +6655,7 @@
         <v>32</v>
       </c>
       <c r="AF32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG32" t="n">
         <v>19</v>
@@ -6664,13 +6664,13 @@
         <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
         <v>120</v>
       </c>
       <c r="AK32" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
         <v>110</v>
@@ -6688,7 +6688,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR32" t="n">
         <v>10</v>
@@ -6703,44 +6703,44 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW32" t="n">
         <v>25</v>
       </c>
       <c r="AX32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY32" t="n">
         <v>16</v>
       </c>
       <c r="AZ32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="BB32" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BC32" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BD32" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -6774,16 +6774,16 @@
         <v>2.64</v>
       </c>
       <c r="G33" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
         <v>2.8</v>
       </c>
       <c r="I33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J33" t="n">
         <v>3.25</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.96</v>
       </c>
       <c r="K33" t="n">
         <v>3.6</v>
@@ -6819,10 +6819,10 @@
         <v>2.1</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W33" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X33" t="n">
         <v>980</v>
@@ -6900,7 +6900,7 @@
         <v>4.1</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
         <v>4.4</v>
@@ -6912,7 +6912,7 @@
         <v>4.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BB33" t="n">
         <v>4.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>10.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>7.2</v>
@@ -781,7 +781,7 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.22</v>
@@ -802,13 +802,13 @@
         <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -880,10 +880,10 @@
         <v>3.55</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -901,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
         <v>4</v>
@@ -916,11 +916,11 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -999,7 +999,7 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="W3" t="n">
         <v>1.15</v>
@@ -1014,7 +1014,7 @@
         <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB3" t="n">
         <v>25</v>
@@ -1029,7 +1029,7 @@
         <v>17.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AG3" t="n">
         <v>980</v>
@@ -1041,7 +1041,7 @@
         <v>980</v>
       </c>
       <c r="AJ3" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AK3" t="n">
         <v>130</v>
@@ -1053,16 +1053,16 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AO3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
@@ -1074,19 +1074,19 @@
         <v>18.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1107,14 +1107,14 @@
         <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1169,13 +1169,13 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1190,13 +1190,13 @@
         <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
         <v>16</v>
@@ -1244,7 +1244,7 @@
         <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN4" t="n">
         <v>7.8</v>
@@ -1256,10 +1256,10 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR4" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
         <v>6.6</v>
@@ -1283,7 +1283,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
         <v>6.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
         <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
@@ -1381,16 +1381,16 @@
         <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X5" t="n">
         <v>23</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
         <v>15</v>
@@ -1447,7 +1447,7 @@
         <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>21</v>
@@ -1465,13 +1465,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW5" t="n">
         <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
@@ -1483,7 +1483,7 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
         <v>12.5</v>
@@ -1495,14 +1495,14 @@
         <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
         <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1584,7 +1584,7 @@
         <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1593,7 +1593,7 @@
         <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
@@ -1602,7 +1602,7 @@
         <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>15.5</v>
@@ -1629,7 +1629,7 @@
         <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1650,7 +1650,7 @@
         <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
         <v>16</v>
@@ -1674,29 +1674,29 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC6" t="n">
         <v>22</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.4</v>
       </c>
-      <c r="BE6" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF6" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
         <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
@@ -1751,7 +1751,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
@@ -1772,16 +1772,16 @@
         <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X7" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1838,7 +1838,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
         <v>4.5</v>
@@ -1847,25 +1847,25 @@
         <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
         <v>3.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
         <v>4.7</v>
@@ -1880,7 +1880,7 @@
         <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>8.6</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
         <v>3.15</v>
@@ -1948,37 +1948,37 @@
         <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
         <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
         <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>16.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
@@ -2053,7 +2053,7 @@
         <v>18</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2065,16 +2065,16 @@
         <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>15</v>
       </c>
       <c r="BF8" t="n">
         <v>14.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2151,16 +2151,16 @@
         <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
         <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V9" t="n">
         <v>2.2</v>
@@ -2169,7 +2169,7 @@
         <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>14</v>
@@ -2205,25 +2205,25 @@
         <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK9" t="n">
         <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>55</v>
       </c>
       <c r="AN9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2250,7 +2250,7 @@
         <v>36</v>
       </c>
       <c r="AY9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
@@ -2259,7 +2259,7 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC9" t="n">
         <v>40</v>
@@ -2271,14 +2271,14 @@
         <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
         <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2336,19 +2336,19 @@
         <v>3.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
         <v>1.86</v>
@@ -2360,7 +2360,7 @@
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
         <v>17.5</v>
@@ -2423,10 +2423,10 @@
         <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,7 +2438,7 @@
         <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2450,7 +2450,7 @@
         <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
         <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
         <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
         <v>2.88</v>
@@ -2587,7 +2587,7 @@
         <v>19.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
         <v>18.5</v>
@@ -2650,7 +2650,7 @@
         <v>8.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
         <v>8.6</v>
@@ -2662,11 +2662,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
         <v>2.64</v>
@@ -2712,37 +2712,37 @@
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.51</v>
@@ -2751,13 +2751,13 @@
         <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
@@ -2778,55 +2778,55 @@
         <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
       </c>
       <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
         <v>50</v>
       </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
       <c r="AM12" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11</v>
-      </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2835,32 +2835,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD12" t="n">
         <v>3.85</v>
       </c>
-      <c r="BD12" t="n">
-        <v>28</v>
-      </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BF12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
@@ -2921,16 +2921,16 @@
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>1.6</v>
@@ -2939,10 +2939,10 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3002,59 +3002,59 @@
         <v>6.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>5.7</v>
       </c>
-      <c r="AW13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BA13" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3124,13 +3124,13 @@
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>1.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
         <v>1.54</v>
@@ -3223,7 +3223,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>3.95</v>
@@ -3238,7 +3238,7 @@
         <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>19</v>
       </c>
       <c r="BF14" t="n">
         <v>18</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>3.25</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>2.34</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.37</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.14</v>
-      </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE15" t="n">
         <v>26</v>
       </c>
-      <c r="AE15" t="n">
-        <v>110</v>
-      </c>
       <c r="AF15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="BA15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.25</v>
       </c>
-      <c r="G16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.74</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
         <v>26</v>
       </c>
-      <c r="AF16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AP16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I17" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.75</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -3700,7 +3700,7 @@
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -3715,10 +3715,10 @@
         <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
         <v>18.5</v>
@@ -3730,7 +3730,7 @@
         <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
@@ -3742,16 +3742,16 @@
         <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
         <v>48</v>
@@ -3766,16 +3766,16 @@
         <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
@@ -3784,25 +3784,25 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
         <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>13.5</v>
@@ -3811,13 +3811,13 @@
         <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
         <v>55</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3852,100 +3852,100 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.6</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>4</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>980</v>
       </c>
       <c r="AB18" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
         <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AH18" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>980</v>
@@ -3960,7 +3960,7 @@
         <v>980</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN18" t="n">
         <v>980</v>
@@ -3969,7 +3969,7 @@
         <v>980</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>4.6</v>
@@ -3978,53 +3978,53 @@
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV18" t="n">
         <v>4.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ18" t="n">
         <v>4.5</v>
       </c>
       <c r="BA18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB18" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG18" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="G19" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
@@ -4115,34 +4115,34 @@
         <v>980</v>
       </c>
       <c r="Z19" t="n">
-        <v>130</v>
+        <v>980</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
         <v>980</v>
       </c>
       <c r="AE19" t="n">
-        <v>140</v>
+        <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>980</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="AJ19" t="n">
         <v>980</v>
@@ -4154,71 +4154,71 @@
         <v>980</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS19" t="n">
         <v>5.8</v>
       </c>
-      <c r="AO19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AT19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW19" t="n">
         <v>5.5</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AX19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD19" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE19" t="n">
-        <v>2.58</v>
+        <v>5.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.16</v>
+        <v>5.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="G20" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="H20" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X20" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
         <v>5.6</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="AO20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP20" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AQ20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG20" t="n">
         <v>2.48</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="X20" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76</v>
+        <v>1.99</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="S21" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="T21" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U21" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AA21" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
         <v>16</v>
       </c>
       <c r="AC21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AU21" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
       </c>
       <c r="AX21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG21" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.8</v>
-      </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>2.46</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>2.68</v>
       </c>
       <c r="X22" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>18.5</v>
+        <v>180</v>
       </c>
       <c r="AB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL22" t="n">
         <v>28</v>
       </c>
-      <c r="AC22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AM22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU22" t="n">
         <v>10</v>
       </c>
-      <c r="AE22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>11</v>
-      </c>
       <c r="AV22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX22" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>42</v>
-      </c>
       <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>19</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>16</v>
-      </c>
       <c r="BA22" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="BB22" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BE22" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.8</v>
+        <v>70</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="J23" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>2.72</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.44</v>
+        <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>2.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AU23" t="n">
         <v>11</v>
       </c>
-      <c r="Y23" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AV23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB23" t="n">
         <v>65</v>
       </c>
-      <c r="AB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC23" t="n">
-        <v>4.1</v>
+        <v>46</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>7.2</v>
+        <v>2.72</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>2.96</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>2.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.81</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Y24" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AB24" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>4.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.57</v>
+        <v>2.96</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>6.4</v>
+        <v>2.38</v>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="S25" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="U25" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="W25" t="n">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="n">
         <v>22</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO25" t="n">
         <v>10</v>
       </c>
-      <c r="AG25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH25" t="n">
+      <c r="AP25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT25" t="n">
         <v>20</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
       </c>
       <c r="AV25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA25" t="n">
         <v>22</v>
       </c>
-      <c r="AW25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX25" t="n">
+      <c r="BB25" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG25" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>70</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W26" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="X26" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA26" t="n">
-        <v>820</v>
+        <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>17</v>
       </c>
       <c r="AE26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="n">
         <v>65</v>
       </c>
-      <c r="AF26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>120</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU26" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB26" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>42</v>
-      </c>
       <c r="BC26" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="BG26" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="I27" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y27" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH27" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AI27" t="n">
         <v>110</v>
       </c>
       <c r="AJ27" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>980</v>
+        <v>180</v>
       </c>
       <c r="AL27" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AN27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA27" t="n">
         <v>40</v>
       </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB27" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BG27" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT28" t="n">
         <v>5.8</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AU28" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC28" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD28" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.98</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="G29" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
         <v>2.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="Y29" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE29" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="G30" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="H30" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="I30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW30" t="n">
         <v>4.1</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="AX30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3.95</v>
       </c>
-      <c r="O30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X30" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="BE30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF30" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>12</v>
-      </c>
       <c r="BG30" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.94</v>
+        <v>2.04</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="H31" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="K31" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="U31" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="X31" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="Y31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA31" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>390</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="BB31" t="n">
         <v>21</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>310</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>28</v>
-      </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF31" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -6568,373 +6568,567 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="G32" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="H32" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="L32" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N32" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="O32" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S32" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="T32" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="V32" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AA32" t="n">
-        <v>30</v>
+        <v>340</v>
       </c>
       <c r="AB32" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AG32" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AL32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM32" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV32" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AX32" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ32" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BC32" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF32" t="n">
         <v>50</v>
       </c>
-      <c r="BF32" t="n">
-        <v>38</v>
-      </c>
       <c r="BG32" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-09 19:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Atletico Nacional Medell</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>2.64</v>
       </c>
-      <c r="G33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="G34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H34" t="n">
         <v>2.8</v>
       </c>
-      <c r="I33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="I34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K34" t="n">
         <v>3.6</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="L34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.08</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>3.45</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>1.35</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>1.92</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1.32</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>3.35</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>1.79</v>
       </c>
-      <c r="U33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X33" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="U34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X34" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC34" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="AD34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM34" t="n">
         <v>120</v>
       </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ34" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS34" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>3.9</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>3.45</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE34" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF33" t="n">
+      <c r="BF34" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-09 17:40:48</t>
+      <c r="BG34" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K2" t="n">
         <v>10.5</v>
       </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
         <v>1000</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -847,10 +847,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -859,68 +859,68 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -969,7 +969,7 @@
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -999,25 +999,25 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="n">
         <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
         <v>14.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
@@ -1026,37 +1026,37 @@
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AG3" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
-        <v>980</v>
+        <v>170</v>
       </c>
       <c r="AJ3" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
-        <v>120</v>
+        <v>520</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>430</v>
       </c>
       <c r="AN3" t="n">
         <v>190</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP3" t="n">
         <v>14</v>
@@ -1068,53 +1068,53 @@
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
         <v>14.5</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1178,16 +1178,16 @@
         <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.62</v>
@@ -1196,58 +1196,58 @@
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="Z4" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AE4" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>340</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,56 +1259,56 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
         <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
       </c>
       <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BE4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
         <v>6.4</v>
@@ -1372,13 +1372,13 @@
         <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.85</v>
@@ -1393,13 +1393,13 @@
         <v>2.64</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="Y5" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AA5" t="n">
         <v>220</v>
@@ -1411,52 +1411,52 @@
         <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="AE5" t="n">
         <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="AJ5" t="n">
         <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>980</v>
+        <v>140</v>
       </c>
       <c r="AM5" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO5" t="n">
         <v>130</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>120</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1465,44 +1465,44 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF5" t="n">
         <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.72</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.68</v>
-      </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.28</v>
@@ -1569,64 +1569,64 @@
         <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
         <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>2.76</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>2.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.6</v>
+        <v>2.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
         <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.34</v>
@@ -1757,10 +1757,10 @@
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.34</v>
@@ -1772,13 +1772,13 @@
         <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1793,28 +1793,28 @@
         <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>100</v>
+        <v>420</v>
       </c>
       <c r="AF7" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
         <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="AJ7" t="n">
         <v>980</v>
@@ -1829,68 +1829,68 @@
         <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
         <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -1969,122 +1969,122 @@
         <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH8" t="n">
         <v>25</v>
       </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AI8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11</v>
       </c>
-      <c r="AD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AZ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA8" t="n">
         <v>8</v>
       </c>
-      <c r="AV8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
         <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
@@ -2136,43 +2136,43 @@
         <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
         <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
         <v>14.5</v>
@@ -2214,16 +2214,16 @@
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
       </c>
       <c r="AP9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2238,7 +2238,7 @@
         <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
         <v>9.800000000000001</v>
@@ -2253,32 +2253,32 @@
         <v>17.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BC9" t="n">
         <v>40</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
         <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2339,10 +2339,10 @@
         <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
@@ -2357,58 +2357,58 @@
         <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
         <v>17.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AA10" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
         <v>110</v>
       </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>11</v>
@@ -2423,10 +2423,10 @@
         <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,7 +2438,7 @@
         <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2450,7 +2450,7 @@
         <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
         <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -2533,16 +2533,16 @@
         <v>1.58</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R11" t="n">
         <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T11" t="n">
         <v>2.2</v>
@@ -2560,13 +2560,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z11" t="n">
         <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
@@ -2578,7 +2578,7 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
         <v>30</v>
@@ -2587,52 +2587,52 @@
         <v>19.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AM11" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
         <v>24</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>18.5</v>
@@ -2647,26 +2647,26 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
         <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
         <v>2.92</v>
@@ -2709,7 +2709,7 @@
         <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
@@ -2778,7 +2778,7 @@
         <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
@@ -2814,7 +2814,7 @@
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2838,16 +2838,16 @@
         <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>3.9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.85</v>
       </c>
       <c r="BE12" t="n">
         <v>21</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
         <v>2.22</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2915,7 +2915,7 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
@@ -2927,10 +2927,10 @@
         <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
         <v>1.6</v>
@@ -2939,7 +2939,7 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
         <v>1.81</v>
@@ -2948,7 +2948,7 @@
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,25 +2957,25 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2984,77 +2984,77 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.96</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.72</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.86</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
         <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BF13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
         <v>2.98</v>
@@ -3097,7 +3097,7 @@
         <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3118,19 +3118,19 @@
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
         <v>1.54</v>
@@ -3145,16 +3145,16 @@
         <v>14.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB14" t="n">
         <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
         <v>15</v>
@@ -3169,16 +3169,16 @@
         <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
         <v>50</v>
@@ -3187,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
         <v>28</v>
@@ -3199,10 +3199,10 @@
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3214,41 +3214,41 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
         <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3327,64 +3327,64 @@
         <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W15" t="n">
         <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL15" t="n">
         <v>980</v>
       </c>
-      <c r="AB15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI15" t="n">
+      <c r="AM15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN15" t="n">
         <v>980</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>36</v>
-      </c>
       <c r="AO15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -3396,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -3408,41 +3408,41 @@
         <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
         <v>1.88</v>
@@ -3491,7 +3491,7 @@
         <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3533,13 +3533,13 @@
         <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -3554,7 +3554,7 @@
         <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>27</v>
@@ -3572,7 +3572,7 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
@@ -3584,13 +3584,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB16" t="n">
         <v>16.5</v>
@@ -3623,20 +3623,20 @@
         <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3700,7 +3700,7 @@
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -3718,16 +3718,16 @@
         <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
         <v>50</v>
@@ -3736,101 +3736,101 @@
         <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>38</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
         <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="AX17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>14</v>
       </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB17" t="n">
         <v>30</v>
       </c>
-      <c r="BB17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BF17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG17" t="n">
         <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="I18" t="n">
         <v>2.96</v>
@@ -3876,7 +3876,7 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.27</v>
@@ -3891,61 +3891,61 @@
         <v>1.21</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U18" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
         <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
         <v>90</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="Z18" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA18" t="n">
         <v>980</v>
       </c>
       <c r="AB18" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
         <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AG18" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
         <v>980</v>
@@ -3954,77 +3954,77 @@
         <v>980</v>
       </c>
       <c r="AK18" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>980</v>
       </c>
       <c r="AM18" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
         <v>2.14</v>
@@ -4067,10 +4067,10 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.28</v>
@@ -4079,25 +4079,25 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
         <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
         <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
         <v>2.34</v>
@@ -4106,7 +4106,7 @@
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
@@ -4118,13 +4118,13 @@
         <v>980</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>980</v>
@@ -4133,19 +4133,19 @@
         <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AH19" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
         <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
         <v>980</v>
@@ -4154,71 +4154,71 @@
         <v>980</v>
       </c>
       <c r="AM19" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
         <v>980</v>
       </c>
       <c r="AP19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB19" t="n">
+      <c r="BG19" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.41</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>10.5</v>
@@ -4264,7 +4264,7 @@
         <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -4279,7 +4279,7 @@
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>1.4</v>
@@ -4288,13 +4288,13 @@
         <v>1.9</v>
       </c>
       <c r="S20" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
@@ -4309,110 +4309,110 @@
         <v>980</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="AC20" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AD20" t="n">
         <v>980</v>
       </c>
       <c r="AE20" t="n">
-        <v>140</v>
+        <v>510</v>
       </c>
       <c r="AF20" t="n">
         <v>980</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>500</v>
       </c>
       <c r="AH20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>400</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>980</v>
       </c>
-      <c r="AI20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>15</v>
-      </c>
       <c r="AK20" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
         <v>980</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AO20" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.6</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>8</v>
       </c>
-      <c r="AS20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>6</v>
-      </c>
       <c r="BA20" t="n">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>19</v>
+        <v>2.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.48</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -4455,7 +4455,7 @@
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
         <v>4.8</v>
@@ -4485,64 +4485,64 @@
         <v>2.28</v>
       </c>
       <c r="T21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V21" t="n">
         <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X21" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="Y21" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="Z21" t="n">
         <v>980</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AB21" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE21" t="n">
         <v>980</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>980</v>
       </c>
       <c r="AJ21" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
         <v>980</v>
       </c>
       <c r="AM21" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>8.4</v>
@@ -4551,62 +4551,62 @@
         <v>980</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD21" t="n">
         <v>13</v>
       </c>
-      <c r="BD21" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="n">
         <v>6.4</v>
@@ -4661,34 +4661,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V22" t="n">
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X22" t="n">
         <v>20</v>
@@ -4700,16 +4700,16 @@
         <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>80</v>
@@ -4727,7 +4727,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK22" t="n">
         <v>15</v>
@@ -4736,10 +4736,10 @@
         <v>28</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO22" t="n">
         <v>85</v>
@@ -4748,7 +4748,7 @@
         <v>19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
         <v>46</v>
@@ -4757,16 +4757,16 @@
         <v>65</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV22" t="n">
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX22" t="n">
         <v>9.6</v>
@@ -4775,32 +4775,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
         <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
         <v>70</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I23" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J23" t="n">
         <v>4.7</v>
@@ -4855,7 +4855,7 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.16</v>
@@ -4876,13 +4876,13 @@
         <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V23" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
         <v>32</v>
@@ -4897,7 +4897,7 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC23" t="n">
         <v>11.5</v>
@@ -4915,7 +4915,7 @@
         <v>19.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4930,7 +4930,7 @@
         <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
         <v>40</v>
@@ -4939,7 +4939,7 @@
         <v>6.2</v>
       </c>
       <c r="AP23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ23" t="n">
         <v>12.5</v>
@@ -4948,7 +4948,7 @@
         <v>12.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>26</v>
@@ -4960,7 +4960,7 @@
         <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>40</v>
@@ -4969,19 +4969,19 @@
         <v>19</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BC23" t="n">
         <v>46</v>
       </c>
       <c r="BD23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE23" t="n">
         <v>50</v>
@@ -4990,11 +4990,11 @@
         <v>34</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5049,10 +5049,10 @@
         <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P24" t="n">
         <v>1.58</v>
@@ -5079,116 +5079,116 @@
         <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>1.54</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>1.44</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.55</v>
+        <v>1.51</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.75</v>
+        <v>1.59</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>1.51</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18</v>
+        <v>1.54</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>1.58</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.3</v>
+        <v>1.58</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.4</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G25" t="n">
         <v>2.96</v>
       </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
       <c r="H25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
         <v>1.26</v>
@@ -5243,40 +5243,40 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R25" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U25" t="n">
         <v>3.05</v>
       </c>
       <c r="V25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="n">
         <v>21</v>
@@ -5294,7 +5294,7 @@
         <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
         <v>26</v>
@@ -5309,7 +5309,7 @@
         <v>23</v>
       </c>
       <c r="AJ25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
         <v>26</v>
@@ -5318,7 +5318,7 @@
         <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AN25" t="n">
         <v>14.5</v>
@@ -5327,10 +5327,10 @@
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
         <v>19.5</v>
@@ -5348,10 +5348,10 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY25" t="n">
         <v>13</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5422,16 +5422,16 @@
         <v>3.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J26" t="n">
         <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
@@ -5440,13 +5440,13 @@
         <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P26" t="n">
         <v>1.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R26" t="n">
         <v>1.29</v>
@@ -5455,34 +5455,34 @@
         <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
         <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
         <v>1.63</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
         <v>27</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
         <v>17</v>
@@ -5494,13 +5494,13 @@
         <v>17.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ26" t="n">
         <v>40</v>
@@ -5512,10 +5512,10 @@
         <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AO26" t="n">
         <v>55</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT26" t="n">
         <v>8.199999999999999</v>
@@ -5542,7 +5542,7 @@
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5551,32 +5551,32 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF26" t="n">
         <v>18</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H27" t="n">
         <v>3.35</v>
@@ -5619,7 +5619,7 @@
         <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
@@ -5631,7 +5631,7 @@
         <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O27" t="n">
         <v>1.71</v>
@@ -5640,19 +5640,19 @@
         <v>1.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
         <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T27" t="n">
         <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V27" t="n">
         <v>1.4</v>
@@ -5661,7 +5661,7 @@
         <v>1.54</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y27" t="n">
         <v>8.4</v>
@@ -5670,52 +5670,52 @@
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC27" t="n">
         <v>7</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
         <v>15</v>
       </c>
       <c r="AH27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AJ27" t="n">
         <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM27" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AN27" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="AO27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ27" t="n">
         <v>7.6</v>
@@ -5727,19 +5727,19 @@
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU27" t="n">
         <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY27" t="n">
         <v>12.5</v>
@@ -5754,13 +5754,13 @@
         <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BD27" t="n">
         <v>60</v>
       </c>
       <c r="BE27" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="BF27" t="n">
         <v>29</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I28" t="n">
         <v>4.4</v>
@@ -5819,19 +5819,19 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
         <v>2.72</v>
@@ -5840,28 +5840,28 @@
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
         <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y28" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>11</v>
-      </c>
       <c r="Z28" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5873,7 +5873,7 @@
         <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
@@ -5885,19 +5885,19 @@
         <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AI28" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AJ28" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="AK28" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AM28" t="n">
         <v>280</v>
@@ -5918,19 +5918,19 @@
         <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
         <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>9.800000000000001</v>
@@ -5939,32 +5939,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB28" t="n">
         <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G29" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="H29" t="n">
         <v>9.6</v>
       </c>
       <c r="I29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K29" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6034,19 +6034,19 @@
         <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T29" t="n">
         <v>2.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
         <v>1.08</v>
       </c>
       <c r="W29" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="X29" t="n">
         <v>90</v>
@@ -6055,16 +6055,16 @@
         <v>980</v>
       </c>
       <c r="Z29" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
         <v>980</v>
@@ -6073,10 +6073,10 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>980</v>
+        <v>7.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>980</v>
@@ -6085,10 +6085,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
         <v>1000</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,59 +6106,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU29" t="n">
         <v>8.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AX29" t="n">
         <v>5.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF29" t="n">
         <v>7</v>
       </c>
-      <c r="BA29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG29" t="n">
-        <v>2.44</v>
+        <v>8.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>1.67</v>
       </c>
       <c r="H30" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>8.4</v>
@@ -6204,7 +6204,7 @@
         <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.37</v>
@@ -6228,13 +6228,13 @@
         <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
         <v>1.13</v>
@@ -6273,7 +6273,7 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
@@ -6282,16 +6282,16 @@
         <v>18.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -6300,13 +6300,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14.5</v>
+        <v>3.75</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
         <v>5.9</v>
@@ -6315,10 +6315,10 @@
         <v>7.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
         <v>7.2</v>
@@ -6327,32 +6327,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC30" t="n">
         <v>16</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
         <v>8.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.04</v>
       </c>
       <c r="G31" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H31" t="n">
         <v>3.85</v>
@@ -6401,7 +6401,7 @@
         <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6425,46 +6425,46 @@
         <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
         <v>1.89</v>
       </c>
       <c r="X31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB31" t="n">
         <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF31" t="n">
         <v>14.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>18.5</v>
@@ -6473,7 +6473,7 @@
         <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK31" t="n">
         <v>23</v>
@@ -6488,19 +6488,19 @@
         <v>15</v>
       </c>
       <c r="AO31" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>13</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>12</v>
-      </c>
       <c r="AR31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6518,35 +6518,35 @@
         <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BB31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC31" t="n">
         <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BF31" t="n">
         <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -6580,34 +6580,34 @@
         <v>2.94</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L32" t="n">
         <v>1.69</v>
       </c>
       <c r="M32" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
         <v>3.2</v>
@@ -6616,37 +6616,37 @@
         <v>1.13</v>
       </c>
       <c r="S32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
         <v>7.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
@@ -6655,28 +6655,28 @@
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH32" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AI32" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AK32" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AL32" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM32" t="n">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6685,13 +6685,13 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>6.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>13</v>
@@ -6709,10 +6709,10 @@
         <v>40</v>
       </c>
       <c r="AX32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ32" t="n">
         <v>24</v>
@@ -6721,7 +6721,7 @@
         <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC32" t="n">
         <v>28</v>
@@ -6730,17 +6730,17 @@
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BG32" t="n">
         <v>34</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H33" t="n">
         <v>2.14</v>
@@ -6789,7 +6789,7 @@
         <v>3.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M33" t="n">
         <v>1.13</v>
@@ -6807,7 +6807,7 @@
         <v>2.68</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
         <v>5.6</v>
@@ -6816,7 +6816,7 @@
         <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
         <v>1.8</v>
@@ -6825,13 +6825,13 @@
         <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA33" t="n">
         <v>30</v>
@@ -6846,19 +6846,19 @@
         <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF33" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AG33" t="n">
         <v>19</v>
       </c>
       <c r="AH33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
         <v>120</v>
@@ -6870,7 +6870,7 @@
         <v>110</v>
       </c>
       <c r="AM33" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN33" t="n">
         <v>1000</v>
@@ -6888,22 +6888,22 @@
         <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY33" t="n">
         <v>16</v>
@@ -6912,16 +6912,16 @@
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB33" t="n">
         <v>36</v>
       </c>
       <c r="BC33" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BE33" t="n">
         <v>50</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -6968,16 +6968,16 @@
         <v>2.64</v>
       </c>
       <c r="G34" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H34" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J34" t="n">
         <v>3.3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.96</v>
       </c>
       <c r="K34" t="n">
         <v>3.6</v>
@@ -6998,31 +6998,31 @@
         <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R34" t="n">
         <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
         <v>1.79</v>
       </c>
       <c r="U34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W34" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X34" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="Y34" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
         <v>980</v>
@@ -7031,13 +7031,13 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AC34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AE34" t="n">
         <v>980</v>
@@ -7046,7 +7046,7 @@
         <v>980</v>
       </c>
       <c r="AG34" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AH34" t="n">
         <v>980</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV34" t="n">
+      <c r="AY34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>4.4</v>
       </c>
       <c r="BA34" t="n">
         <v>4.7</v>
       </c>
       <c r="BB34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC34" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD34" t="n">
-        <v>30</v>
-      </c>
       <c r="BE34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -760,34 +760,34 @@
         <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
         <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
         <v>1.52</v>
@@ -802,13 +802,13 @@
         <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>500</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -880,7 +880,7 @@
         <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AV2" t="n">
         <v>4.2</v>
@@ -889,38 +889,38 @@
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -975,19 +975,19 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
         <v>3.25</v>
@@ -996,13 +996,13 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1014,16 +1014,16 @@
         <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>30</v>
@@ -1032,19 +1032,19 @@
         <v>420</v>
       </c>
       <c r="AG3" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI3" t="n">
         <v>170</v>
       </c>
       <c r="AJ3" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AK3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL3" t="n">
         <v>520</v>
@@ -1053,10 +1053,10 @@
         <v>430</v>
       </c>
       <c r="AN3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP3" t="n">
         <v>14</v>
@@ -1092,29 +1092,29 @@
         <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1154,55 +1154,55 @@
         <v>14.5</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.33</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.32</v>
-      </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
         <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
         <v>170</v>
@@ -1211,13 +1211,13 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AE4" t="n">
         <v>360</v>
@@ -1226,10 +1226,10 @@
         <v>8.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>280</v>
@@ -1238,43 +1238,43 @@
         <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="AM4" t="n">
         <v>340</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>9.199999999999999</v>
@@ -1295,20 +1295,20 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
         <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
         <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
         <v>7.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -1363,25 +1363,25 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
         <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
@@ -1390,13 +1390,13 @@
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X5" t="n">
         <v>44</v>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="Z5" t="n">
         <v>210</v>
@@ -1414,7 +1414,7 @@
         <v>190</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AF5" t="n">
         <v>10</v>
@@ -1429,13 +1429,13 @@
         <v>470</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
         <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>390</v>
@@ -1447,16 +1447,16 @@
         <v>130</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1468,7 +1468,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.28</v>
@@ -1557,10 +1557,10 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
         <v>2.16</v>
@@ -1584,7 +1584,7 @@
         <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,16 +1641,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1662,31 +1662,31 @@
         <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BD6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="BF6" t="n">
         <v>3.45</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
@@ -1739,7 +1739,7 @@
         <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
@@ -1769,7 +1769,7 @@
         <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
@@ -1778,7 +1778,7 @@
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1808,10 +1808,10 @@
         <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>330</v>
@@ -1820,13 +1820,13 @@
         <v>980</v>
       </c>
       <c r="AK7" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>85</v>
@@ -1841,10 +1841,10 @@
         <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AT7" t="n">
         <v>4.9</v>
@@ -1853,10 +1853,10 @@
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX7" t="n">
         <v>5.6</v>
@@ -1865,10 +1865,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1877,20 +1877,20 @@
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
         <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
         <v>11.5</v>
@@ -2038,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
         <v>8.4</v>
@@ -2062,13 +2062,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
         <v>8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
         <v>7.8</v>
@@ -2080,11 +2080,11 @@
         <v>6.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
@@ -2139,16 +2139,16 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>1.74</v>
@@ -2163,7 +2163,7 @@
         <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2217,7 +2217,7 @@
         <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2259,7 +2259,7 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BC9" t="n">
         <v>40</v>
@@ -2271,14 +2271,14 @@
         <v>46</v>
       </c>
       <c r="BF9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
         <v>8</v>
@@ -2324,16 +2324,16 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.29</v>
@@ -2360,10 +2360,10 @@
         <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
         <v>22</v>
@@ -2372,13 +2372,13 @@
         <v>160</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>25</v>
@@ -2396,7 +2396,7 @@
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
         <v>17</v>
@@ -2411,22 +2411,22 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
         <v>17.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -2438,7 +2438,7 @@
         <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -2450,7 +2450,7 @@
         <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2459,20 +2459,20 @@
         <v>14.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
         <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
         <v>1.58</v>
@@ -2548,7 +2548,7 @@
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
         <v>1.69</v>
@@ -2566,7 +2566,7 @@
         <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
@@ -2581,7 +2581,7 @@
         <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AG11" t="n">
         <v>19.5</v>
@@ -2590,7 +2590,7 @@
         <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -2602,7 +2602,7 @@
         <v>400</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -2611,7 +2611,7 @@
         <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.9</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>8.4</v>
@@ -2656,7 +2656,7 @@
         <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>8.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2826,7 +2826,7 @@
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2847,7 +2847,7 @@
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE12" t="n">
         <v>21</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
         <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
         <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2969,7 +2969,7 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AG13" t="n">
         <v>40</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3029,19 +3029,19 @@
         <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
@@ -3050,11 +3050,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3226,16 +3226,16 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
         <v>19</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
@@ -3318,7 +3318,7 @@
         <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
         <v>1.64</v>
@@ -3327,7 +3327,7 @@
         <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W15" t="n">
         <v>1.37</v>
@@ -3342,7 +3342,7 @@
         <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB15" t="n">
         <v>16</v>
@@ -3354,7 +3354,7 @@
         <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>70</v>
@@ -3369,13 +3369,13 @@
         <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AK15" t="n">
         <v>210</v>
       </c>
       <c r="AL15" t="n">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="AM15" t="n">
         <v>200</v>
@@ -3426,7 +3426,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BD15" t="n">
         <v>8.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
         <v>1.88</v>
@@ -3488,7 +3488,7 @@
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.44</v>
@@ -3545,7 +3545,7 @@
         <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>100</v>
@@ -3590,7 +3590,7 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
         <v>16.5</v>
@@ -3632,11 +3632,11 @@
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3673,10 +3673,10 @@
         <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -3715,13 +3715,13 @@
         <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
         <v>1.61</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
@@ -3760,7 +3760,7 @@
         <v>38</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -3769,19 +3769,19 @@
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
         <v>20</v>
@@ -3790,10 +3790,10 @@
         <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
         <v>26</v>
@@ -3805,7 +3805,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
         <v>34</v>
@@ -3820,7 +3820,7 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF17" t="n">
         <v>16.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H18" t="n">
         <v>2.64</v>
@@ -3876,37 +3876,37 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T18" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
         <v>1.54</v>
@@ -3924,7 +3924,7 @@
         <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>500</v>
@@ -3939,7 +3939,7 @@
         <v>980</v>
       </c>
       <c r="AF18" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AG18" t="n">
         <v>36</v>
@@ -3951,10 +3951,10 @@
         <v>980</v>
       </c>
       <c r="AJ18" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK18" t="n">
         <v>980</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>980</v>
@@ -3969,16 +3969,16 @@
         <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,10 +3990,10 @@
         <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
         <v>7</v>
@@ -4002,29 +4002,29 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC18" t="n">
         <v>8</v>
       </c>
-      <c r="BC18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
         <v>980</v>
       </c>
       <c r="AG19" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AH19" t="n">
         <v>60</v>
@@ -4145,10 +4145,10 @@
         <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
         <v>980</v>
@@ -4163,19 +4163,19 @@
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
         <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>5.5</v>
@@ -4184,7 +4184,7 @@
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AX19" t="n">
         <v>7.6</v>
@@ -4196,7 +4196,7 @@
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BB19" t="n">
         <v>8.800000000000001</v>
@@ -4205,20 +4205,20 @@
         <v>8</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BG19" t="n">
         <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G20" t="n">
         <v>1.41</v>
@@ -4258,13 +4258,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
         <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -4297,7 +4297,7 @@
         <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
         <v>3.35</v>
@@ -4339,7 +4339,7 @@
         <v>400</v>
       </c>
       <c r="AJ20" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
         <v>500</v>
@@ -4360,10 +4360,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
@@ -4375,7 +4375,7 @@
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW20" t="n">
         <v>4.2</v>
@@ -4399,20 +4399,20 @@
         <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BE20" t="n">
         <v>11</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -4458,13 +4458,13 @@
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.24</v>
       </c>
       <c r="M21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
         <v>5.6</v>
@@ -4485,7 +4485,7 @@
         <v>2.28</v>
       </c>
       <c r="T21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U21" t="n">
         <v>2.46</v>
@@ -4494,25 +4494,25 @@
         <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="n">
         <v>65</v>
       </c>
       <c r="Z21" t="n">
-        <v>980</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>34</v>
@@ -4542,22 +4542,22 @@
         <v>980</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>250</v>
       </c>
       <c r="AN21" t="n">
         <v>8.4</v>
       </c>
       <c r="AO21" t="n">
-        <v>980</v>
+        <v>240</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS21" t="n">
         <v>8.199999999999999</v>
@@ -4572,7 +4572,7 @@
         <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
@@ -4587,7 +4587,7 @@
         <v>7.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>9</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
         <v>6.6</v>
       </c>
       <c r="J22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K22" t="n">
         <v>4.6</v>
       </c>
-      <c r="K22" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
         <v>1.83</v>
@@ -4688,22 +4688,22 @@
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA22" t="n">
         <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
@@ -4727,7 +4727,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>15</v>
@@ -4736,10 +4736,10 @@
         <v>28</v>
       </c>
       <c r="AM22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO22" t="n">
         <v>85</v>
@@ -4748,7 +4748,7 @@
         <v>19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>46</v>
@@ -4763,19 +4763,19 @@
         <v>9.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>65</v>
       </c>
       <c r="AX22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY22" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
         <v>55</v>
@@ -4793,14 +4793,14 @@
         <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
         <v>70</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4867,10 +4867,10 @@
         <v>1.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S23" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T23" t="n">
         <v>1.57</v>
@@ -4882,7 +4882,7 @@
         <v>2.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
         <v>32</v>
@@ -4912,13 +4912,13 @@
         <v>46</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>110</v>
@@ -4927,13 +4927,13 @@
         <v>55</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO23" t="n">
         <v>6.2</v>
@@ -4963,7 +4963,7 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY23" t="n">
         <v>19</v>
@@ -4987,14 +4987,14 @@
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG23" t="n">
         <v>5.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
         <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU24" t="n">
         <v>1.47</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AV24" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AX24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>1.59</v>
       </c>
-      <c r="AY24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BA24" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>2.92</v>
       </c>
       <c r="G25" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I25" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5252,7 +5252,7 @@
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.84</v>
@@ -5267,7 +5267,7 @@
         <v>3.05</v>
       </c>
       <c r="V25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W25" t="n">
         <v>1.51</v>
@@ -5276,7 +5276,7 @@
         <v>30</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z25" t="n">
         <v>21</v>
@@ -5294,16 +5294,16 @@
         <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
         <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
         <v>23</v>
@@ -5318,13 +5318,13 @@
         <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN25" t="n">
         <v>14.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP25" t="n">
         <v>28</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
         <v>3.15</v>
@@ -5431,7 +5431,7 @@
         <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
@@ -5461,19 +5461,19 @@
         <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
         <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
         <v>190</v>
@@ -5494,7 +5494,7 @@
         <v>17.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
@@ -5509,7 +5509,7 @@
         <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
@@ -5527,10 +5527,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT26" t="n">
         <v>8.199999999999999</v>
@@ -5551,7 +5551,7 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
         <v>40</v>
@@ -5566,7 +5566,7 @@
         <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF26" t="n">
         <v>18</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.72</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H27" t="n">
         <v>3.35</v>
@@ -5661,7 +5661,7 @@
         <v>1.54</v>
       </c>
       <c r="X27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y27" t="n">
         <v>8.4</v>
@@ -5700,13 +5700,13 @@
         <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AL27" t="n">
         <v>95</v>
       </c>
       <c r="AM27" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>210</v>
@@ -5733,7 +5733,7 @@
         <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
         <v>50</v>
@@ -5742,7 +5742,7 @@
         <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5751,10 +5751,10 @@
         <v>40</v>
       </c>
       <c r="BB27" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD27" t="n">
         <v>60</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
         <v>3.95</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.35</v>
@@ -5831,7 +5831,7 @@
         <v>1.58</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q28" t="n">
         <v>2.72</v>
@@ -5840,7 +5840,7 @@
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T28" t="n">
         <v>2.26</v>
@@ -5849,7 +5849,7 @@
         <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W28" t="n">
         <v>1.8</v>
@@ -5900,7 +5900,7 @@
         <v>170</v>
       </c>
       <c r="AM28" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN28" t="n">
         <v>32</v>
@@ -5915,7 +5915,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS28" t="n">
         <v>10.5</v>
@@ -5945,10 +5945,10 @@
         <v>10.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC28" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BD28" t="n">
         <v>55</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G29" t="n">
         <v>1.42</v>
       </c>
       <c r="H29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>15.5</v>
@@ -6010,7 +6010,7 @@
         <v>4.6</v>
       </c>
       <c r="K29" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.35</v>
@@ -6064,7 +6064,7 @@
         <v>6.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AD29" t="n">
         <v>980</v>
@@ -6085,13 +6085,13 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6127,13 +6127,13 @@
         <v>8.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
         <v>8.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -6228,13 +6228,13 @@
         <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V30" t="n">
         <v>1.13</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -6401,13 +6401,13 @@
         <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O31" t="n">
         <v>1.3</v>
@@ -6416,22 +6416,22 @@
         <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
         <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
         <v>1.77</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
         <v>1.89</v>
@@ -6446,16 +6446,16 @@
         <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
         <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
         <v>55</v>
@@ -6500,7 +6500,7 @@
         <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6521,10 +6521,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -6533,10 +6533,10 @@
         <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF31" t="n">
         <v>12</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -6589,10 +6589,10 @@
         <v>3.15</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K32" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L32" t="n">
         <v>1.69</v>
@@ -6634,10 +6634,10 @@
         <v>7.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA32" t="n">
         <v>280</v>
@@ -6646,7 +6646,7 @@
         <v>7.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
@@ -6661,13 +6661,13 @@
         <v>16</v>
       </c>
       <c r="AH32" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="n">
         <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK32" t="n">
         <v>60</v>
@@ -6676,7 +6676,7 @@
         <v>120</v>
       </c>
       <c r="AM32" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6685,7 +6685,7 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
         <v>6.6</v>
@@ -6694,28 +6694,28 @@
         <v>15</v>
       </c>
       <c r="AS32" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT32" t="n">
         <v>6.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AX32" t="n">
         <v>15</v>
       </c>
       <c r="AY32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA32" t="n">
         <v>40</v>
@@ -6724,13 +6724,13 @@
         <v>27</v>
       </c>
       <c r="BC32" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF32" t="n">
         <v>32</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -6771,28 +6771,28 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.59</v>
       </c>
       <c r="M33" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N33" t="n">
         <v>2.62</v>
@@ -6801,7 +6801,7 @@
         <v>1.56</v>
       </c>
       <c r="P33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q33" t="n">
         <v>2.68</v>
@@ -6810,25 +6810,25 @@
         <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T33" t="n">
         <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X33" t="n">
         <v>9</v>
       </c>
       <c r="Y33" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Z33" t="n">
         <v>11.5</v>
@@ -6837,19 +6837,19 @@
         <v>30</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
         <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF33" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AG33" t="n">
         <v>19</v>
@@ -6876,13 +6876,13 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP33" t="n">
         <v>8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR33" t="n">
         <v>10</v>
@@ -6891,10 +6891,10 @@
         <v>21</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
@@ -6903,22 +6903,22 @@
         <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>20</v>
       </c>
       <c r="BA33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC33" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BD33" t="n">
         <v>40</v>
@@ -6927,14 +6927,14 @@
         <v>50</v>
       </c>
       <c r="BF33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG33" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G34" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H34" t="n">
         <v>2.82</v>
@@ -6980,37 +6980,37 @@
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L34" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
         <v>2.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T34" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V34" t="n">
         <v>1.48</v>
@@ -7073,10 +7073,10 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR34" t="n">
         <v>4.2</v>
@@ -7091,10 +7091,10 @@
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX34" t="n">
         <v>4.1</v>
@@ -7109,7 +7109,7 @@
         <v>4.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC34" t="n">
         <v>4.5</v>
@@ -7118,17 +7118,17 @@
         <v>4.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF34" t="n">
         <v>4.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,52 +757,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
         <v>42</v>
@@ -847,13 +847,13 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
         <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -877,10 +877,10 @@
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="AV2" t="n">
         <v>4.2</v>
@@ -889,38 +889,38 @@
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -954,91 +954,91 @@
         <v>7.2</v>
       </c>
       <c r="G3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
         <v>42</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="AG3" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>260</v>
@@ -1050,25 +1050,25 @@
         <v>520</v>
       </c>
       <c r="AM3" t="n">
-        <v>430</v>
+        <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1080,10 +1080,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
@@ -1095,26 +1095,26 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC3" t="n">
         <v>14</v>
       </c>
-      <c r="BC3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1145,94 +1145,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AE4" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AI4" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="AJ4" t="n">
         <v>11</v>
@@ -1241,74 +1241,74 @@
         <v>19.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="AN4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR4" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1339,55 +1339,55 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
         <v>6.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
         <v>2.66</v>
@@ -1396,19 +1396,19 @@
         <v>44</v>
       </c>
       <c r="Y5" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="n">
         <v>210</v>
       </c>
       <c r="AA5" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>190</v>
@@ -1417,7 +1417,7 @@
         <v>260</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1432,31 +1432,31 @@
         <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
         <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>390</v>
+        <v>700</v>
       </c>
       <c r="AN5" t="n">
         <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1465,10 +1465,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1477,10 +1477,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1489,20 +1489,20 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
         <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>25</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.86</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.05</v>
+        <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.58</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.35</v>
+        <v>16.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.98</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.78</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.72</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.98</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.74</v>
+        <v>9.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.45</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1790,31 +1790,31 @@
         <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>420</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
         <v>980</v>
@@ -1823,7 +1823,7 @@
         <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
@@ -1832,7 +1832,7 @@
         <v>85</v>
       </c>
       <c r="AO7" t="n">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -1841,25 +1841,25 @@
         <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.96</v>
+        <v>2.08</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>6.2</v>
@@ -1868,7 +1868,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1877,20 +1877,20 @@
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X8" t="n">
         <v>44</v>
@@ -1990,10 +1990,10 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>60</v>
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2023,10 +2023,10 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
@@ -2038,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>8.4</v>
@@ -2062,29 +2062,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
         <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
         <v>4.7</v>
@@ -2154,7 +2154,7 @@
         <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
         <v>1.56</v>
@@ -2163,7 +2163,7 @@
         <v>2.72</v>
       </c>
       <c r="V9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2178,7 +2178,7 @@
         <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
         <v>26</v>
@@ -2202,10 +2202,10 @@
         <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="n">
         <v>44</v>
@@ -2214,19 +2214,19 @@
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AP9" t="n">
         <v>27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
         <v>13.5</v>
@@ -2238,7 +2238,7 @@
         <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>9.800000000000001</v>
@@ -2250,7 +2250,7 @@
         <v>36</v>
       </c>
       <c r="AY9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
@@ -2259,7 +2259,7 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BC9" t="n">
         <v>40</v>
@@ -2268,17 +2268,17 @@
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BG9" t="n">
         <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2309,76 +2309,76 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
         <v>160</v>
       </c>
       <c r="AA10" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>25</v>
@@ -2387,22 +2387,22 @@
         <v>260</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>110</v>
@@ -2411,68 +2411,68 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
       </c>
       <c r="AV10" t="n">
         <v>19.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY10" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
         <v>8.199999999999999</v>
@@ -2566,7 +2566,7 @@
         <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -2632,41 +2632,41 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>18.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC11" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
         <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
         <v>2.92</v>
@@ -2715,28 +2715,28 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
         <v>1.71</v>
@@ -2745,7 +2745,7 @@
         <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.52</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
       </c>
       <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.52</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3005,10 +3005,10 @@
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3029,32 +3029,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>2.98</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I14" t="n">
         <v>2.82</v>
@@ -3103,13 +3103,13 @@
         <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
@@ -3118,13 +3118,13 @@
         <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
         <v>1.67</v>
@@ -3136,7 +3136,7 @@
         <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
         <v>19</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="n">
         <v>2.28</v>
@@ -3297,28 +3297,28 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
         <v>1.64</v>
@@ -3330,10 +3330,10 @@
         <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
@@ -3342,10 +3342,10 @@
         <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AB15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
         <v>9</v>
@@ -3360,13 +3360,13 @@
         <v>70</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
         <v>440</v>
@@ -3375,7 +3375,7 @@
         <v>210</v>
       </c>
       <c r="AL15" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AM15" t="n">
         <v>200</v>
@@ -3384,7 +3384,7 @@
         <v>980</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>15.5</v>
@@ -3408,7 +3408,7 @@
         <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG15" t="n">
         <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
         <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
         <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
         <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3548,10 +3548,10 @@
         <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3560,22 +3560,22 @@
         <v>27</v>
       </c>
       <c r="AI16" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
         <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3590,7 +3590,7 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,10 +3614,10 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>17.5</v>
@@ -3632,11 +3632,11 @@
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3667,31 +3667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="I17" t="n">
         <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -3700,13 +3700,13 @@
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3718,7 +3718,7 @@
         <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
         <v>17</v>
@@ -3727,7 +3727,7 @@
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
         <v>50</v>
@@ -3745,7 +3745,7 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3769,13 +3769,13 @@
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>13</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF17" t="n">
         <v>16.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3861,52 +3861,52 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
         <v>1.54</v>
@@ -3915,22 +3915,22 @@
         <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="Y18" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
         <v>32</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
         <v>980</v>
@@ -3960,7 +3960,7 @@
         <v>980</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>330</v>
       </c>
       <c r="AN18" t="n">
         <v>55</v>
@@ -3969,16 +3969,16 @@
         <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,10 +3990,10 @@
         <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY18" t="n">
         <v>7</v>
@@ -4002,29 +4002,29 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
         <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="n">
         <v>2.14</v>
@@ -4064,22 +4064,22 @@
         <v>3.6</v>
       </c>
       <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -4088,13 +4088,13 @@
         <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
         <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
@@ -4103,7 +4103,7 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
         <v>1.87</v>
@@ -4163,7 +4163,7 @@
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.8</v>
@@ -4172,7 +4172,7 @@
         <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AX19" t="n">
         <v>7.6</v>
@@ -4196,29 +4196,29 @@
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.56</v>
+        <v>44</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BG19" t="n">
         <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G20" t="n">
         <v>1.41</v>
@@ -4261,19 +4261,19 @@
         <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
@@ -4282,25 +4282,25 @@
         <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.9</v>
       </c>
       <c r="S20" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
         <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X20" t="n">
         <v>980</v>
@@ -4357,13 +4357,13 @@
         <v>320</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>4.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
@@ -4375,16 +4375,16 @@
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
         <v>4.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ20" t="n">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BE20" t="n">
         <v>11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -4461,28 +4461,28 @@
         <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S21" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
         <v>1.57</v>
@@ -4494,7 +4494,7 @@
         <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X21" t="n">
         <v>80</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4637,76 +4637,76 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
         <v>6.2</v>
       </c>
-      <c r="I22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="X22" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA22" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC22" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10</v>
       </c>
       <c r="AD22" t="n">
         <v>23</v>
@@ -4715,7 +4715,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
@@ -4730,43 +4730,43 @@
         <v>16</v>
       </c>
       <c r="AK22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS22" t="n">
         <v>100</v>
       </c>
-      <c r="AN22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AT22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>22</v>
       </c>
-      <c r="AR22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>21</v>
-      </c>
       <c r="AW22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX22" t="n">
         <v>9.4</v>
@@ -4775,32 +4775,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BE22" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H23" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="I23" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.7</v>
       </c>
-      <c r="K23" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -4861,61 +4861,61 @@
         <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="S23" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="T23" t="n">
         <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y23" t="n">
         <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
@@ -4924,49 +4924,49 @@
         <v>110</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AP23" t="n">
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV23" t="n">
         <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
@@ -4975,26 +4975,26 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BC23" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BD23" t="n">
         <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="G24" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N24" t="n">
         <v>2.84</v>
       </c>
-      <c r="I24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="G25" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5237,55 +5237,55 @@
         <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S25" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V25" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X25" t="n">
         <v>30</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB25" t="n">
         <v>21</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>22</v>
       </c>
       <c r="AC25" t="n">
         <v>10.5</v>
@@ -5294,10 +5294,10 @@
         <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
         <v>13.5</v>
@@ -5306,22 +5306,22 @@
         <v>13</v>
       </c>
       <c r="AI25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL25" t="n">
         <v>26</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>27</v>
       </c>
       <c r="AM25" t="n">
         <v>38</v>
       </c>
       <c r="AN25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO25" t="n">
         <v>10.5</v>
@@ -5330,28 +5330,28 @@
         <v>28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV25" t="n">
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY25" t="n">
         <v>13</v>
@@ -5360,29 +5360,29 @@
         <v>12.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB25" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BC25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD25" t="n">
         <v>24</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>25</v>
       </c>
       <c r="BE25" t="n">
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5416,67 +5416,67 @@
         <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
         <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
         <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
         <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>10.5</v>
@@ -5488,13 +5488,13 @@
         <v>17</v>
       </c>
       <c r="AE26" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AF26" t="n">
         <v>17.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
@@ -5503,10 +5503,10 @@
         <v>160</v>
       </c>
       <c r="AJ26" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL26" t="n">
         <v>980</v>
@@ -5515,7 +5515,7 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
         <v>55</v>
@@ -5524,16 +5524,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
@@ -5551,13 +5551,13 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA26" t="n">
         <v>40</v>
       </c>
       <c r="BB26" t="n">
-        <v>28</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
         <v>21</v>
@@ -5566,17 +5566,17 @@
         <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
         <v>34</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G27" t="n">
         <v>2.86</v>
@@ -5616,46 +5616,46 @@
         <v>3.35</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="L27" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N27" t="n">
         <v>2.32</v>
       </c>
       <c r="O27" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="P27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
         <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
         <v>1.54</v>
@@ -5664,10 +5664,10 @@
         <v>7</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
         <v>70</v>
@@ -5676,7 +5676,7 @@
         <v>7</v>
       </c>
       <c r="AC27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD27" t="n">
         <v>17.5</v>
@@ -5685,7 +5685,7 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
         <v>15</v>
@@ -5700,22 +5700,22 @@
         <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL27" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="n">
         <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AO27" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>7.6</v>
@@ -5724,7 +5724,7 @@
         <v>17.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AT27" t="n">
         <v>6.2</v>
@@ -5733,7 +5733,7 @@
         <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW27" t="n">
         <v>50</v>
@@ -5742,7 +5742,7 @@
         <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5751,26 +5751,26 @@
         <v>40</v>
       </c>
       <c r="BB27" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BC27" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD27" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE27" t="n">
         <v>110</v>
       </c>
       <c r="BF27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG27" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>4.3</v>
@@ -5819,28 +5819,28 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M28" t="n">
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.58</v>
       </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T28" t="n">
         <v>2.26</v>
@@ -5852,7 +5852,7 @@
         <v>1.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS28" t="n">
         <v>10.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -5995,73 +5995,73 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.35</v>
       </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="V29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W29" t="n">
         <v>3.35</v>
       </c>
       <c r="X29" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Y29" t="n">
         <v>980</v>
       </c>
       <c r="Z29" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
         <v>23</v>
@@ -6073,16 +6073,16 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AH29" t="n">
         <v>980</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ29" t="n">
         <v>21</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,28 +6106,28 @@
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS29" t="n">
         <v>4.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
@@ -6136,7 +6136,7 @@
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
         <v>5.6</v>
@@ -6145,20 +6145,20 @@
         <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -6189,64 +6189,64 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G30" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I30" t="n">
         <v>8.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
         <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
         <v>1.72</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6255,104 +6255,104 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.75</v>
+        <v>1.22</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.9</v>
+        <v>1.29</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.8</v>
+        <v>1.29</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>7.2</v>
+        <v>1.29</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.800000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.9</v>
+        <v>1.23</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.55</v>
+        <v>1.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>1.22</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.1</v>
+        <v>1.17</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.4</v>
+        <v>1.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -6383,61 +6383,61 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="G31" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="H31" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
         <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
         <v>1.3</v>
       </c>
       <c r="P31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.89</v>
-      </c>
       <c r="X31" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
         <v>16</v>
@@ -6446,85 +6446,85 @@
         <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE31" t="n">
         <v>55</v>
       </c>
       <c r="AF31" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
         <v>18.5</v>
       </c>
       <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO31" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
       </c>
       <c r="AP31" t="n">
         <v>14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -6533,20 +6533,20 @@
         <v>18.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BF31" t="n">
         <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -6586,43 +6586,43 @@
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>2.88</v>
       </c>
       <c r="K32" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L32" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="M32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N32" t="n">
         <v>2.28</v>
       </c>
       <c r="O32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="P32" t="n">
         <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R32" t="n">
         <v>1.13</v>
       </c>
       <c r="S32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="T32" t="n">
         <v>2.42</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V32" t="n">
         <v>1.47</v>
@@ -6634,16 +6634,16 @@
         <v>7.2</v>
       </c>
       <c r="Y32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB32" t="n">
         <v>7.6</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>7.8</v>
       </c>
       <c r="AC32" t="n">
         <v>7</v>
@@ -6667,7 +6667,7 @@
         <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AK32" t="n">
         <v>60</v>
@@ -6691,19 +6691,19 @@
         <v>6.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS32" t="n">
         <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
         <v>46</v>
@@ -6721,16 +6721,16 @@
         <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BC32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF32" t="n">
         <v>32</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -6774,37 +6774,37 @@
         <v>4.1</v>
       </c>
       <c r="G33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H33" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.59</v>
       </c>
       <c r="M33" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P33" t="n">
         <v>1.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R33" t="n">
         <v>1.19</v>
@@ -6819,10 +6819,10 @@
         <v>1.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
         <v>9</v>
@@ -6888,7 +6888,7 @@
         <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -6900,7 +6900,7 @@
         <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX33" t="n">
         <v>22</v>
@@ -6909,10 +6909,10 @@
         <v>16.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA33" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB33" t="n">
         <v>38</v>
@@ -6930,11 +6930,11 @@
         <v>40</v>
       </c>
       <c r="BG33" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -6965,58 +6965,58 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G34" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H34" t="n">
         <v>2.82</v>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R34" t="n">
         <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U34" t="n">
         <v>2.12</v>
       </c>
       <c r="V34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X34" t="n">
         <v>15</v>
@@ -7085,7 +7085,7 @@
         <v>4.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="G2" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
         <v>500</v>
@@ -847,7 +847,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="AK2" t="n">
         <v>65</v>
@@ -859,46 +859,46 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>3.8</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
         <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
         <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>5</v>
@@ -907,20 +907,20 @@
         <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
         <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>7.2</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I3" t="n">
         <v>1.57</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -975,13 +975,13 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
         <v>1.92</v>
@@ -990,22 +990,22 @@
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="W3" t="n">
         <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
         <v>7.8</v>
@@ -1017,10 +1017,10 @@
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
@@ -1029,22 +1029,22 @@
         <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="AG3" t="n">
         <v>48</v>
       </c>
       <c r="AH3" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AK3" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AL3" t="n">
         <v>520</v>
@@ -1053,13 +1053,13 @@
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.8</v>
@@ -1068,7 +1068,7 @@
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1095,26 +1095,26 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L4" t="n">
         <v>1.38</v>
       </c>
-      <c r="H4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.39</v>
-      </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
         <v>4</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>100</v>
       </c>
       <c r="Z4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AB4" t="n">
         <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL4" t="n">
         <v>50</v>
       </c>
-      <c r="AE4" t="n">
-        <v>420</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AN4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>490</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BA4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB4" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1369,34 +1369,34 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>210</v>
@@ -1405,19 +1405,19 @@
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AE5" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1426,13 +1426,13 @@
         <v>130</v>
       </c>
       <c r="AI5" t="n">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
         <v>80</v>
@@ -1441,19 +1441,19 @@
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1468,10 +1468,10 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1563,28 +1563,28 @@
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1605,7 +1605,7 @@
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
         <v>170</v>
@@ -1620,7 +1620,7 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="AJ6" t="n">
         <v>500</v>
@@ -1650,7 +1650,7 @@
         <v>16.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1659,10 +1659,10 @@
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX6" t="n">
         <v>16.5</v>
@@ -1674,19 +1674,19 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4.2</v>
@@ -1751,16 +1751,16 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.35</v>
@@ -1769,16 +1769,16 @@
         <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1796,7 +1796,7 @@
         <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
@@ -1805,7 +1805,7 @@
         <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AG7" t="n">
         <v>40</v>
@@ -1841,25 +1841,25 @@
         <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AY7" t="n">
         <v>6.2</v>
@@ -1868,7 +1868,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1877,20 +1877,20 @@
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.7</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I8" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>36</v>
@@ -1987,13 +1987,13 @@
         <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
         <v>60</v>
@@ -2002,46 +2002,46 @@
         <v>70</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AK8" t="n">
         <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AP8" t="n">
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7.8</v>
@@ -2050,10 +2050,10 @@
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2062,29 +2062,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
         <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="I9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
@@ -2133,7 +2133,7 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2145,40 +2145,40 @@
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
         <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
         <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB9" t="n">
         <v>26</v>
@@ -2190,13 +2190,13 @@
         <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2205,34 +2205,34 @@
         <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
         <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
         <v>55</v>
       </c>
       <c r="AN9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
         <v>24</v>
@@ -2247,38 +2247,38 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BC9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2309,100 +2309,100 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.45</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL10" t="n">
         <v>110</v>
@@ -2411,68 +2411,68 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX10" t="n">
         <v>9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BE10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF10" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G11" t="n">
         <v>4.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -2527,16 +2527,16 @@
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -2545,13 +2545,13 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W11" t="n">
         <v>1.3</v>
@@ -2566,13 +2566,13 @@
         <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2584,7 +2584,7 @@
         <v>75</v>
       </c>
       <c r="AG11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH11" t="n">
         <v>60</v>
@@ -2596,7 +2596,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AL11" t="n">
         <v>400</v>
@@ -2608,19 +2608,19 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -2635,7 +2635,7 @@
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
         <v>16</v>
@@ -2644,29 +2644,29 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2736,7 +2736,7 @@
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
         <v>1.71</v>
@@ -2748,49 +2748,49 @@
         <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y12" t="n">
         <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
         <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
         <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>50</v>
@@ -2799,10 +2799,10 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO12" t="n">
         <v>30</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>12.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.6</v>
       </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
         <v>4.4</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.6</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2963,19 +2963,19 @@
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
         <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3032,29 +3032,29 @@
         <v>11</v>
       </c>
       <c r="BA13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD13" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3127,70 +3127,70 @@
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>42</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>42</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>55</v>
-      </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
         <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -3202,7 +3202,7 @@
         <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3226,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3241,14 +3241,14 @@
         <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
         <v>19</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I15" t="n">
         <v>2.28</v>
@@ -3297,79 +3297,79 @@
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
         <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
         <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>70</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
         <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="AK15" t="n">
         <v>210</v>
@@ -3384,65 +3384,65 @@
         <v>980</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3485,10 @@
         <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -3512,7 +3512,7 @@
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
         <v>1.98</v>
@@ -3530,7 +3530,7 @@
         <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
         <v>42</v>
@@ -3542,13 +3542,13 @@
         <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
         <v>260</v>
@@ -3566,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
         <v>44</v>
@@ -3575,7 +3575,7 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
@@ -3590,7 +3590,7 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -3626,17 +3626,17 @@
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF16" t="n">
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
         <v>2.54</v>
@@ -3682,7 +3682,7 @@
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
@@ -3703,7 +3703,7 @@
         <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
@@ -3721,7 +3721,7 @@
         <v>1.65</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
@@ -3757,7 +3757,7 @@
         <v>40</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
         <v>28</v>
@@ -3784,13 +3784,13 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3814,13 +3814,13 @@
         <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
         <v>16.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
         <v>2.78</v>
@@ -3870,43 +3870,43 @@
         <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
         <v>1.54</v>
@@ -3918,7 +3918,7 @@
         <v>75</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>980</v>
@@ -3927,10 +3927,10 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>32</v>
@@ -3945,7 +3945,7 @@
         <v>36</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
         <v>980</v>
@@ -3957,10 +3957,10 @@
         <v>980</v>
       </c>
       <c r="AL18" t="n">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AM18" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>55</v>
@@ -3972,59 +3972,59 @@
         <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD18" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18</v>
       </c>
       <c r="BE18" t="n">
         <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>2.06</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
         <v>3.75</v>
@@ -4073,46 +4073,46 @@
         <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.32</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.34</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
       </c>
       <c r="Y19" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="Z19" t="n">
         <v>980</v>
@@ -4121,13 +4121,13 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>980</v>
+        <v>180</v>
       </c>
       <c r="AC19" t="n">
         <v>14</v>
       </c>
       <c r="AD19" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AE19" t="n">
         <v>980</v>
@@ -4163,62 +4163,62 @@
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.58</v>
+        <v>5.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV19" t="n">
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.05</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>7.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ19" t="n">
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE19" t="n">
         <v>44</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
         <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4258,13 +4258,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
         <v>5.2</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
@@ -4303,7 +4303,7 @@
         <v>3.4</v>
       </c>
       <c r="X20" t="n">
-        <v>980</v>
+        <v>95</v>
       </c>
       <c r="Y20" t="n">
         <v>980</v>
@@ -4327,7 +4327,7 @@
         <v>510</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AG20" t="n">
         <v>500</v>
@@ -4339,7 +4339,7 @@
         <v>400</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
         <v>500</v>
@@ -4357,62 +4357,62 @@
         <v>320</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
         <v>6.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.86</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -4467,19 +4467,19 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
         <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q21" t="n">
         <v>1.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S21" t="n">
         <v>2.36</v>
@@ -4488,7 +4488,7 @@
         <v>1.57</v>
       </c>
       <c r="U21" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V21" t="n">
         <v>1.3</v>
@@ -4542,25 +4542,25 @@
         <v>980</v>
       </c>
       <c r="AM21" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
         <v>240</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4584,7 +4584,7 @@
         <v>8.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
         <v>7.2</v>
@@ -4596,17 +4596,17 @@
         <v>13</v>
       </c>
       <c r="BE21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
         <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4637,85 +4637,85 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="G22" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
@@ -4727,49 +4727,49 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AO22" t="n">
         <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AS22" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9.6</v>
@@ -4778,29 +4778,29 @@
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
         <v>75</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4831,34 +4831,34 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J23" t="n">
         <v>4.7</v>
       </c>
-      <c r="G23" t="n">
+      <c r="K23" t="n">
         <v>4.8</v>
       </c>
-      <c r="H23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P23" t="n">
         <v>2.86</v>
@@ -4867,22 +4867,22 @@
         <v>1.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S23" t="n">
         <v>2.32</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U23" t="n">
         <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
         <v>30</v>
@@ -4891,10 +4891,10 @@
         <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA23" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
         <v>26</v>
@@ -4906,16 +4906,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
@@ -4924,31 +4924,31 @@
         <v>110</v>
       </c>
       <c r="AK23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM23" t="n">
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP23" t="n">
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
         <v>25</v>
@@ -4960,13 +4960,13 @@
         <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
@@ -4975,26 +4975,26 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BC23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD23" t="n">
         <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5031,164 +5031,164 @@
         <v>2.94</v>
       </c>
       <c r="H24" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.51</v>
+        <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.58</v>
+        <v>17.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.52</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.47</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.56</v>
+        <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.62</v>
+        <v>10</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.61</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.56</v>
+        <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.59</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.62</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.62</v>
+        <v>9.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.64</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.64</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.64</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G25" t="n">
         <v>2.78</v>
       </c>
-      <c r="G25" t="n">
-        <v>2.82</v>
-      </c>
       <c r="H25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5237,52 +5237,52 @@
         <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W25" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
         <v>23</v>
       </c>
       <c r="AA25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB25" t="n">
         <v>21</v>
@@ -5291,19 +5291,19 @@
         <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI25" t="n">
         <v>24</v>
@@ -5321,52 +5321,52 @@
         <v>38</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>10.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT25" t="n">
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY25" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
         <v>23</v>
       </c>
       <c r="BB25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD25" t="n">
         <v>24</v>
@@ -5375,14 +5375,14 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5413,100 +5413,100 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G26" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
         <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC26" t="n">
         <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>980</v>
       </c>
       <c r="AF26" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AI26" t="n">
         <v>160</v>
       </c>
       <c r="AJ26" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AK26" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="n">
         <v>980</v>
@@ -5515,68 +5515,68 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AT26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE26" t="n">
         <v>11</v>
       </c>
-      <c r="AR26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5619,40 +5619,40 @@
         <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K27" t="n">
         <v>2.94</v>
       </c>
       <c r="L27" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
         <v>1.18</v>
       </c>
       <c r="N27" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5661,13 +5661,13 @@
         <v>1.54</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
         <v>70</v>
@@ -5685,7 +5685,7 @@
         <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG27" t="n">
         <v>15</v>
@@ -5700,7 +5700,7 @@
         <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AL27" t="n">
         <v>260</v>
@@ -5709,16 +5709,16 @@
         <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR27" t="n">
         <v>17.5</v>
@@ -5730,7 +5730,7 @@
         <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV27" t="n">
         <v>15.5</v>
@@ -5742,16 +5742,16 @@
         <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BB27" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BC27" t="n">
         <v>40</v>
@@ -5763,14 +5763,14 @@
         <v>110</v>
       </c>
       <c r="BF27" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BG27" t="n">
         <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
         <v>4.3</v>
@@ -5828,13 +5828,13 @@
         <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P28" t="n">
         <v>1.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
@@ -5843,16 +5843,16 @@
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V28" t="n">
         <v>1.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X28" t="n">
         <v>10</v>
@@ -5891,13 +5891,13 @@
         <v>290</v>
       </c>
       <c r="AJ28" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AM28" t="n">
         <v>500</v>
@@ -5915,7 +5915,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AS28" t="n">
         <v>10.5</v>
@@ -5930,7 +5930,7 @@
         <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AX28" t="n">
         <v>9.800000000000001</v>
@@ -5942,7 +5942,7 @@
         <v>23</v>
       </c>
       <c r="BA28" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BB28" t="n">
         <v>25</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G29" t="n">
         <v>1.41</v>
@@ -6007,46 +6007,46 @@
         <v>12.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
         <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R29" t="n">
         <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V29" t="n">
         <v>1.09</v>
       </c>
       <c r="W29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X29" t="n">
         <v>40</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AC29" t="n">
         <v>23</v>
@@ -6073,10 +6073,10 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AH29" t="n">
         <v>980</v>
@@ -6097,19 +6097,19 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
         <v>19</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
         <v>4.2</v>
@@ -6118,25 +6118,25 @@
         <v>6</v>
       </c>
       <c r="AU29" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AX29" t="n">
         <v>6.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BB29" t="n">
         <v>5.6</v>
@@ -6145,20 +6145,20 @@
         <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
         <v>6.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="H30" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
@@ -6219,34 +6219,34 @@
         <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
         <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6255,104 +6255,104 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.29</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.22</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.18</v>
+        <v>5.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.29</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.29</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.23</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.2</v>
+        <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.22</v>
+        <v>19.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.17</v>
+        <v>5.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>
@@ -6425,10 +6425,10 @@
         <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
         <v>1.29</v>
@@ -6446,13 +6446,13 @@
         <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
         <v>17.5</v>
@@ -6461,13 +6461,13 @@
         <v>55</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
@@ -6482,25 +6482,25 @@
         <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO31" t="n">
         <v>55</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>14.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS31" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="AT31" t="n">
         <v>9</v>
@@ -6515,38 +6515,38 @@
         <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
       </c>
       <c r="BC31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BF31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -6577,49 +6577,49 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I32" t="n">
         <v>3.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K32" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N32" t="n">
         <v>2.28</v>
       </c>
       <c r="O32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
         <v>1.13</v>
       </c>
       <c r="S32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U32" t="n">
         <v>1.64</v>
@@ -6628,25 +6628,25 @@
         <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y32" t="n">
         <v>7.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA32" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AB32" t="n">
         <v>7.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
@@ -6655,28 +6655,28 @@
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AG32" t="n">
         <v>16</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AI32" t="n">
         <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AK32" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="AL32" t="n">
         <v>120</v>
       </c>
       <c r="AM32" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6688,7 +6688,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR32" t="n">
         <v>15.5</v>
@@ -6697,22 +6697,22 @@
         <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AX32" t="n">
         <v>15</v>
       </c>
       <c r="AY32" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ32" t="n">
         <v>25</v>
@@ -6721,26 +6721,26 @@
         <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BC32" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG32" t="n">
         <v>34</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
         <v>1.59</v>
       </c>
       <c r="M33" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N33" t="n">
         <v>2.7</v>
@@ -6816,7 +6816,7 @@
         <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V33" t="n">
         <v>1.85</v>
@@ -6873,13 +6873,13 @@
         <v>240</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO33" t="n">
         <v>30</v>
       </c>
       <c r="AP33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
         <v>6</v>
@@ -6915,10 +6915,10 @@
         <v>50</v>
       </c>
       <c r="BB33" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BC33" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BD33" t="n">
         <v>40</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -6974,13 +6974,13 @@
         <v>2.82</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J34" t="n">
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.44</v>
@@ -7013,7 +7013,7 @@
         <v>2.12</v>
       </c>
       <c r="V34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W34" t="n">
         <v>1.55</v>
@@ -7025,7 +7025,7 @@
         <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
@@ -7043,13 +7043,13 @@
         <v>980</v>
       </c>
       <c r="AF34" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT34" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AY34" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -757,55 +757,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
         <v>10.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
         <v>4.8</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY2" t="n">
         <v>5.7</v>
       </c>
-      <c r="AV2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BD2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I3" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.42</v>
@@ -984,7 +984,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -993,34 +993,34 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="W3" t="n">
         <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Z3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
@@ -1029,92 +1029,92 @@
         <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>420</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AL3" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="AM3" t="n">
         <v>700</v>
       </c>
       <c r="AN3" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU3" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K4" t="n">
         <v>5.5</v>
       </c>
-      <c r="K4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z4" t="n">
         <v>100</v>
       </c>
-      <c r="Z4" t="n">
-        <v>140</v>
-      </c>
       <c r="AA4" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AE4" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="AF4" t="n">
         <v>7.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AJ4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
         <v>280</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>490</v>
+        <v>370</v>
       </c>
       <c r="AP4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR4" t="n">
         <v>16</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14</v>
-      </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BA4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC4" t="n">
         <v>14.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
       </c>
       <c r="BD4" t="n">
         <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>4.3</v>
@@ -1390,16 +1390,16 @@
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="X5" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
@@ -1411,7 +1411,7 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1423,19 +1423,19 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
         <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
@@ -1453,10 +1453,10 @@
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT5" t="n">
         <v>8.199999999999999</v>
@@ -1468,7 +1468,7 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1480,7 +1480,7 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
         <v>13.5</v>
@@ -1492,7 +1492,7 @@
         <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
         <v>6.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1560,46 +1560,46 @@
         <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
         <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
         <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1608,28 +1608,28 @@
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AL6" t="n">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1638,7 +1638,7 @@
         <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AP6" t="n">
         <v>13.5</v>
@@ -1647,7 +1647,7 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
         <v>21</v>
@@ -1674,7 +1674,7 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB6" t="n">
         <v>16.5</v>
@@ -1692,11 +1692,11 @@
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G7" t="n">
         <v>1.69</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.72</v>
       </c>
       <c r="H7" t="n">
         <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1793,7 +1793,7 @@
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1805,7 +1805,7 @@
         <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AG7" t="n">
         <v>40</v>
@@ -1838,37 +1838,37 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1877,20 +1877,20 @@
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -1954,10 +1954,10 @@
         <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
         <v>2.96</v>
@@ -1969,10 +1969,10 @@
         <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -2002,7 +2002,7 @@
         <v>70</v>
       </c>
       <c r="AG8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2023,7 +2023,7 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
         <v>14.5</v>
@@ -2056,7 +2056,7 @@
         <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>9.800000000000001</v>
@@ -2068,23 +2068,23 @@
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
         <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BF8" t="n">
         <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G9" t="n">
         <v>4.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.9</v>
       </c>
       <c r="H9" t="n">
         <v>1.76</v>
@@ -2127,10 +2127,10 @@
         <v>1.77</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.28</v>
@@ -2145,28 +2145,28 @@
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V9" t="n">
         <v>2.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
         <v>28</v>
@@ -2175,10 +2175,10 @@
         <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB9" t="n">
         <v>26</v>
@@ -2187,7 +2187,7 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE9" t="n">
         <v>15.5</v>
@@ -2208,10 +2208,10 @@
         <v>110</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
         <v>55</v>
@@ -2226,10 +2226,10 @@
         <v>27</v>
       </c>
       <c r="AQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>13</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
         <v>18.5</v>
@@ -2238,10 +2238,10 @@
         <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.41</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
       </c>
       <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11</v>
       </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>700</v>
+        <v>310</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>8.6</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.3</v>
@@ -2515,10 +2515,10 @@
         <v>2.42</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
         <v>1.64</v>
@@ -2545,7 +2545,7 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
         <v>1.69</v>
@@ -2620,10 +2620,10 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -2647,16 +2647,16 @@
         <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
         <v>9.199999999999999</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2727,28 +2727,28 @@
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
         <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
         <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V12" t="n">
         <v>1.52</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
         <v>17.5</v>
@@ -2799,7 +2799,7 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>30</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -2915,40 +2915,40 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,25 +2957,25 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>500</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>980</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
         <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3020,7 +3020,7 @@
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3032,7 +3032,7 @@
         <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
         <v>7</v>
@@ -3041,7 +3041,7 @@
         <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
@@ -3050,11 +3050,11 @@
         <v>9.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3109,22 +3109,22 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.69</v>
@@ -3133,25 +3133,25 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
@@ -3160,10 +3160,10 @@
         <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
@@ -3172,10 +3172,10 @@
         <v>17</v>
       </c>
       <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>40</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>42</v>
       </c>
       <c r="AK14" t="n">
         <v>30</v>
@@ -3187,49 +3187,49 @@
         <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT14" t="n">
         <v>10</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3241,14 +3241,14 @@
         <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3309,40 +3309,40 @@
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
         <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
         <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
         <v>17</v>
@@ -3354,10 +3354,10 @@
         <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="n">
         <v>15.5</v>
@@ -3369,10 +3369,10 @@
         <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>230</v>
+        <v>440</v>
       </c>
       <c r="AK15" t="n">
-        <v>210</v>
+        <v>980</v>
       </c>
       <c r="AL15" t="n">
         <v>980</v>
@@ -3381,10 +3381,10 @@
         <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>16.5</v>
@@ -3396,13 +3396,13 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
         <v>9.6</v>
@@ -3423,7 +3423,7 @@
         <v>16.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BC15" t="n">
         <v>16.5</v>
@@ -3432,17 +3432,17 @@
         <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I16" t="n">
         <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -3503,7 +3503,7 @@
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
@@ -3512,7 +3512,7 @@
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T16" t="n">
         <v>1.98</v>
@@ -3524,13 +3524,13 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
         <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
         <v>42</v>
@@ -3542,7 +3542,7 @@
         <v>8</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>22</v>
@@ -3578,19 +3578,19 @@
         <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>6.6</v>
@@ -3602,7 +3602,7 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3614,10 +3614,10 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC16" t="n">
         <v>17.5</v>
@@ -3626,17 +3626,17 @@
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -3691,22 +3691,22 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3718,7 +3718,7 @@
         <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
@@ -3730,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
@@ -3754,7 +3754,7 @@
         <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
         <v>36</v>
@@ -3769,10 +3769,10 @@
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -3793,7 +3793,7 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
         <v>26</v>
@@ -3814,7 +3814,7 @@
         <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>30</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G18" t="n">
         <v>2.78</v>
@@ -3876,25 +3876,25 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
         <v>1.47</v>
@@ -3903,13 +3903,13 @@
         <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>1.56</v>
@@ -3918,7 +3918,7 @@
         <v>75</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="Z18" t="n">
         <v>980</v>
@@ -3954,7 +3954,7 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>130</v>
@@ -3969,7 +3969,7 @@
         <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.2</v>
@@ -3981,22 +3981,22 @@
         <v>16.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
@@ -4005,26 +4005,26 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
         <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.36</v>
@@ -4091,28 +4091,28 @@
         <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
         <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
       </c>
       <c r="Y19" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="Z19" t="n">
         <v>980</v>
@@ -4121,7 +4121,7 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AC19" t="n">
         <v>14</v>
@@ -4163,40 +4163,40 @@
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.8</v>
+        <v>2.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
         <v>7.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB19" t="n">
         <v>11.5</v>
@@ -4205,20 +4205,20 @@
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
         <v>44</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4279,22 +4279,22 @@
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
         <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
@@ -4306,10 +4306,10 @@
         <v>95</v>
       </c>
       <c r="Y20" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -4318,7 +4318,7 @@
         <v>980</v>
       </c>
       <c r="AC20" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="AD20" t="n">
         <v>980</v>
@@ -4327,13 +4327,13 @@
         <v>510</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG20" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AI20" t="n">
         <v>400</v>
@@ -4372,7 +4372,7 @@
         <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
         <v>12.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY20" t="n">
         <v>6.2</v>
@@ -4396,23 +4396,23 @@
         <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>1.93</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.28</v>
@@ -4470,13 +4470,13 @@
         <v>5.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
         <v>2.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R21" t="n">
         <v>1.66</v>
@@ -4485,10 +4485,10 @@
         <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V21" t="n">
         <v>1.3</v>
@@ -4503,7 +4503,7 @@
         <v>65</v>
       </c>
       <c r="Z21" t="n">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
@@ -4548,19 +4548,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4572,7 +4572,7 @@
         <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
@@ -4584,10 +4584,10 @@
         <v>8.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC21" t="n">
         <v>9</v>
@@ -4596,17 +4596,17 @@
         <v>13</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
         <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G22" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.42</v>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>1.32</v>
@@ -4673,61 +4673,61 @@
         <v>1.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
         <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
         <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
         <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4739,37 +4739,37 @@
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR22" t="n">
         <v>36</v>
       </c>
       <c r="AS22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>65</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
         <v>9.6</v>
@@ -4793,14 +4793,14 @@
         <v>100</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.28</v>
@@ -4861,7 +4861,7 @@
         <v>1.17</v>
       </c>
       <c r="P23" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q23" t="n">
         <v>1.52</v>
@@ -4870,7 +4870,7 @@
         <v>1.73</v>
       </c>
       <c r="S23" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
         <v>1.58</v>
@@ -4879,10 +4879,10 @@
         <v>2.68</v>
       </c>
       <c r="V23" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
         <v>30</v>
@@ -4906,7 +4906,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
         <v>44</v>
@@ -4915,7 +4915,7 @@
         <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
@@ -4933,10 +4933,10 @@
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP23" t="n">
         <v>29</v>
@@ -4972,13 +4972,13 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB23" t="n">
         <v>95</v>
       </c>
       <c r="BC23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD23" t="n">
         <v>38</v>
@@ -4987,14 +4987,14 @@
         <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG23" t="n">
         <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="H24" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>2.92</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L24" t="n">
         <v>1.56</v>
@@ -5049,16 +5049,16 @@
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R24" t="n">
         <v>1.21</v>
@@ -5070,58 +5070,58 @@
         <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="X24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y24" t="n">
-        <v>9.4</v>
-      </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>190</v>
       </c>
       <c r="AJ24" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AL24" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5130,65 +5130,65 @@
         <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AP24" t="n">
         <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY24" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BD24" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF24" t="n">
         <v>11</v>
       </c>
-      <c r="BF24" t="n">
-        <v>10</v>
-      </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G25" t="n">
         <v>2.76</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.78</v>
       </c>
       <c r="H25" t="n">
         <v>2.54</v>
@@ -5255,16 +5255,16 @@
         <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T25" t="n">
         <v>1.42</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V25" t="n">
         <v>1.64</v>
@@ -5276,7 +5276,7 @@
         <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
         <v>23</v>
@@ -5300,7 +5300,7 @@
         <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
         <v>12.5</v>
@@ -5315,13 +5315,13 @@
         <v>24</v>
       </c>
       <c r="AL25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM25" t="n">
         <v>38</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO25" t="n">
         <v>10.5</v>
@@ -5348,13 +5348,13 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX25" t="n">
         <v>24</v>
       </c>
       <c r="AY25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
@@ -5375,14 +5375,14 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5413,127 +5413,127 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G26" t="n">
         <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.39</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.38</v>
       </c>
       <c r="W26" t="n">
         <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z26" t="n">
         <v>48</v>
       </c>
       <c r="AA26" t="n">
-        <v>900</v>
+        <v>340</v>
       </c>
       <c r="AB26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD26" t="n">
         <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>980</v>
+        <v>190</v>
       </c>
       <c r="AF26" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AJ26" t="n">
         <v>95</v>
       </c>
       <c r="AK26" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AL26" t="n">
-        <v>980</v>
+        <v>200</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
         <v>7.4</v>
@@ -5551,32 +5551,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>10</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
         <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G27" t="n">
         <v>2.86</v>
@@ -5637,7 +5637,7 @@
         <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q27" t="n">
         <v>3.45</v>
@@ -5652,7 +5652,7 @@
         <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
         <v>1.41</v>
@@ -5742,7 +5742,7 @@
         <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>26</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5819,25 +5819,25 @@
         <v>3.35</v>
       </c>
       <c r="L28" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O28" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
@@ -5846,7 +5846,7 @@
         <v>2.24</v>
       </c>
       <c r="U28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
         <v>1.3</v>
@@ -5888,7 +5888,7 @@
         <v>110</v>
       </c>
       <c r="AI28" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
         <v>30</v>
@@ -5897,7 +5897,7 @@
         <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM28" t="n">
         <v>500</v>
@@ -5918,7 +5918,7 @@
         <v>24</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5927,7 +5927,7 @@
         <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA28" t="n">
         <v>29</v>
@@ -5954,17 +5954,17 @@
         <v>55</v>
       </c>
       <c r="BE28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG28" t="n">
         <v>11</v>
       </c>
-      <c r="BF28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5995,52 +5995,52 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G29" t="n">
         <v>1.41</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="I29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K29" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.75</v>
       </c>
-      <c r="O29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
         <v>1.09</v>
@@ -6052,7 +6052,7 @@
         <v>40</v>
       </c>
       <c r="Y29" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="Z29" t="n">
         <v>110</v>
@@ -6061,104 +6061,104 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD29" t="n">
         <v>980</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>980</v>
       </c>
       <c r="AI29" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AJ29" t="n">
         <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL29" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="AT29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX29" t="n">
         <v>6</v>
       </c>
-      <c r="AU29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
         <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -6189,79 +6189,79 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G30" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
         <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
@@ -6270,19 +6270,19 @@
         <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
         <v>55</v>
@@ -6291,7 +6291,7 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -6303,56 +6303,56 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
         <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC30" t="n">
         <v>19.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>
@@ -6416,7 +6416,7 @@
         <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
@@ -6425,7 +6425,7 @@
         <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
         <v>2.2</v>
@@ -6437,7 +6437,7 @@
         <v>2.02</v>
       </c>
       <c r="X31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y31" t="n">
         <v>16</v>
@@ -6449,7 +6449,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
         <v>8.199999999999999</v>
@@ -6461,7 +6461,7 @@
         <v>55</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG31" t="n">
         <v>10.5</v>
@@ -6491,13 +6491,13 @@
         <v>55</v>
       </c>
       <c r="AP31" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ31" t="n">
         <v>14.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS31" t="n">
         <v>46</v>
@@ -6512,16 +6512,16 @@
         <v>15.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
         <v>42</v>
@@ -6536,7 +6536,7 @@
         <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF31" t="n">
         <v>11.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -6583,13 +6583,13 @@
         <v>3.1</v>
       </c>
       <c r="H32" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K32" t="n">
         <v>2.94</v>
@@ -6601,7 +6601,7 @@
         <v>1.18</v>
       </c>
       <c r="N32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O32" t="n">
         <v>1.75</v>
@@ -6610,7 +6610,7 @@
         <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R32" t="n">
         <v>1.13</v>
@@ -6625,7 +6625,7 @@
         <v>1.64</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W32" t="n">
         <v>1.47</v>
@@ -6643,7 +6643,7 @@
         <v>400</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6655,22 +6655,22 @@
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AG32" t="n">
         <v>16</v>
       </c>
       <c r="AH32" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="n">
         <v>120</v>
       </c>
       <c r="AJ32" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AK32" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AL32" t="n">
         <v>120</v>
@@ -6697,7 +6697,7 @@
         <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
@@ -6706,13 +6706,13 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX32" t="n">
         <v>15</v>
       </c>
       <c r="AY32" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
         <v>25</v>
@@ -6721,26 +6721,26 @@
         <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BC32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>13.5</v>
+        <v>100</v>
       </c>
       <c r="BF32" t="n">
         <v>34</v>
       </c>
       <c r="BG32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>4.3</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I33" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="J33" t="n">
         <v>3.25</v>
@@ -6795,7 +6795,7 @@
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O33" t="n">
         <v>1.57</v>
@@ -6819,19 +6819,19 @@
         <v>1.73</v>
       </c>
       <c r="V33" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W33" t="n">
         <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y33" t="n">
         <v>6.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
         <v>30</v>
@@ -6840,7 +6840,7 @@
         <v>11</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
         <v>12</v>
@@ -6861,7 +6861,7 @@
         <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK33" t="n">
         <v>1000</v>
@@ -6882,19 +6882,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS33" t="n">
         <v>25</v>
       </c>
       <c r="AT33" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
@@ -6909,13 +6909,13 @@
         <v>16.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA33" t="n">
         <v>50</v>
       </c>
       <c r="BB33" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BC33" t="n">
         <v>55</v>
@@ -6924,17 +6924,17 @@
         <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG33" t="n">
         <v>25</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>2.68</v>
       </c>
       <c r="G34" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I34" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
         <v>1.44</v>
@@ -6998,13 +6998,13 @@
         <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R34" t="n">
         <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T34" t="n">
         <v>1.79</v>
@@ -7013,10 +7013,10 @@
         <v>2.12</v>
       </c>
       <c r="V34" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
         <v>15</v>
@@ -7064,7 +7064,7 @@
         <v>980</v>
       </c>
       <c r="AM34" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN34" t="n">
         <v>1000</v>
@@ -7073,16 +7073,16 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT34" t="n">
         <v>9.199999999999999</v>
@@ -7091,44 +7091,44 @@
         <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX34" t="n">
         <v>15.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC34" t="n">
         <v>4.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF34" t="n">
         <v>4.9</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -763,34 +763,34 @@
         <v>1.26</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
         <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.64</v>
@@ -799,13 +799,13 @@
         <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
         <v>4.8</v>
@@ -835,10 +835,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -850,7 +850,7 @@
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>500</v>
@@ -859,7 +859,7 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
         <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
         <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
         <v>6.6</v>
       </c>
-      <c r="G3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="H3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="I3" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -981,10 +981,10 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
@@ -993,128 +993,128 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB3" t="n">
         <v>22</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>42</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>290</v>
+      </c>
+      <c r="AL3" t="n">
         <v>90</v>
       </c>
-      <c r="AG3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>700</v>
-      </c>
       <c r="AM3" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AW3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AY3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF3" t="n">
         <v>16</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>120</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>760</v>
       </c>
       <c r="AB4" t="n">
         <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AE4" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
       </c>
       <c r="AL4" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW4" t="n">
         <v>15</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AX4" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G5" t="n">
         <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
         <v>7.2</v>
@@ -1363,22 +1363,22 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
         <v>1.85</v>
@@ -1387,13 +1387,13 @@
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
         <v>2.64</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y5" t="n">
         <v>38</v>
@@ -1411,13 +1411,13 @@
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1429,13 +1429,13 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>16.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
@@ -1444,16 +1444,16 @@
         <v>7.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
         <v>12.5</v>
@@ -1468,10 +1468,10 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
@@ -1483,13 +1483,13 @@
         <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BE5" t="n">
         <v>12</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1566,25 +1566,25 @@
         <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1593,13 +1593,13 @@
         <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1608,10 +1608,10 @@
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1635,10 +1635,10 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
         <v>13.5</v>
@@ -1680,23 +1680,23 @@
         <v>16.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
         <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
         <v>1.69</v>
@@ -1736,13 +1736,13 @@
         <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1751,7 +1751,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -1763,28 +1763,28 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
         <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>2.44</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="n">
         <v>980</v>
@@ -1793,43 +1793,43 @@
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AE7" t="n">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="AF7" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI7" t="n">
-        <v>700</v>
+        <v>330</v>
       </c>
       <c r="AJ7" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
@@ -1841,28 +1841,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.54</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>14.5</v>
@@ -1871,26 +1871,26 @@
         <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
         <v>2.26</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J8" t="n">
         <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
@@ -1951,10 +1951,10 @@
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
         <v>1.48</v>
@@ -1966,13 +1966,13 @@
         <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -1981,13 +1981,13 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
         <v>9.199999999999999</v>
@@ -1996,19 +1996,19 @@
         <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
         <v>290</v>
@@ -2017,31 +2017,31 @@
         <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO8" t="n">
         <v>14.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7.8</v>
@@ -2059,7 +2059,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>16.5</v>
@@ -2068,23 +2068,23 @@
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
         <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
         <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.4</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
         <v>2.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA9" t="n">
         <v>19</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH9" t="n">
         <v>15.5</v>
       </c>
-      <c r="AF9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15</v>
-      </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
         <v>110</v>
       </c>
       <c r="AK9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL9" t="n">
         <v>46</v>
       </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
       <c r="AM9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AY9" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>95</v>
       </c>
       <c r="BC9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF9" t="n">
         <v>38</v>
       </c>
-      <c r="BE9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>34</v>
-      </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
@@ -2336,13 +2336,13 @@
         <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
         <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
         <v>1.41</v>
@@ -2351,16 +2351,16 @@
         <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X10" t="n">
         <v>17</v>
@@ -2387,7 +2387,7 @@
         <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2405,7 +2405,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>980</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
@@ -2420,13 +2420,13 @@
         <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR10" t="n">
         <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
@@ -2438,7 +2438,7 @@
         <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AX10" t="n">
         <v>10.5</v>
@@ -2468,11 +2468,11 @@
         <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I11" t="n">
         <v>2.42</v>
@@ -2518,25 +2518,25 @@
         <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="R11" t="n">
         <v>1.17</v>
@@ -2557,13 +2557,13 @@
         <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="n">
         <v>7.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
         <v>85</v>
@@ -2587,7 +2587,7 @@
         <v>19</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AI11" t="n">
         <v>210</v>
@@ -2596,7 +2596,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>400</v>
@@ -2614,10 +2614,10 @@
         <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
         <v>28</v>
@@ -2626,13 +2626,13 @@
         <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AX11" t="n">
         <v>19</v>
@@ -2644,29 +2644,29 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>48</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC11" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE11" t="n">
         <v>10</v>
       </c>
-      <c r="BD11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.9</v>
@@ -2742,22 +2742,22 @@
         <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
         <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
@@ -2799,19 +2799,19 @@
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>16</v>
@@ -2823,44 +2823,44 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
         <v>21</v>
       </c>
       <c r="BF12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.35</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -2921,7 +2921,7 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
@@ -2930,25 +2930,25 @@
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
         <v>1.58</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,7 +2957,7 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
         <v>8.4</v>
@@ -2969,13 +2969,13 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
         <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2984,7 +2984,7 @@
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2993,7 +2993,7 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,7 +3005,7 @@
         <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
@@ -3014,13 +3014,13 @@
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3032,29 +3032,29 @@
         <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3118,7 +3118,7 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
@@ -3127,22 +3127,22 @@
         <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
         <v>21</v>
@@ -3160,10 +3160,10 @@
         <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
@@ -3175,22 +3175,22 @@
         <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
         <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
         <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -3220,35 +3220,35 @@
         <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BE14" t="n">
         <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
         <v>21</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3279,64 +3279,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
         <v>3.85</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
         <v>2.18</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
         <v>1.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
@@ -3345,10 +3345,10 @@
         <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>11.5</v>
@@ -3360,19 +3360,19 @@
         <v>170</v>
       </c>
       <c r="AG15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH15" t="n">
         <v>16.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="AJ15" t="n">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="AK15" t="n">
-        <v>980</v>
+        <v>210</v>
       </c>
       <c r="AL15" t="n">
         <v>980</v>
@@ -3381,13 +3381,13 @@
         <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>10.5</v>
@@ -3396,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AT15" t="n">
         <v>14.5</v>
@@ -3411,38 +3411,38 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AY15" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>16.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BG15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
         <v>5.1</v>
@@ -3488,7 +3488,7 @@
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -3503,7 +3503,7 @@
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
@@ -3548,7 +3548,7 @@
         <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
@@ -3602,7 +3602,7 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AX16" t="n">
         <v>8.800000000000001</v>
@@ -3626,17 +3626,17 @@
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
         <v>2.5</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I17" t="n">
         <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3697,19 +3697,19 @@
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
         <v>2.32</v>
@@ -3721,22 +3721,22 @@
         <v>1.66</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
         <v>14</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
         <v>12.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
@@ -3745,7 +3745,7 @@
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3754,7 +3754,7 @@
         <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
         <v>36</v>
@@ -3766,71 +3766,71 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV17" t="n">
         <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
         <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BF17" t="n">
         <v>16.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H18" t="n">
         <v>2.66</v>
@@ -3885,31 +3885,31 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W18" t="n">
         <v>1.56</v>
@@ -3975,13 +3975,13 @@
         <v>7.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS18" t="n">
         <v>16.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
         <v>7.4</v>
@@ -4005,13 +4005,13 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="BE18" t="n">
         <v>9.6</v>
@@ -4020,11 +4020,11 @@
         <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
         <v>14</v>
       </c>
       <c r="AD19" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
         <v>980</v>
@@ -4169,56 +4169,56 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="AT19" t="n">
         <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>7.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC19" t="n">
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF19" t="n">
         <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
@@ -4273,7 +4273,7 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
@@ -4285,7 +4285,7 @@
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="S20" t="n">
         <v>2.02</v>
@@ -4294,16 +4294,16 @@
         <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="X20" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
         <v>1000</v>
@@ -4315,22 +4315,22 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AC20" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AD20" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AE20" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
         <v>980</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>980</v>
@@ -4339,7 +4339,7 @@
         <v>400</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
         <v>500</v>
@@ -4351,68 +4351,68 @@
         <v>330</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AO20" t="n">
         <v>320</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>1.83</v>
       </c>
       <c r="G21" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H21" t="n">
         <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>4.2</v>
@@ -4467,7 +4467,7 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O21" t="n">
         <v>1.18</v>
@@ -4479,7 +4479,7 @@
         <v>1.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S21" t="n">
         <v>2.36</v>
@@ -4488,13 +4488,13 @@
         <v>1.58</v>
       </c>
       <c r="U21" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X21" t="n">
         <v>80</v>
@@ -4551,13 +4551,13 @@
         <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AS21" t="n">
         <v>9</v>
@@ -4566,25 +4566,25 @@
         <v>11.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
         <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
         <v>8.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB21" t="n">
         <v>11.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4643,97 +4643,97 @@
         <v>1.75</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
         <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA22" t="n">
         <v>150</v>
       </c>
       <c r="AB22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="n">
         <v>9.6</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
         <v>120</v>
@@ -4742,19 +4742,19 @@
         <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
@@ -4781,16 +4781,16 @@
         <v>70</v>
       </c>
       <c r="BB22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4831,73 +4831,73 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="J23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.6</v>
       </c>
-      <c r="K23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R23" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="T23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>13</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC23" t="n">
         <v>11</v>
@@ -4933,16 +4933,16 @@
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>12.5</v>
@@ -4951,7 +4951,7 @@
         <v>18</v>
       </c>
       <c r="AT23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU23" t="n">
         <v>10.5</v>
@@ -4963,38 +4963,38 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BC23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="I24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M24" t="n">
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
       </c>
       <c r="AI24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL24" t="n">
         <v>190</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>65</v>
-      </c>
       <c r="AM24" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN24" t="n">
         <v>1000</v>
       </c>
-      <c r="AN24" t="n">
-        <v>55</v>
-      </c>
       <c r="AO24" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV24" t="n">
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AX24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
       <c r="BA24" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
         <v>11</v>
       </c>
-      <c r="BC24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>13</v>
-      </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         <v>2.74</v>
       </c>
       <c r="G25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I25" t="n">
         <v>2.54</v>
       </c>
-      <c r="I25" t="n">
-        <v>2.56</v>
-      </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.24</v>
@@ -5255,16 +5255,16 @@
         <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S25" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T25" t="n">
         <v>1.42</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V25" t="n">
         <v>1.64</v>
@@ -5273,13 +5273,13 @@
         <v>1.56</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
         <v>40</v>
@@ -5294,7 +5294,7 @@
         <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
@@ -5312,7 +5312,7 @@
         <v>44</v>
       </c>
       <c r="AK25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -5321,10 +5321,10 @@
         <v>38</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP25" t="n">
         <v>30</v>
@@ -5375,14 +5375,14 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5416,16 +5416,16 @@
         <v>2.24</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
         <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
         <v>3.7</v>
@@ -5446,22 +5446,22 @@
         <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
         <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
         <v>1.74</v>
@@ -5470,13 +5470,13 @@
         <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AA26" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
         <v>10.5</v>
@@ -5497,13 +5497,13 @@
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AI26" t="n">
         <v>980</v>
       </c>
       <c r="AJ26" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
         <v>65</v>
@@ -5515,10 +5515,10 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AO26" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP26" t="n">
         <v>13</v>
@@ -5527,22 +5527,22 @@
         <v>12</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
@@ -5554,29 +5554,29 @@
         <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BE26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG26" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
         <v>2.86</v>
@@ -5622,7 +5622,7 @@
         <v>2.86</v>
       </c>
       <c r="K27" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.73</v>
@@ -5637,7 +5637,7 @@
         <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q27" t="n">
         <v>3.45</v>
@@ -5661,7 +5661,7 @@
         <v>1.54</v>
       </c>
       <c r="X27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y27" t="n">
         <v>8.199999999999999</v>
@@ -5703,7 +5703,7 @@
         <v>60</v>
       </c>
       <c r="AL27" t="n">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="AM27" t="n">
         <v>500</v>
@@ -5712,10 +5712,10 @@
         <v>80</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
         <v>7.4</v>
@@ -5742,7 +5742,7 @@
         <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ27" t="n">
         <v>26</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>4.3</v>
@@ -5828,13 +5828,13 @@
         <v>2.64</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P28" t="n">
         <v>1.54</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R28" t="n">
         <v>1.19</v>
@@ -5843,10 +5843,10 @@
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
         <v>1.3</v>
@@ -5855,13 +5855,13 @@
         <v>1.83</v>
       </c>
       <c r="X28" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
         <v>10.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5870,22 +5870,22 @@
         <v>6.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF28" t="n">
         <v>11.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="n">
         <v>500</v>
@@ -5894,10 +5894,10 @@
         <v>30</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL28" t="n">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AM28" t="n">
         <v>500</v>
@@ -5909,16 +5909,16 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
       </c>
       <c r="AS28" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5927,22 +5927,22 @@
         <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA28" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
         <v>25</v>
@@ -5954,17 +5954,17 @@
         <v>55</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BG28" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H29" t="n">
         <v>11.5</v>
@@ -6007,10 +6007,10 @@
         <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.41</v>
@@ -6031,22 +6031,22 @@
         <v>2.06</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
         <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V29" t="n">
         <v>1.09</v>
       </c>
       <c r="W29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X29" t="n">
         <v>40</v>
@@ -6061,7 +6061,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC29" t="n">
         <v>22</v>
@@ -6106,59 +6106,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW29" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB29" t="n">
         <v>10</v>
       </c>
       <c r="BC29" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF29" t="n">
         <v>7.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>1.93</v>
       </c>
       <c r="G30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I30" t="n">
         <v>5.1</v>
@@ -6204,7 +6204,7 @@
         <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.49</v>
@@ -6231,22 +6231,22 @@
         <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U30" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V30" t="n">
         <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>13.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
         <v>42</v>
@@ -6255,34 +6255,34 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>55</v>
@@ -6297,19 +6297,19 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
         <v>6.8</v>
@@ -6318,7 +6318,7 @@
         <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX30" t="n">
         <v>9.6</v>
@@ -6327,10 +6327,10 @@
         <v>9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB30" t="n">
         <v>19.5</v>
@@ -6339,20 +6339,20 @@
         <v>19.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.2</v>
+        <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF30" t="n">
         <v>12.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>1.97</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>
@@ -6401,7 +6401,7 @@
         <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6416,28 +6416,28 @@
         <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V31" t="n">
         <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
         <v>16</v>
@@ -6452,7 +6452,7 @@
         <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
         <v>17.5</v>
@@ -6485,13 +6485,13 @@
         <v>95</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO31" t="n">
         <v>55</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>14.5</v>
@@ -6521,7 +6521,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
         <v>42</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
         <v>1.18</v>
       </c>
       <c r="N32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O32" t="n">
         <v>1.75</v>
@@ -6610,7 +6610,7 @@
         <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
         <v>1.13</v>
@@ -6625,7 +6625,7 @@
         <v>1.64</v>
       </c>
       <c r="V32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
         <v>1.47</v>
@@ -6637,7 +6637,7 @@
         <v>7.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AA32" t="n">
         <v>400</v>
@@ -6652,37 +6652,37 @@
         <v>16</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AG32" t="n">
         <v>16</v>
       </c>
       <c r="AH32" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ32" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="AK32" t="n">
-        <v>340</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AM32" t="n">
         <v>360</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP32" t="n">
         <v>6.2</v>
@@ -6706,7 +6706,7 @@
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX32" t="n">
         <v>15</v>
@@ -6721,26 +6721,26 @@
         <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BC32" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
       </c>
       <c r="BE32" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="BF32" t="n">
         <v>34</v>
       </c>
       <c r="BG32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -6774,25 +6774,25 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H33" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I33" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M33" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N33" t="n">
         <v>2.68</v>
@@ -6801,34 +6801,34 @@
         <v>1.57</v>
       </c>
       <c r="P33" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R33" t="n">
         <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T33" t="n">
         <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V33" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z33" t="n">
         <v>12</v>
@@ -6849,10 +6849,10 @@
         <v>32</v>
       </c>
       <c r="AF33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH33" t="n">
         <v>27</v>
@@ -6864,7 +6864,7 @@
         <v>110</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL33" t="n">
         <v>110</v>
@@ -6876,16 +6876,16 @@
         <v>130</v>
       </c>
       <c r="AO33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS33" t="n">
         <v>25</v>
@@ -6906,7 +6906,7 @@
         <v>22</v>
       </c>
       <c r="AY33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ33" t="n">
         <v>24</v>
@@ -6921,7 +6921,7 @@
         <v>55</v>
       </c>
       <c r="BD33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE33" t="n">
         <v>48</v>
@@ -6930,11 +6930,11 @@
         <v>38</v>
       </c>
       <c r="BG33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.68</v>
       </c>
       <c r="G34" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H34" t="n">
         <v>2.84</v>
@@ -6977,7 +6977,7 @@
         <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
         <v>3.5</v>
@@ -6995,7 +6995,7 @@
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q34" t="n">
         <v>2.1</v>
@@ -7010,7 +7010,7 @@
         <v>1.79</v>
       </c>
       <c r="U34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V34" t="n">
         <v>1.5</v>
@@ -7025,31 +7025,31 @@
         <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AE34" t="n">
         <v>980</v>
       </c>
       <c r="AF34" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AG34" t="n">
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AQ34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU34" t="n">
         <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF34" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG34" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-10.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:30:02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="G2" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>16.5</v>
+        <v>5.1</v>
       </c>
       <c r="AG2" t="n">
         <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.1</v>
+        <v>75</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>5.7</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.72</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:59:59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.6</v>
+        <v>750</v>
       </c>
       <c r="H3" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>95</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V3" t="n">
+        <v>50</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
         <v>1.42</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AP3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA3" t="n">
         <v>23</v>
       </c>
-      <c r="AH3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>32</v>
-      </c>
       <c r="BB3" t="n">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="BC3" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>1.38</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
         <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
         <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>4.1</v>
@@ -1175,94 +1175,94 @@
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
         <v>3.9</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="Z4" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>760</v>
+        <v>710</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="AD4" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AE4" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AF4" t="n">
         <v>7</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>790</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>430</v>
+      </c>
+      <c r="AP4" t="n">
         <v>16</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>17.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1271,10 +1271,10 @@
         <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1283,32 +1283,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>18.5</v>
+        <v>150</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1339,79 +1339,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
         <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Z5" t="n">
-        <v>150</v>
+        <v>980</v>
       </c>
       <c r="AA5" t="n">
         <v>700</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1423,86 +1423,86 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AI5" t="n">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS5" t="n">
         <v>12</v>
       </c>
-      <c r="AS5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AT5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BE5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
         <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1560,73 +1560,73 @@
         <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
         <v>80</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AL6" t="n">
         <v>95</v>
@@ -1635,68 +1635,68 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>20</v>
-      </c>
       <c r="BG6" t="n">
-        <v>19.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -1751,40 +1751,40 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="Y7" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="Z7" t="n">
         <v>980</v>
@@ -1793,43 +1793,43 @@
         <v>700</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
-        <v>420</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AK7" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AL7" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
@@ -1838,59 +1838,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
         <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>3.05</v>
       </c>
       <c r="AX7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>3.15</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
         <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>21</v>
+        <v>2.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
         <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
@@ -1954,7 +1954,7 @@
         <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.48</v>
@@ -1966,125 +1966,125 @@
         <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
         <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AF8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM8" t="n">
         <v>75</v>
       </c>
-      <c r="AL8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>320</v>
-      </c>
       <c r="AN8" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
         <v>14</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AS8" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA8" t="n">
         <v>14</v>
       </c>
-      <c r="BA8" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
         <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
         <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.19</v>
@@ -2151,16 +2151,16 @@
         <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V9" t="n">
         <v>2.28</v>
@@ -2169,13 +2169,13 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
         <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
         <v>19</v>
@@ -2223,16 +2223,16 @@
         <v>7.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
         <v>22</v>
@@ -2244,7 +2244,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
         <v>36</v>
@@ -2271,14 +2271,14 @@
         <v>55</v>
       </c>
       <c r="BF9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
@@ -2333,37 +2333,37 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="Y10" t="n">
         <v>19.5</v>
@@ -2375,31 +2375,31 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
         <v>20</v>
@@ -2411,49 +2411,49 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>14</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>16</v>
       </c>
       <c r="AR10" t="n">
         <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>65</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
@@ -2462,17 +2462,17 @@
         <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
         <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L11" t="n">
         <v>1.65</v>
@@ -2527,10 +2527,10 @@
         <v>1.16</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
         <v>1.47</v>
@@ -2539,58 +2539,58 @@
         <v>2.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.69</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.7</v>
       </c>
       <c r="W11" t="n">
         <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>900</v>
@@ -2599,7 +2599,7 @@
         <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
@@ -2608,65 +2608,65 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS11" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>19</v>
-      </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>1.84</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>1.84</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.4</v>
+        <v>1.84</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>3.05</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2715,7 +2715,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2724,7 +2724,7 @@
         <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
         <v>1.98</v>
@@ -2739,128 +2739,128 @@
         <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AB12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>24</v>
-      </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
         <v>21</v>
       </c>
       <c r="BF12" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BG12" t="n">
         <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
         <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
@@ -2915,85 +2915,85 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
         <v>500</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3008,19 +3008,19 @@
         <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
         <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="AX13" t="n">
         <v>8.4</v>
@@ -3029,32 +3029,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>9.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
         <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
         <v>2.7</v>
@@ -3097,40 +3097,40 @@
         <v>2.96</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
         <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.52</v>
@@ -3139,116 +3139,116 @@
         <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>980</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AA14" t="n">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="AB14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BC14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD14" t="n">
-        <v>17.5</v>
+        <v>1.66</v>
       </c>
       <c r="BE14" t="n">
         <v>19</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.1</v>
@@ -3309,140 +3309,140 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="AB15" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AC15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>230</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>210</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>18</v>
-      </c>
       <c r="AX15" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>2.62</v>
       </c>
       <c r="BC15" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>34</v>
+        <v>2.62</v>
       </c>
       <c r="BE15" t="n">
-        <v>12</v>
+        <v>2.64</v>
       </c>
       <c r="BF15" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -3503,7 +3503,7 @@
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
@@ -3512,131 +3512,131 @@
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW16" t="n">
         <v>44</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>28</v>
-      </c>
       <c r="AX16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AY16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB16" t="n">
         <v>9</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD16" t="n">
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR17" t="n">
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
@@ -3885,40 +3885,40 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
         <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="Y18" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="Z18" t="n">
         <v>980</v>
@@ -3927,13 +3927,13 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AD18" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AE18" t="n">
         <v>980</v>
@@ -3942,10 +3942,10 @@
         <v>980</v>
       </c>
       <c r="AG18" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AI18" t="n">
         <v>980</v>
@@ -3954,77 +3954,77 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AL18" t="n">
-        <v>130</v>
+        <v>980</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>16.5</v>
+        <v>2.34</v>
       </c>
       <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BC18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>13</v>
-      </c>
       <c r="BD18" t="n">
-        <v>15.5</v>
+        <v>2.32</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>2.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.36</v>
@@ -4088,7 +4088,7 @@
         <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
         <v>1.47</v>
@@ -4100,13 +4100,13 @@
         <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
         <v>980</v>
@@ -4121,13 +4121,13 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE19" t="n">
         <v>980</v>
@@ -4139,16 +4139,16 @@
         <v>40</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AI19" t="n">
         <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="AL19" t="n">
         <v>980</v>
@@ -4157,68 +4157,68 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.8</v>
+        <v>2.36</v>
       </c>
       <c r="AT19" t="n">
         <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AZ19" t="n">
         <v>9</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD19" t="n">
-        <v>14.5</v>
+        <v>3.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>46</v>
+        <v>2.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I20" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.23</v>
@@ -4273,146 +4273,146 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.13</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB20" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AM20" t="n">
-        <v>330</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AQ20" t="n">
         <v>17.5</v>
       </c>
       <c r="AR20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA20" t="n">
         <v>28</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
+      <c r="BB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC20" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.7</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4452,13 +4452,13 @@
         <v>3.95</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.28</v>
@@ -4467,13 +4467,13 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q21" t="n">
         <v>1.57</v>
@@ -4485,22 +4485,22 @@
         <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
         <v>2.08</v>
       </c>
       <c r="X21" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="Y21" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="Z21" t="n">
         <v>980</v>
@@ -4509,34 +4509,34 @@
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AE21" t="n">
         <v>980</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AI21" t="n">
         <v>980</v>
       </c>
       <c r="AJ21" t="n">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AL21" t="n">
         <v>980</v>
@@ -4545,68 +4545,68 @@
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
-        <v>600</v>
+        <v>980</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>2.94</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>15.5</v>
+        <v>3.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>2.18</v>
       </c>
       <c r="AT21" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>18</v>
+        <v>2.48</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.4</v>
+        <v>2.48</v>
       </c>
       <c r="BB21" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC21" t="n">
         <v>9</v>
       </c>
       <c r="BD21" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>2.14</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G22" t="n">
         <v>1.74</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.75</v>
       </c>
       <c r="H22" t="n">
         <v>5.8</v>
@@ -4649,10 +4649,10 @@
         <v>5.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
@@ -4661,34 +4661,34 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X22" t="n">
         <v>14.5</v>
@@ -4706,7 +4706,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>22</v>
@@ -4721,7 +4721,7 @@
         <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>80</v>
@@ -4730,13 +4730,13 @@
         <v>17.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL22" t="n">
         <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
         <v>11</v>
@@ -4748,7 +4748,7 @@
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR22" t="n">
         <v>40</v>
@@ -4763,25 +4763,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>19.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC22" t="n">
         <v>17</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4837,16 +4837,16 @@
         <v>5.2</v>
       </c>
       <c r="H23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.7</v>
       </c>
-      <c r="I23" t="n">
-        <v>1.71</v>
-      </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.27</v>
@@ -4855,37 +4855,37 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
         <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S23" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V23" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W23" t="n">
         <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y23" t="n">
         <v>14</v>
@@ -4897,28 +4897,28 @@
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC23" t="n">
         <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF23" t="n">
         <v>44</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH23" t="n">
         <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>110</v>
@@ -4933,19 +4933,19 @@
         <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO23" t="n">
         <v>6.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR23" t="n">
         <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>12.5</v>
       </c>
       <c r="AS23" t="n">
         <v>18</v>
@@ -4957,7 +4957,7 @@
         <v>10.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
@@ -4966,13 +4966,13 @@
         <v>42</v>
       </c>
       <c r="AY23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
         <v>90</v>
@@ -4987,14 +4987,14 @@
         <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG23" t="n">
         <v>6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="H24" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L24" t="n">
         <v>1.55</v>
@@ -5049,146 +5049,146 @@
         <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R24" t="n">
         <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.53</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X24" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
         <v>14.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
         <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AK24" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL24" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA24" t="n">
-        <v>27</v>
+        <v>4.7</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G25" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H25" t="n">
         <v>2.52</v>
@@ -5237,7 +5237,7 @@
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5249,37 +5249,37 @@
         <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R25" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S25" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U25" t="n">
         <v>3.25</v>
       </c>
       <c r="V25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
         <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>40</v>
@@ -5297,10 +5297,10 @@
         <v>23</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
         <v>12.5</v>
@@ -5312,19 +5312,19 @@
         <v>44</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM25" t="n">
         <v>38</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AP25" t="n">
         <v>30</v>
@@ -5360,13 +5360,13 @@
         <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
         <v>40</v>
       </c>
       <c r="BC25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
         <v>24</v>
@@ -5375,14 +5375,14 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </